--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -9,7 +9,10 @@
   <sheets>
     <sheet name="Rounds" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Holes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Baseline Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Shots" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Clubs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Handicap History" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Baseline Summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,40 +439,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AO2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="27" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="26" customWidth="1" min="23" max="23"/>
-    <col width="19" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="18" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="19" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="27" customWidth="1" min="29" max="29"/>
+    <col width="17" customWidth="1" min="30" max="30"/>
+    <col width="19" customWidth="1" min="31" max="31"/>
+    <col width="20" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="19" customWidth="1" min="34" max="34"/>
+    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="14" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="11" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -535,95 +548,145 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>one_putts</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>three_putts</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>putts_per_gir</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>gir_hits</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>gir_pct</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>fairway_hits</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>fairway_chances_inferred</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>fairway_pct_inferred</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>scramble_chances_inferred</t>
-        </is>
-      </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>scramble_saves_inferred</t>
+          <t>fairway_chances</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>scramble_pct_inferred</t>
+          <t>fairway_pct</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>updown_chances_native</t>
+          <t>scramble_chances</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>updowns_native</t>
+          <t>scramble_saves</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>sand_save_chances_native</t>
+          <t>scramble_pct</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>sand_chances_native</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>sand_saves_native</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>penalties</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>avg_drive_yd</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>longest_drive_yd</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>avg_approach_proximity_yd</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>sg_total_approx</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>sg_off_tee_approx</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>sg_approach_approx</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>sg_short_game_approx</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>sg_putting_approx</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>user_hcp</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>drive_hcp</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>approach_hcp</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>chip_hcp</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>sand_hcp</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>putt_hcp</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>par_inferred_sum</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>pulled_at</t>
         </is>
@@ -673,62 +736,92 @@
         <v>38</v>
       </c>
       <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>27.8</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>14</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>64.3</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>13</v>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>237.3</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-22.76</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-14.24</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-3.82</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-20.4148</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>-7.49223</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AK2" t="n">
         <v>-30</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AL2" t="n">
         <v>-30</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AM2" t="n">
         <v>-4.95085</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AN2" t="n">
         <v>-10.2852</v>
       </c>
-      <c r="AD2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2026-06-06 22:59 UTC</t>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>2026-06-06 23:18 UTC</t>
         </is>
       </c>
     </row>
@@ -743,29 +836,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="23" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
-    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -791,82 +887,97 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>par_calibrated</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>shots</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>score_to_par</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>putts</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>penalties</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>gir</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>fairway_hit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>fairway_miss_left</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>fairway_miss_right</t>
-        </is>
-      </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>fw_miss_left</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>fw_miss_right</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>updown_chance_native</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>updown_native</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>sand_save_chance_native</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>sand_chance_native</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>sand_save_native</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>hole_length_yd_inferred</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>par_inferred</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>score_to_par_inferred</t>
+          <t>hole_len_yd</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>scramble_chance_inferred</t>
+          <t>drive_yd</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>scramble_save_inferred</t>
+          <t>approach_proximity_yd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>scramble_chance</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>scramble_save</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>sg_hole_approx</t>
         </is>
       </c>
     </row>
@@ -888,28 +999,28 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -921,19 +1032,28 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
         <v>348.7</v>
       </c>
-      <c r="Q2" t="n">
-        <v>4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2</v>
-      </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>186.8</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-1.448</v>
       </c>
     </row>
     <row r="3">
@@ -954,17 +1074,17 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
         <v>4</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>3</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -975,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -987,19 +1107,26 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>115.8</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>30.9</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-1.026</v>
       </c>
     </row>
     <row r="4">
@@ -1020,25 +1147,25 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
         <v>2</v>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1053,19 +1180,28 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
         <v>315.1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>253.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-1.048</v>
       </c>
     </row>
     <row r="5">
@@ -1089,22 +1225,22 @@
         <v>5</v>
       </c>
       <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1119,19 +1255,28 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>505.7</v>
       </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>257.2</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>24.9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.322</v>
       </c>
     </row>
     <row r="6">
@@ -1152,28 +1297,28 @@
         <v>5</v>
       </c>
       <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
         <v>6</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1185,19 +1330,28 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>346</v>
       </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>152.9</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-1.466</v>
       </c>
     </row>
     <row r="7">
@@ -1218,28 +1372,28 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
         <v>7</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1251,19 +1405,26 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
         <v>155.3</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>4</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>13.6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-3.238</v>
       </c>
     </row>
     <row r="8">
@@ -1287,22 +1448,22 @@
         <v>5</v>
       </c>
       <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1317,19 +1478,28 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
         <v>280.6</v>
       </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>237.6</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-1.166</v>
       </c>
     </row>
     <row r="9">
@@ -1353,22 +1523,22 @@
         <v>4</v>
       </c>
       <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1383,19 +1553,28 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>374.6</v>
       </c>
-      <c r="Q9" t="n">
-        <v>4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>269.9</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>14.9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.051</v>
       </c>
     </row>
     <row r="10">
@@ -1416,25 +1595,25 @@
         <v>9</v>
       </c>
       <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
         <v>6</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1449,19 +1628,28 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>431.3</v>
       </c>
-      <c r="Q10" t="n">
-        <v>4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>242.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>5.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-1.528</v>
       </c>
     </row>
     <row r="11">
@@ -1482,28 +1670,28 @@
         <v>10</v>
       </c>
       <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
         <v>5</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1515,19 +1703,28 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>363.7</v>
       </c>
-      <c r="Q11" t="n">
-        <v>4</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>265.8</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>23.8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.637</v>
       </c>
     </row>
     <row r="12">
@@ -1548,28 +1745,28 @@
         <v>11</v>
       </c>
       <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
         <v>4</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
         <v>2</v>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1581,19 +1778,26 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>166.3</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>4.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.8090000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1614,28 +1818,28 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
         <v>7</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
         <v>2</v>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1647,19 +1851,28 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>418.3</v>
       </c>
-      <c r="Q13" t="n">
-        <v>4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3</v>
-      </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>237.2</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>10.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-2.173</v>
       </c>
     </row>
     <row r="14">
@@ -1680,25 +1893,25 @@
         <v>13</v>
       </c>
       <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
         <v>6</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
         <v>3</v>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1713,19 +1926,28 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>383</v>
       </c>
-      <c r="Q14" t="n">
-        <v>4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2</v>
-      </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>241.7</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-1.856</v>
       </c>
     </row>
     <row r="15">
@@ -1746,16 +1968,16 @@
         <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -1764,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1779,19 +2001,28 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>473.6</v>
       </c>
-      <c r="Q15" t="n">
-        <v>5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3</v>
-      </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>215.1</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-2.877</v>
       </c>
     </row>
     <row r="16">
@@ -1812,28 +2043,28 @@
         <v>15</v>
       </c>
       <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="n">
         <v>5</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
         <v>2</v>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1845,19 +2076,28 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
         <v>356.1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>254.1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>12.9</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.6879999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1878,28 +2118,28 @@
         <v>16</v>
       </c>
       <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
         <v>4</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
         <v>2</v>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1911,19 +2151,26 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
         <v>119.1</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>17.9</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.833</v>
       </c>
     </row>
     <row r="18">
@@ -1947,22 +2194,22 @@
         <v>5</v>
       </c>
       <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>3</v>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1977,19 +2224,28 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
         <v>252</v>
       </c>
-      <c r="Q18" t="n">
-        <v>4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>240.5</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>4.3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-1.631</v>
       </c>
     </row>
     <row r="19">
@@ -2013,22 +2269,22 @@
         <v>4</v>
       </c>
       <c r="F19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
         <v>2</v>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2043,19 +2299,28 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
         <v>424.4</v>
       </c>
-      <c r="Q19" t="n">
-        <v>4</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>267.9</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.033</v>
       </c>
     </row>
   </sheetData>
@@ -2069,10 +2334,6180 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:O96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>round_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>hole_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>shot_num</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>club_category</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>shot_distance_yd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>start_dist_to_pin_yd</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>end_dist_to_pin_yd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lie_approx</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>is_tee</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>is_putt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>penalties</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>category_approx</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>sg_shot_approx</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>186.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>348.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>167.8</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.133</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4 Iron</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>167.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>136.3</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.638</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6 Iron</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>136.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.313</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>club12</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.747</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8 Iron</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.405</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.055</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.579</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>253.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>315.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>club11</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.757</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>club13</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.041</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.299</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>257.2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>505.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.152</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>4 Iron</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.472</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4 Iron</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>154</v>
+      </c>
+      <c r="H19" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.017</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="H20" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.038</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.357</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>346</v>
+      </c>
+      <c r="I22" t="n">
+        <v>193.7</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.277</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4 Iron</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>193.7</v>
+      </c>
+      <c r="I23" t="n">
+        <v>154.8</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.577</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>160.2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>154.8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.114</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>club12</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.341</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.777</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>club11</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="I29" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.731</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>6</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>club13</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>91</v>
+      </c>
+      <c r="H30" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="I30" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.596</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>club11</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H31" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I31" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>-0.554</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>club11</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>-0.641</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H33" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>0.048</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3 Wood</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>237.6</v>
+      </c>
+      <c r="H35" t="n">
+        <v>280.6</v>
+      </c>
+      <c r="I35" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>9 Iron</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>-0.6889999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>7</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>9 Iron</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="I37" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>-0.414</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>7</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>-0.067</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>7</v>
+      </c>
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="H40" t="n">
+        <v>374.6</v>
+      </c>
+      <c r="I40" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>7 Iron</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="H41" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="I41" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>-0.249</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H42" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>0.078</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>8</v>
+      </c>
+      <c r="D43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>9</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>242.5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>431.3</v>
+      </c>
+      <c r="I44" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>-0.078</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>9</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>club4</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="I45" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>-0.726</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>9</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4 Iron</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="H46" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="I46" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>-0.526</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>9</v>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>club12</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>9</v>
+      </c>
+      <c r="D48" t="n">
+        <v>5</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H48" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>-0.211</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>9</v>
+      </c>
+      <c r="D49" t="n">
+        <v>6</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>10</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>265.8</v>
+      </c>
+      <c r="H50" t="n">
+        <v>363.7</v>
+      </c>
+      <c r="I50" t="n">
+        <v>111</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>10</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>club11</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="H51" t="n">
+        <v>111</v>
+      </c>
+      <c r="I51" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>-0.638</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>10</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>club13</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="H52" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="I52" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>10</v>
+      </c>
+      <c r="D53" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>10</v>
+      </c>
+      <c r="D54" t="n">
+        <v>5</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>0.266</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>11</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>6 Iron</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>162.4</v>
+      </c>
+      <c r="H55" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="I55" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>11</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>club12</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H56" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="I56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>11</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H57" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>-0.262</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>11</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>12</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>237.2</v>
+      </c>
+      <c r="H59" t="n">
+        <v>418.3</v>
+      </c>
+      <c r="I59" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>-0.06900000000000001</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>12</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>4 Iron</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="H60" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>-0.423</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>12</v>
+      </c>
+      <c r="D61" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>club11</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="H61" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="I61" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>12</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>club11</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="H62" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="I62" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>-0.744</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>12</v>
+      </c>
+      <c r="D63" t="n">
+        <v>5</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>club11</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H63" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>-0.376</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>12</v>
+      </c>
+      <c r="D64" t="n">
+        <v>6</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H64" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>-0.024</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>12</v>
+      </c>
+      <c r="D65" t="n">
+        <v>7</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>13</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>241.7</v>
+      </c>
+      <c r="H66" t="n">
+        <v>383</v>
+      </c>
+      <c r="I66" t="n">
+        <v>151.6</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>0.014</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>13</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>4 Iron</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>151.6</v>
+      </c>
+      <c r="I67" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>-0.588</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>13</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>club12</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="H68" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="I68" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>-0.225</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>13</v>
+      </c>
+      <c r="D69" t="n">
+        <v>4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H69" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I69" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>-0.491</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>13</v>
+      </c>
+      <c r="D70" t="n">
+        <v>5</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>-0.579</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>13</v>
+      </c>
+      <c r="D71" t="n">
+        <v>6</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>14</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>215.1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>473.6</v>
+      </c>
+      <c r="I72" t="n">
+        <v>260</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>-0.335</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>14</v>
+      </c>
+      <c r="D73" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>club4</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="H73" t="n">
+        <v>260</v>
+      </c>
+      <c r="I73" t="n">
+        <v>196.6</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>-0.591</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>14</v>
+      </c>
+      <c r="D74" t="n">
+        <v>3</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>4 Iron</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="H74" t="n">
+        <v>196.6</v>
+      </c>
+      <c r="I74" t="n">
+        <v>142.9</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
+        <v>-0.519</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>14</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>4 Iron</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="H75" t="n">
+        <v>142.9</v>
+      </c>
+      <c r="I75" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>-0.634</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>14</v>
+      </c>
+      <c r="D76" t="n">
+        <v>5</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>9 Iron</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="H76" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="I76" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
+        <v>-0.424</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>14</v>
+      </c>
+      <c r="D77" t="n">
+        <v>6</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H77" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="I77" t="n">
+        <v>20</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="O77" t="n">
+        <v>-0.592</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>14</v>
+      </c>
+      <c r="D78" t="n">
+        <v>7</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>club13</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>20</v>
+      </c>
+      <c r="H78" t="n">
+        <v>20</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O78" t="n">
+        <v>0.218</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>15</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>254.1</v>
+      </c>
+      <c r="H79" t="n">
+        <v>356.1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="O79" t="n">
+        <v>0.103</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>15</v>
+      </c>
+      <c r="D80" t="n">
+        <v>2</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>6 Iron</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>62</v>
+      </c>
+      <c r="H80" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="I80" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O80" t="n">
+        <v>-0.575</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>15</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>club13</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="H81" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="I81" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O81" t="n">
+        <v>-0.261</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>15</v>
+      </c>
+      <c r="D82" t="n">
+        <v>4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H82" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O82" t="n">
+        <v>0.032</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>15</v>
+      </c>
+      <c r="D83" t="n">
+        <v>5</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O83" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>16</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>8 Iron</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>146.4</v>
+      </c>
+      <c r="H84" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="I84" t="n">
+        <v>29</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O84" t="n">
+        <v>-0.521</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>16</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>club12</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H85" t="n">
+        <v>29</v>
+      </c>
+      <c r="I85" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="O85" t="n">
+        <v>-0.477</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>16</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="H86" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O86" t="n">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>16</v>
+      </c>
+      <c r="D87" t="n">
+        <v>4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O87" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>17</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>3 Wood</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>240.5</v>
+      </c>
+      <c r="H88" t="n">
+        <v>252</v>
+      </c>
+      <c r="I88" t="n">
+        <v>24</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="O88" t="n">
+        <v>-0.078</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>17</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>club13</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="H89" t="n">
+        <v>24</v>
+      </c>
+      <c r="I89" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="O89" t="n">
+        <v>-0.286</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>17</v>
+      </c>
+      <c r="D90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>2</v>
+      </c>
+      <c r="H90" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I90" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O90" t="n">
+        <v>-0.701</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>17</v>
+      </c>
+      <c r="D91" t="n">
+        <v>4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O91" t="n">
+        <v>-0.579</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>17</v>
+      </c>
+      <c r="D92" t="n">
+        <v>5</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O92" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>18</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>267.9</v>
+      </c>
+      <c r="H93" t="n">
+        <v>424.4</v>
+      </c>
+      <c r="I93" t="n">
+        <v>156.8</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="O93" t="n">
+        <v>0.064</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>18</v>
+      </c>
+      <c r="D94" t="n">
+        <v>2</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>6 Iron</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>151.8</v>
+      </c>
+      <c r="H94" t="n">
+        <v>156.8</v>
+      </c>
+      <c r="I94" t="n">
+        <v>5</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="O94" t="n">
+        <v>0.179</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>18</v>
+      </c>
+      <c r="D95" t="n">
+        <v>3</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H95" t="n">
+        <v>5</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O95" t="n">
+        <v>-0.223</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>18</v>
+      </c>
+      <c r="D96" t="n">
+        <v>4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="O96" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>club_category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>smart_distance_yd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>normalized_yd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tee_yd</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fairway_yd</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>rough_yd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>sand_yd</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>longest_yd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>range_low_yd</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>range_high_yd</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dispersion_yd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>gir_pct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>usage_count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>262.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>262.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>266.8</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>270.4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>257.023</v>
+      </c>
+      <c r="K2" t="n">
+        <v>267.043</v>
+      </c>
+      <c r="L2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3 Wood</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>203.7</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>239.8</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>club3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>184</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>club4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>172.9</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6 Iron</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>155.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>155.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>151.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>126.7</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>149.003</v>
+      </c>
+      <c r="K6" t="n">
+        <v>156.705</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>50</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>143.7</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>160.3</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7 Iron</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>100</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4 Iron</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>117.015</v>
+      </c>
+      <c r="K9" t="n">
+        <v>136.906</v>
+      </c>
+      <c r="L9" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>8 Iron</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>122</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>146.1</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>9 Iron</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>112.163</v>
+      </c>
+      <c r="K11" t="n">
+        <v>112.163</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>club11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>98</v>
+      </c>
+      <c r="G12" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>100.952</v>
+      </c>
+      <c r="K12" t="n">
+        <v>102.889</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>club12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>club13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>72.9575</v>
+      </c>
+      <c r="K14" t="n">
+        <v>82.7062</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>round_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>user_hcp</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>drive_hcp</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>approach_hcp</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>chip_hcp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sand_hcp</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>putt_hcp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-20.4148</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-7.49223</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-4.95085</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-10.2852</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -2082,12 +8517,11 @@
           <t>ARCCOS STROKES-GAINED BASELINE</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rounds in baseline</t>
+          <t>Rounds</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2097,293 +8531,361 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Holes / Shots</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>18 / 95</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Date range</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>2026-06-06 -&gt; 2026-06-06</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Metric (averaged across all pulled rounds)</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Metric (avg across rounds)</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Avg score</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Avg score to par</t>
+          <t>Avg score</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Avg putts / round</t>
+          <t>Avg score to par</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GIR %</t>
+          <t>SG total (approx vs scratch)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.8</v>
+        <v>-22.76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fairway % (par-3s excluded via inferred par)</t>
+          <t>SG off-tee (approx)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64.3</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Scrambling % (DERIVED: missed GIR, holed &lt;= inferred par)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>0</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SG approach (approx)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-14.24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Scramble chances / round (derived)</t>
+          <t>SG short game (approx) — PRIORITY</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>13</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Scramble saves / round (derived)</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>0</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SG putting (approx)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-3.82</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Up&amp;down chances / round (NATIVE — unpopulated so far)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>0</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GIR %</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>27.8</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Up&amp;downs / round (NATIVE — unpopulated so far)</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>0</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fairway %</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>64.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Sand save chances / round (NATIVE — unpopulated so far)</t>
+          <t>Scrambling % (derived) — PRIORITY</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Sand saves / round (NATIVE — unpopulated so far)</t>
+          <t>Approach proximity (yd) — PRIORITY</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>driveHcp (Arccos category metric — SG proxy, unverified)</t>
+          <t>Putts / round</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-7.49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>approachHcp (SG proxy, unverified)</t>
+          <t>1-putts / round</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>chipHcp (SG proxy, unverified) — SHORT GAME</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>-30</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3-putts / round</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>sandHcp (SG proxy, unverified) — SHORT GAME</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>-4.95</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Putts per GIR</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>puttHcp (SG proxy, unverified)</t>
+          <t>Avg drive (yd)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-10.29</v>
+        <v>237.3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Longest drive (yd)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>269.9</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>PROVENANCE</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Penalties / round</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Source: UNOFFICIAL reverse-engineered Arccos Golf API (api.arccosgolf.com),</t>
-        </is>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>chipHcp (Arccos metric) — PRIORITY</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-30</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>pulled by a custom stdlib Python client (pull_arccos.py); endpoints derived</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>from skhavari/arccos-export; not affiliated with Arccos Golf LLC; may break</t>
-        </is>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>sandHcp (Arccos metric) — PRIORITY</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>-4.95</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>if Arccos changes their backend.</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>PROVENANCE &amp; GLOSSARY</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-06 23:00 UTC   |   Rounds: 1</t>
+          <t>Source: UNOFFICIAL reverse-engineered Arccos API (api.arccosgolf.com), pulled by</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CAVEATS: (1) *_inferred columns are DERIVED — per-hole par is not exposed by</t>
+          <t>pull_arccos.py (custom stdlib client). Not affiliated with Arccos Golf LLC.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>the API; par inferred from GPS hole length (&lt;= 245yd par3, &lt;= 470 par4, else par5).</t>
+          <t>Date pulled: 2026-06-06 23:18 UTC  |  Rounds: 1  Shots: 95</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>(2) Scrambling is derived (missed GIR + holed out &lt;= inferred par); native</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>isUpDown/isSandSave flags were unpopulated at pull time and are kept verbatim.</t>
+          <t>REAL (native API): score, putts, GIR, fairway flags, penalties, clubs/terrain</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>(3) drive/approach/chip/sand/putt Hcp are Arccos per-category handicap-style</t>
+          <t>distances + dispersion + GIR%, Arccos category handicaps (drive/approach/chip/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>metrics with UNVERIFIED semantics — a labeled SG proxy, NOT true strokes</t>
+          <t>sand/putt Hcp — proprietary NEGATIVE scale, NOT USGA; clamped at -30).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>gained (the /v2/sga endpoint is permission-gated for dashboard tokens).</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>(4) GPS coordinates and round notes are excluded from all outputs.</t>
+          <t>DERIVED (computed here, labeled _approx / _calibrated / _inferred):</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>- par_calibrated: GPS hole length -&gt; par class, nudged so holes sum to course par.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>- Strokes Gained (sg_*_approx): RECONSTRUCTED from shot start/end GPS distance-to-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  pin vs a published baseline (Broadie, 'Assessing Golfer Performance on the PGA TOUR' Table 9 (2003-2010 ShotLink) + PGA Tour SG-Putting 2010 baseline; same as 'Every Shot Counts'.). The official /v2/sga endpoint is</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  permission-gated (401) for dashboard tokens, so SG is rebuilt, NOT from Arccos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Lie per shot is approximate (only tee/green are reliable) — treat SG as indicative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>- scramble_pct: missed GIR + holed out &lt;= par_calibrated. Native isUpDown flags were</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  unpopulated at pull time (kept verbatim as *_native).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>- approach_proximity_yd: end distance-to-pin of the last non-putt shot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GPS coordinates, names, email, DOB are EXCLUDED from all outputs.</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Shots" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Clubs" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Handicap History" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Baseline Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Career Stats" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Baseline Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +33,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
@@ -68,10 +73,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -439,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO2"/>
+  <dimension ref="A1:AU2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -453,36 +459,42 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="17" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="21" customWidth="1" min="24" max="24"/>
-    <col width="19" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="18" customWidth="1" min="28" max="28"/>
-    <col width="27" customWidth="1" min="29" max="29"/>
-    <col width="17" customWidth="1" min="30" max="30"/>
-    <col width="19" customWidth="1" min="31" max="31"/>
-    <col width="20" customWidth="1" min="32" max="32"/>
-    <col width="22" customWidth="1" min="33" max="33"/>
-    <col width="19" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
-    <col width="11" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
-    <col width="10" customWidth="1" min="39" max="39"/>
-    <col width="10" customWidth="1" min="40" max="40"/>
-    <col width="11" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="19" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
+    <col width="27" customWidth="1" min="30" max="30"/>
+    <col width="17" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="20" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="19" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="36" max="36"/>
+    <col width="20" customWidth="1" min="37" max="37"/>
+    <col width="21" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="11" customWidth="1" min="42" max="42"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="10" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="11" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -543,150 +555,180 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>pace_of_play</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>putts</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>one_putts</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>three_putts</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>putts_per_gir</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>gir_hits</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>gir_pct</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>fairway_hits</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>fairway_chances</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>fairway_pct</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>scramble_chances</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>scramble_saves</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>scramble_pct</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>sand_chances_native</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>sand_saves_native</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>penalties</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>avg_drive_yd</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>longest_drive_yd</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>avg_approach_proximity_yd</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>sg_total_approx</t>
-        </is>
-      </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>sg_off_tee_approx</t>
+          <t>sg_total_arccos</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>sg_approach_approx</t>
+          <t>sg_off_tee_arccos</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>sg_short_game_approx</t>
+          <t>sg_approach_arccos</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>sg_putting_approx</t>
+          <t>sg_short_arccos</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>sg_putting_arccos</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>sg_total_broadie</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>sg_off_tee_broadie</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>sg_approach_broadie</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>sg_short_broadie</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>sg_putting_broadie</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
           <t>user_hcp</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>drive_hcp</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>approach_hcp</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>chip_hcp</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>sand_hcp</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>putt_hcp</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>pulled_at</t>
         </is>
@@ -732,41 +774,43 @@
       <c r="K2" t="n">
         <v>24</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>05:05:52</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
         <v>38</v>
       </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
       <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>2.4</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>5</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>27.8</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>9</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>14</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>64.3</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>13</v>
       </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
       <c r="W2" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -775,53 +819,71 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
         <v>237.3</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>269.9</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>12</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
+        <v>-23.7</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>-22.76</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AK2" t="n">
         <v>-0.71</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AL2" t="n">
         <v>-14.24</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AM2" t="n">
         <v>-4</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AN2" t="n">
         <v>-3.82</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AO2" t="n">
         <v>-20.4148</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AP2" t="n">
         <v>-7.49223</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AQ2" t="n">
         <v>-30</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AR2" t="n">
         <v>-30</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AS2" t="n">
         <v>-4.95085</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AT2" t="n">
         <v>-10.2852</v>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>2026-06-06 23:18 UTC</t>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2026-06-06 23:33 UTC</t>
         </is>
       </c>
     </row>
@@ -836,32 +898,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:Y19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="17" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="17" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -887,97 +951,107 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>par_calibrated</t>
+          <t>par</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>par_source</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>shots</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>net_score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>score_to_par</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>putts</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>penalties</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>gir</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>fairway_hit</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>fw_miss_left</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>fw_miss_right</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>updown_chance_native</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>updown_native</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>sand_chance_native</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>sand_save_native</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>hole_len_yd</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>drive_yd</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>approach_proximity_yd</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>scramble_chance</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>scramble_save</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>sg_hole_approx</t>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sg_hole_broadie</t>
         </is>
       </c>
     </row>
@@ -1001,32 +1075,34 @@
       <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1038,21 +1114,27 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
         <v>348.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>186.8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>1.7</v>
       </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
       <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
         <v>-1.448</v>
       </c>
     </row>
@@ -1076,21 +1158,23 @@
       <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>4</v>
       </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
       <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
         <v>3</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
@@ -1101,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1113,19 +1197,25 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>115.8</v>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="n">
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
         <v>30.9</v>
       </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
       <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
         <v>-1.026</v>
       </c>
     </row>
@@ -1149,29 +1239,31 @@
       <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
       <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -1186,21 +1278,27 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
         <v>315.1</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>253.3</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>4.1</v>
       </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
       <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
         <v>-1.048</v>
       </c>
     </row>
@@ -1224,29 +1322,31 @@
       <c r="E5" t="n">
         <v>5</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>5</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1261,21 +1361,27 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>505.7</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>257.2</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>24.9</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
       <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
         <v>-0.322</v>
       </c>
     </row>
@@ -1299,32 +1405,34 @@
       <c r="E6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1336,21 +1444,27 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>346</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>152.9</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>3.7</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
       <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>-1.466</v>
       </c>
     </row>
@@ -1374,32 +1488,34 @@
       <c r="E7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>7</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>4</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1411,19 +1527,25 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
         <v>155.3</v>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="n">
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
         <v>13.6</v>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
       <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
         <v>-3.238</v>
       </c>
     </row>
@@ -1445,31 +1567,33 @@
         <v>7</v>
       </c>
       <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>5</v>
       </c>
-      <c r="F8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1484,21 +1608,27 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>280.6</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>237.6</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
       <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
         <v>-1.166</v>
       </c>
     </row>
@@ -1522,29 +1652,31 @@
       <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>4</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1559,21 +1691,27 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
         <v>374.6</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>269.9</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>14.9</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
       <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
         <v>-0.051</v>
       </c>
     </row>
@@ -1595,31 +1733,33 @@
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>6</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1634,21 +1774,27 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
         <v>431.3</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>242.5</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>5.2</v>
       </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
       <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
         <v>-1.528</v>
       </c>
     </row>
@@ -1672,32 +1818,34 @@
       <c r="E11" t="n">
         <v>4</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>5</v>
       </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
       <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1709,21 +1857,27 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
         <v>363.7</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>265.8</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>23.8</v>
       </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
       <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
         <v>-0.637</v>
       </c>
     </row>
@@ -1747,32 +1901,34 @@
       <c r="E12" t="n">
         <v>3</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>4</v>
       </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
       <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1784,19 +1940,25 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
         <v>166.3</v>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="n">
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
         <v>4.5</v>
       </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
       <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
         <v>-0.8090000000000001</v>
       </c>
     </row>
@@ -1818,34 +1980,36 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
         <v>7</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3</v>
       </c>
       <c r="H13" t="n">
         <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1857,21 +2021,27 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
         <v>418.3</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>237.2</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>10.5</v>
       </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
       <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
         <v>-2.173</v>
       </c>
     </row>
@@ -1895,29 +2065,31 @@
       <c r="E14" t="n">
         <v>4</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
         <v>6</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1932,21 +2104,27 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
         <v>383</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>241.7</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
       <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
         <v>-1.856</v>
       </c>
     </row>
@@ -1970,20 +2148,22 @@
       <c r="E15" t="n">
         <v>5</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
         <v>7</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1992,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2007,21 +2187,27 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
         <v>473.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>215.1</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
         <v>20</v>
       </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
       <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
         <v>-2.877</v>
       </c>
     </row>
@@ -2045,32 +2231,34 @@
       <c r="E16" t="n">
         <v>4</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
         <v>5</v>
       </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
       <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2082,21 +2270,27 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
         <v>356.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>254.1</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>12.9</v>
       </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
       <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
         <v>-0.6879999999999999</v>
       </c>
     </row>
@@ -2120,32 +2314,34 @@
       <c r="E17" t="n">
         <v>3</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
         <v>4</v>
       </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
       <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2157,19 +2353,25 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
         <v>119.1</v>
       </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="n">
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
         <v>17.9</v>
       </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
       <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
         <v>-0.833</v>
       </c>
     </row>
@@ -2191,31 +2393,33 @@
         <v>17</v>
       </c>
       <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
         <v>5</v>
       </c>
-      <c r="F18" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
         <v>3</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2230,21 +2434,27 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
         <v>252</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>240.5</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>4.3</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
       <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
         <v>-1.631</v>
       </c>
     </row>
@@ -2268,29 +2478,31 @@
       <c r="E19" t="n">
         <v>4</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
         <v>4</v>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
       <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2305,21 +2517,27 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
         <v>424.4</v>
       </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
         <v>267.9</v>
       </c>
-      <c r="T19" t="n">
+      <c r="V19" t="n">
         <v>5</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
       <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
         <v>0.033</v>
       </c>
     </row>
@@ -2619,12 +2837,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>club12</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2676,12 +2894,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2733,12 +2951,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2847,12 +3065,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2904,12 +3122,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2961,12 +3179,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3075,12 +3293,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>club11</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3132,12 +3350,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>club13</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3189,12 +3407,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3246,12 +3464,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3474,12 +3692,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3531,12 +3749,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3759,12 +3977,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>club12</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3816,12 +4034,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3873,12 +4091,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,12 +4205,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>club11</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4044,12 +4262,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>club13</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4101,12 +4319,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>club11</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4158,12 +4376,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>club11</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4215,12 +4433,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4272,12 +4490,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4500,12 +4718,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4557,12 +4775,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -4728,12 +4946,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -4785,12 +5003,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -4899,12 +5117,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>club4</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5013,12 +5231,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>club12</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -5070,12 +5288,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -5127,12 +5345,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -5241,12 +5459,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>club11</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -5298,12 +5516,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>club13</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -5355,12 +5573,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -5412,12 +5630,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -5526,12 +5744,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>club12</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -5583,12 +5801,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -5640,12 +5858,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -5811,12 +6029,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>club11</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -5868,12 +6086,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>club11</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -5925,12 +6143,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>club11</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -5982,12 +6200,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -6039,12 +6257,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -6210,12 +6428,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>club12</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -6267,12 +6485,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -6324,12 +6542,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -6381,12 +6599,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -6495,12 +6713,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>club4</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -6723,12 +6941,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -6780,12 +6998,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>club13</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -6951,12 +7169,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>club13</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -7008,12 +7226,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -7065,12 +7283,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -7179,12 +7397,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>club12</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -7236,12 +7454,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -7293,12 +7511,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -7407,12 +7625,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>club13</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -7464,12 +7682,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -7521,12 +7739,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -7578,12 +7796,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -7749,12 +7967,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -7806,12 +8024,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>Putter</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -7857,23 +8075,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7889,60 +8109,70 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>club_make</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>club_model</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>smart_distance_yd</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>normalized_yd</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tee_yd</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>fairway_yd</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rough_yd</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sand_yd</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>longest_yd</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>range_low_yd</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>range_high_yd</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>dispersion_yd</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>gir_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>usage_count</t>
         </is>
@@ -7959,32 +8189,42 @@
           <t>Driver</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Cobra</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DS-ADAPT LS</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>262.8</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>262.8</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>266.8</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
         <v>270.4</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>257.023</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>267.043</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>10</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
         <v>12</v>
       </c>
     </row>
@@ -7999,41 +8239,59 @@
           <t>Wood</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cobra</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DS-ADAPT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>203.7</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
         <v>239.8</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>club3</t>
+          <t>5 Wood</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cobra</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DS-ADAPT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>184</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -8042,26 +8300,36 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>club4</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cobra</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DS-ADAPT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>172.9</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -8070,7 +8338,9 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8085,38 +8355,48 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Srixon</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ZX7 Mk II</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>155.8</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>155.8</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>161.9</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>151.5</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>126.7</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
         <v>161.9</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>149.003</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>156.705</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>7.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>50</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8131,22 +8411,32 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Srixon</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ZX7 Mk II</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>143.7</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
         <v>160.3</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8161,24 +8451,34 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Srixon</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ZX7 Mk II</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>133.6</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
         <v>121.1</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
         <v>100</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8193,36 +8493,46 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Srixon</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ZX7 Mk II</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>126.2</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>126.2</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
         <v>146.9</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>106.6</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="n">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="n">
         <v>153.5</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>117.015</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>136.906</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>19.9</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>33.3</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
     </row>
@@ -8237,24 +8547,34 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Srixon</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ZX7 Mk II</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>122</v>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="n">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
         <v>146.1</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
         <v>50</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8269,95 +8589,123 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Srixon</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ZX7 Mk II</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
         <v>108.1</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>108.1</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="n">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
         <v>112.2</v>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="n">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
         <v>112.2</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>112.163</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>112.163</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>club11</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cleveland</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RTX 6 ZipCore</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>100.3</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>100.3</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="n">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
         <v>98</v>
       </c>
-      <c r="G12" t="n">
-        <v>104.5</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
         <v>104.5</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="L12" t="n">
         <v>100.952</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>102.889</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>1.9</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>club12</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Cleveland</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>RTX 6 ZipCore</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>86.8</v>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -8366,47 +8714,59 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>club13</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cleveland</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>RTX 6 ZipCore</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>80.7</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>80.7</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="n">
-        <v>81.09999999999999</v>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
         <v>90.8</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>72.9575</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>82.7062</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
         <v>6</v>
       </c>
     </row>
@@ -8504,7 +8864,1417 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B144"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>CAREER STATS (Arccos aggregate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>STROKES GAINED (vs scratch)</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SG total</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-23.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SG driving</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SG approach</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-14.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SG short</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-6.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SG putting</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>KEY RATES</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>fairway_pct</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>64.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>gir_pct</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>scramble_chip_save_pct</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>chip_down_pct</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chip_error_rate</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sand_save_pct</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>three_putt_pct</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>one_putt_pct</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>putts_per_round</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>CAREER BY CATEGORY (raw)</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>-- drive --</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>drive.noOfFairWaysHit</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>drive.noOfFairWaysRight</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>drive.noOfFairWaysLeft</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>drive.noOfFairwayAttempts</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>drive.noOfPlusOnePenalties</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>drive.noOfRecoveryShotsHit</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>drive.noOfPlusTwoPenalties</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>drive.noOfTimesRecoveryRequired</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>drive.totalDistance</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>3035.27</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>drive.maxDistance</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>247.29</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>drive.noOfDriveShotsNotIgnored</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>drive.noOfDriveShots</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>drive.deltaDistance</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>28.86</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>drive.noOfGreensHitInRegulation</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>drive.noOfShort</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>drive.noOfRecoveryShots</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>drive.noOfRecoveryShotsNotIgnored</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>drive.totalDistanceRecoveryShots</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>64.45999999999999</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>drive.maxDistanceRecoveryShots</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>35.59</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>drive.deltaDistanceRecoveryShots</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>drive.driveHcp</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>-7.49</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>drive.expectedDistance</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>drive.expectedDistanceRangeLow</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>drive.expectedDistanceRangeHigh</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>-- approach --</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>approach.noOfPlusOnePenalties</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>approach.noOfShotsInSand</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>approach.noOfPlusTwoPenalties</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>approach.noOfGreensHitInRegulation</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>approach.noOfGreens</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>approach.noOfHoles</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>approach.noOfGreensHit</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>approach.noOfRight</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>approach.noOfLong</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>approach.noOfLeft</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>approach.noOfShort</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>approach.noOfApproachShots</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>approach.noOfStrokesToGetDown</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>approach.totalDistanceToPin</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>816.3099999999999</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>approach.totalDistanceToPinOnGreensHit</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>115.97</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>approach.totalDistanceToPinOnGreensHitInRegulation</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>73.01000000000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>approach.noOfLayUpShots</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>approach.approachHcp</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>-- chip --</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>chip.noOfPlusOnePenalties</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>chip.noOfErrors</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>chip.noOfPlusTwoPenalties</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>chip.noOfZeroPutts</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>chip.noOfOnePutts</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>chip.noOfTwoPutts</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>chip.noOfThreePlusPutts</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>chip.noOfChipDownChances</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>chip.noOfChipDownSuccesses</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>chip.noOfChipSaveChances</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>chip.noOfChipSaveSuccesses</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>chip.noOfChipShots</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>chip.noOfStrokesToGetDown</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>chip.totalDistanceToPin</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>101.19</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>chip.totalDistanceToPinOnChipDownChances</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>79.17</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>chip.totalDistanceToPinOnChipSaveChances</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>65.29000000000001</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>chip.totalDistanceToPinOnChipDownSuccess</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>chip.totalDistanceToPinOnChipSaveSuccesses</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>chip.totalDistanceToPinOnGreensHitInRegulation</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>chip.noOfGreensHitInRegulation</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>chip.noOfRight</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>chip.noOfLong</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>chip.noOfLeft</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>chip.noOfShort</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>chip.chipHcp</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>-- sand --</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>sand.noOfPlusOnePenalties</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>sand.noOfErrors</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>sand.noOfPlusTwoPenalties</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>sand.noOfZeroPutts</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>sand.noOfOnePutts</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>sand.noOfTwoPutts</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>sand.noOfThreePlusPutts</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>sand.noOfSandDownChances</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>sand.noOfSandDownSuccesses</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>sand.noOfSandSaveChances</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>sand.noOfSandSaveSuccesses</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>sand.noOfSandShots</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>sand.noOfStrokesToGetDown</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>sand.totalDistanceToPin</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>sand.totalDistanceToPinOnSandSaveChances</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>sand.totalDistanceToPinOnSandDownChances</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>sand.totalDistanceToPinOnSandDownSuccesses</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>sand.totalDistanceToPinOnSandSaveSuccesses</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>sand.totalDistanceToPinOnGreensHitInRegulation</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>sand.noOfGreensHitInRegulation</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>sand.noOfRight</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>sand.noOfLong</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>sand.noOfLeft</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>sand.noOfShort</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>sand.sandHcp</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>-4.95</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>-- putt --</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>putt.zeroPutts</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>putt.onePutts</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>putt.twoPutts</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>putt.threePlusPutts</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>putt.totalPutts</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>putt.noOfHoles</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>putt.noOfPuttsAfterGir</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>putt.noOfGirsHit</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>putt.noOfPlusOnePenalites</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>putt.noOfPlusTwoPenalites</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>putt.strokesGained</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>putt.puttHcp</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>-10.29</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>-- overall --</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>overall.noOfEagles</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>overall.noOfBirdies</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>overall.noOfPars</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>overall.noOfBogeys</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>overall.noOfDoubleBogeys</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>overall.noOfParThree</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>overall.parThreeTotalStrokes</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>overall.noOfParFour</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>overall.parFourTotalStrokes</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>overall.noOfParFive</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>overall.parFiveTotalStrokes</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>overall.noOfHoles</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>overall.userHcp</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>-20.41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -8512,7 +10282,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ARCCOS STROKES-GAINED BASELINE</t>
         </is>
@@ -8587,303 +10357,415 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SG total (approx vs scratch)</t>
+          <t>SG total — Arccos (vs scratch)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-22.76</v>
+        <v>-23.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SG off-tee (approx)</t>
+          <t>SG off-tee — Arccos</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.71</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SG approach (approx)</t>
+          <t>SG approach — Arccos</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-14.24</v>
+        <v>-14.6</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>SG short game (approx) — PRIORITY</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-4</v>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SG short game — Arccos — PRIORITY</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>-6.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SG putting (approx)</t>
+          <t>SG putting — Arccos</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-3.82</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GIR %</t>
+          <t>SG total — Broadie reconstruction (cross-check)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27.8</v>
+        <v>-22.76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>GIR %</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Fairway %</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
         <v>64.3</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Scrambling % (derived) — PRIORITY</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Approach proximity (yd) — PRIORITY</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Proximity, last shot to pin (yd) — PRIORITY</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
         <v>12</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Putts / round</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1-putts / round</t>
+          <t>Putts / round</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3-putts / round</t>
+          <t>1-putts / round</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Putts per GIR</t>
+          <t>3-putts / round</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Avg drive (yd)</t>
+          <t>Putts per GIR</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>237.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Longest drive (yd)</t>
+          <t>Avg drive (yd)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>269.9</v>
+        <v>237.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Longest drive (yd)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>269.9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Penalties / round</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>chipHcp (Arccos metric) — PRIORITY</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B26" s="4" t="n">
         <v>-30</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>sandHcp (Arccos metric) — PRIORITY</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B27" s="4" t="n">
         <v>-4.95</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>PROVENANCE &amp; GLOSSARY</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Source: UNOFFICIAL reverse-engineered Arccos API (api.arccosgolf.com), pulled by</t>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>CAREER AGGREGATE (Arccos)</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>pull_arccos.py (custom stdlib client). Not affiliated with Arccos Golf LLC.</t>
-        </is>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Chip/short-game save % — PRIORITY</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Date pulled: 2026-06-06 23:18 UTC  |  Rounds: 1  Shots: 95</t>
-        </is>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Chip 'get it close' % — PRIORITY</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>11.1</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Chip error rate % — PRIORITY</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>18.2</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>REAL (native API): score, putts, GIR, fairway flags, penalties, clubs/terrain</t>
-        </is>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Sand save % — PRIORITY</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>distances + dispersion + GIR%, Arccos category handicaps (drive/approach/chip/</t>
-        </is>
+          <t>GIR % (career)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>27.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sand/putt Hcp — proprietary NEGATIVE scale, NOT USGA; clamped at -30).</t>
-        </is>
+          <t>Fairway % (career)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>64.3</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3-putt % (career)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>16.7</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DERIVED (computed here, labeled _approx / _calibrated / _inferred):</t>
-        </is>
+          <t>1-putt % (career)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>5.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>- par_calibrated: GPS hole length -&gt; par class, nudged so holes sum to course par.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>- Strokes Gained (sg_*_approx): RECONSTRUCTED from shot start/end GPS distance-to-</t>
-        </is>
+          <t>Putts / round (career)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  pin vs a published baseline (Broadie, 'Assessing Golfer Performance on the PGA TOUR' Table 9 (2003-2010 ShotLink) + PGA Tour SG-Putting 2010 baseline; same as 'Every Shot Counts'.). The official /v2/sga endpoint is</t>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>PROVENANCE &amp; GLOSSARY</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  permission-gated (401) for dashboard tokens, so SG is rebuilt, NOT from Arccos.</t>
+          <t>Source: UNOFFICIAL reverse-engineered Arccos API (api.arccosgolf.com), pulled by</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Lie per shot is approximate (only tee/green are reliable) — treat SG as indicative.</t>
+          <t>pull_arccos.py (custom stdlib client). Not affiliated with Arccos Golf LLC.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>- scramble_pct: missed GIR + holed out &lt;= par_calibrated. Native isUpDown flags were</t>
+          <t>Date pulled: 2026-06-06 23:33 UTC  |  Rounds: 1  Shots: 95</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  unpopulated at pull time (kept verbatim as *_native).</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>- approach_proximity_yd: end distance-to-pin of the last non-putt shot.</t>
+          <t>REAL (native API): score, putts, GIR, fairway flags, penalties, clubs/terrain</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
+        <is>
+          <t>distances + dispersion + GIR%, Arccos category handicaps (drive/approach/chip/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>sand/putt Hcp — proprietary NEGATIVE scale, NOT USGA; clamped at -30).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DERIVED (computed here, labeled _approx / _calibrated / _inferred):</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>- par_calibrated: GPS hole length -&gt; par class, nudged so holes sum to course par.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>- Strokes Gained (sg_*_approx): RECONSTRUCTED from shot start/end GPS distance-to-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  pin vs a published baseline (Broadie, 'Assessing Golfer Performance on the PGA TOUR' Table 9 (2003-2010 ShotLink) + PGA Tour SG-Putting 2010 baseline; same as 'Every Shot Counts'.). The official /v2/sga endpoint is</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  permission-gated (401) for dashboard tokens, so SG is rebuilt, NOT from Arccos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Lie per shot is approximate (only tee/green are reliable) — treat SG as indicative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>- scramble_pct: missed GIR + holed out &lt;= par_calibrated. Native isUpDown flags were</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  unpopulated at pull time (kept verbatim as *_native).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>- approach_proximity_yd: end distance-to-pin of the last non-putt shot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>GPS coordinates, names, email, DOB are EXCLUDED from all outputs.</t>
         </is>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-06-06 23:33 UTC</t>
+          <t>2026-06-06 23:53 UTC</t>
         </is>
       </c>
     </row>
@@ -10670,7 +10670,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-06 23:33 UTC  |  Rounds: 1  Shots: 95</t>
+          <t>Date pulled: 2026-06-06 23:53 UTC  |  Rounds: 1  Shots: 95</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU2"/>
+  <dimension ref="A1:AT2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,6 @@
     <col width="10" customWidth="1" min="44" max="44"/>
     <col width="10" customWidth="1" min="45" max="45"/>
     <col width="10" customWidth="1" min="46" max="46"/>
-    <col width="11" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -728,11 +727,6 @@
           <t>putt_hcp</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>pulled_at</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -880,11 +874,6 @@
       </c>
       <c r="AT2" t="n">
         <v>-10.2852</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2026-06-06 23:53 UTC</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -10670,7 +10659,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-06 23:53 UTC  |  Rounds: 1  Shots: 95</t>
+          <t>Date pulled: 2026-06-06 23:55 UTC  |  Rounds: 1  Shots: 95</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -857,24 +857,12 @@
       <c r="AN2" t="n">
         <v>-3.82</v>
       </c>
-      <c r="AO2" t="n">
-        <v>-20.4148</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-7.49223</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-30</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-30</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-4.95085</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-10.2852</v>
-      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8178,16 +8166,8 @@
           <t>Driver</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Cobra</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>DS-ADAPT LS</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>262.8</v>
       </c>
@@ -8228,16 +8208,8 @@
           <t>Wood</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Cobra</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>DS-ADAPT</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>203.7</v>
       </c>
@@ -8260,24 +8232,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5 Wood</t>
+          <t>club3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wood</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Cobra</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>DS-ADAPT</t>
-        </is>
-      </c>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>184</v>
       </c>
@@ -8306,16 +8270,8 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Cobra</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>DS-ADAPT</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>172.9</v>
       </c>
@@ -8344,16 +8300,8 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Srixon</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ZX7 Mk II</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>155.8</v>
       </c>
@@ -8400,16 +8348,8 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Srixon</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ZX7 Mk II</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
         <v>143.7</v>
       </c>
@@ -8440,16 +8380,8 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Srixon</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ZX7 Mk II</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
         <v>133.6</v>
       </c>
@@ -8482,16 +8414,8 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Srixon</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ZX7 Mk II</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>126.2</v>
       </c>
@@ -8536,16 +8460,8 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Srixon</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ZX7 Mk II</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
         <v>122</v>
       </c>
@@ -8578,16 +8494,8 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Srixon</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ZX7 Mk II</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>108.1</v>
       </c>
@@ -8628,16 +8536,8 @@
           <t>Wedge</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>RTX 6 ZipCore</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
         <v>100.3</v>
       </c>
@@ -8682,16 +8582,8 @@
           <t>Wedge</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>RTX 6 ZipCore</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
         <v>86.8</v>
       </c>
@@ -8720,16 +8612,8 @@
           <t>Wedge</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>RTX 6 ZipCore</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
         <v>80.7</v>
       </c>
@@ -8770,7 +8654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8819,29 +8703,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>27924130</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-20.4148</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-7.49223</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-30</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-4.95085</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-10.2852</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8853,7 +8714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B144"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -8884,9 +8745,6 @@
           <t>SG total</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>-23.7</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8894,9 +8752,6 @@
           <t>SG driving</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>-1.2</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8904,9 +8759,6 @@
           <t>SG approach</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>-14.6</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8914,9 +8766,6 @@
           <t>SG short</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>-6.1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8924,9 +8773,6 @@
           <t>SG putting</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>-1.8</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -8945,9 +8791,6 @@
           <t>fairway_pct</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>64.3</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8955,9 +8798,6 @@
           <t>gir_pct</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>27.8</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8965,9 +8805,6 @@
           <t>scramble_chip_save_pct</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8975,9 +8812,6 @@
           <t>chip_down_pct</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>11.1</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8985,9 +8819,6 @@
           <t>chip_error_rate</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>18.2</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8995,9 +8826,6 @@
           <t>sand_save_pct</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9005,9 +8833,6 @@
           <t>three_putt_pct</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>16.7</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9015,9 +8840,6 @@
           <t>one_putt_pct</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>5.6</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9025,9 +8847,6 @@
           <t>putts_per_round</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>38</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -9050,1206 +8869,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>drive.noOfFairWaysHit</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>9</v>
+          <t>-- approach --</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>drive.noOfFairWaysRight</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
+          <t>-- chip --</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>drive.noOfFairWaysLeft</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>5</v>
+          <t>-- sand --</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>drive.noOfFairwayAttempts</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>14</v>
+          <t>-- putt --</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>drive.noOfPlusOnePenalties</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>drive.noOfRecoveryShotsHit</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>drive.noOfPlusTwoPenalties</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>drive.noOfTimesRecoveryRequired</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>drive.totalDistance</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>3035.27</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>drive.maxDistance</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>247.29</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>drive.noOfDriveShotsNotIgnored</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>drive.noOfDriveShots</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>drive.deltaDistance</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>28.86</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>drive.noOfGreensHitInRegulation</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>drive.noOfShort</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>drive.noOfRecoveryShots</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>drive.noOfRecoveryShotsNotIgnored</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>drive.totalDistanceRecoveryShots</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>64.45999999999999</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>drive.maxDistanceRecoveryShots</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>35.59</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>drive.deltaDistanceRecoveryShots</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>3.36</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>drive.driveHcp</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>-7.49</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>drive.expectedDistance</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>drive.expectedDistanceRangeLow</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>drive.expectedDistanceRangeHigh</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>-- approach --</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>approach.noOfPlusOnePenalties</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>approach.noOfShotsInSand</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>approach.noOfPlusTwoPenalties</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>approach.noOfGreensHitInRegulation</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>approach.noOfGreens</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>approach.noOfHoles</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>approach.noOfGreensHit</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>approach.noOfRight</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>approach.noOfLong</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>approach.noOfLeft</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>approach.noOfShort</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>approach.noOfApproachShots</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>approach.noOfStrokesToGetDown</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>approach.totalDistanceToPin</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>816.3099999999999</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>approach.totalDistanceToPinOnGreensHit</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>115.97</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>approach.totalDistanceToPinOnGreensHitInRegulation</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>73.01000000000001</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>approach.noOfLayUpShots</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>approach.approachHcp</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>-- chip --</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>chip.noOfPlusOnePenalties</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>chip.noOfErrors</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>chip.noOfPlusTwoPenalties</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>chip.noOfZeroPutts</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>chip.noOfOnePutts</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>chip.noOfTwoPutts</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>chip.noOfThreePlusPutts</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>chip.noOfChipDownChances</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>chip.noOfChipDownSuccesses</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>chip.noOfChipSaveChances</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>chip.noOfChipSaveSuccesses</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>chip.noOfChipShots</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>chip.noOfStrokesToGetDown</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>chip.totalDistanceToPin</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>101.19</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>chip.totalDistanceToPinOnChipDownChances</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>79.17</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>chip.totalDistanceToPinOnChipSaveChances</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>65.29000000000001</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>chip.totalDistanceToPinOnChipDownSuccess</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>chip.totalDistanceToPinOnChipSaveSuccesses</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>chip.totalDistanceToPinOnGreensHitInRegulation</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>chip.noOfGreensHitInRegulation</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>chip.noOfRight</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>chip.noOfLong</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>chip.noOfLeft</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>chip.noOfShort</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>chip.chipHcp</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>-- sand --</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>sand.noOfPlusOnePenalties</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>sand.noOfErrors</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>sand.noOfPlusTwoPenalties</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>sand.noOfZeroPutts</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>sand.noOfOnePutts</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>sand.noOfTwoPutts</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>sand.noOfThreePlusPutts</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>sand.noOfSandDownChances</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>sand.noOfSandDownSuccesses</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>sand.noOfSandSaveChances</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>sand.noOfSandSaveSuccesses</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>sand.noOfSandShots</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>sand.noOfStrokesToGetDown</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>sand.totalDistanceToPin</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>16.61</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>sand.totalDistanceToPinOnSandSaveChances</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>16.61</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>sand.totalDistanceToPinOnSandDownChances</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>16.61</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>sand.totalDistanceToPinOnSandDownSuccesses</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>sand.totalDistanceToPinOnSandSaveSuccesses</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>sand.totalDistanceToPinOnGreensHitInRegulation</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>sand.noOfGreensHitInRegulation</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>sand.noOfRight</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>sand.noOfLong</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>sand.noOfLeft</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>sand.noOfShort</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>sand.sandHcp</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>-4.95</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>-- putt --</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>putt.zeroPutts</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>putt.onePutts</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>putt.twoPutts</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>putt.threePlusPutts</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>putt.totalPutts</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>putt.noOfHoles</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>putt.noOfPuttsAfterGir</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>putt.noOfGirsHit</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>putt.noOfPlusOnePenalites</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>putt.noOfPlusTwoPenalites</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>putt.strokesGained</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>putt.puttHcp</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>-10.29</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
           <t>-- overall --</t>
         </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>overall.noOfEagles</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>overall.noOfBirdies</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>overall.noOfPars</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>overall.noOfBogeys</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>overall.noOfDoubleBogeys</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>overall.noOfParThree</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>overall.parThreeTotalStrokes</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>overall.noOfParFour</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>overall.parFourTotalStrokes</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>overall.noOfParFive</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>overall.parFiveTotalStrokes</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>overall.noOfHoles</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>overall.userHcp</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>-20.41</v>
       </c>
     </row>
   </sheetData>
@@ -10519,8 +9168,10 @@
           <t>chipHcp (Arccos metric) — PRIORITY</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n">
-        <v>-30</v>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -10529,8 +9180,10 @@
           <t>sandHcp (Arccos metric) — PRIORITY</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n">
-        <v>-4.95</v>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -10551,8 +9204,10 @@
           <t>Chip/short-game save % — PRIORITY</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n">
-        <v>0</v>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -10561,8 +9216,10 @@
           <t>Chip 'get it close' % — PRIORITY</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n">
-        <v>11.1</v>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -10571,8 +9228,10 @@
           <t>Chip error rate % — PRIORITY</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n">
-        <v>18.2</v>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -10581,8 +9240,10 @@
           <t>Sand save % — PRIORITY</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n">
-        <v>0</v>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -10591,8 +9252,10 @@
           <t>GIR % (career)</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>27.8</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -10601,8 +9264,10 @@
           <t>Fairway % (career)</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>64.3</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -10611,8 +9276,10 @@
           <t>3-putt % (career)</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>16.7</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -10621,8 +9288,10 @@
           <t>1-putt % (career)</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>5.6</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -10631,8 +9300,10 @@
           <t>Putts / round (career)</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>38</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -10659,7 +9330,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-06 23:55 UTC  |  Rounds: 1  Shots: 95</t>
+          <t>Date pulled: 2026-06-07 12:00 UTC  |  Rounds: 1  Shots: 95</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -857,12 +857,24 @@
       <c r="AN2" t="n">
         <v>-3.82</v>
       </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>-20.4148</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-7.49223</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-4.95085</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-10.2852</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8166,8 +8178,16 @@
           <t>Driver</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Cobra</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DS-ADAPT LS</t>
+        </is>
+      </c>
       <c r="E2" t="n">
         <v>262.8</v>
       </c>
@@ -8208,8 +8228,16 @@
           <t>Wood</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cobra</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DS-ADAPT</t>
+        </is>
+      </c>
       <c r="E3" t="n">
         <v>203.7</v>
       </c>
@@ -8232,16 +8260,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>club3</t>
+          <t>5 Wood</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cobra</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DS-ADAPT</t>
+        </is>
+      </c>
       <c r="E4" t="n">
         <v>184</v>
       </c>
@@ -8270,8 +8306,16 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cobra</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DS-ADAPT</t>
+        </is>
+      </c>
       <c r="E5" t="n">
         <v>172.9</v>
       </c>
@@ -8300,8 +8344,16 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Srixon</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ZX7 Mk II</t>
+        </is>
+      </c>
       <c r="E6" t="n">
         <v>155.8</v>
       </c>
@@ -8348,8 +8400,16 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Srixon</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ZX7 Mk II</t>
+        </is>
+      </c>
       <c r="E7" t="n">
         <v>143.7</v>
       </c>
@@ -8380,8 +8440,16 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Srixon</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ZX7 Mk II</t>
+        </is>
+      </c>
       <c r="E8" t="n">
         <v>133.6</v>
       </c>
@@ -8414,8 +8482,16 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Srixon</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ZX7 Mk II</t>
+        </is>
+      </c>
       <c r="E9" t="n">
         <v>126.2</v>
       </c>
@@ -8460,8 +8536,16 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Srixon</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ZX7 Mk II</t>
+        </is>
+      </c>
       <c r="E10" t="n">
         <v>122</v>
       </c>
@@ -8494,8 +8578,16 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Srixon</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ZX7 Mk II</t>
+        </is>
+      </c>
       <c r="E11" t="n">
         <v>108.1</v>
       </c>
@@ -8536,8 +8628,16 @@
           <t>Wedge</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cleveland</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RTX 6 ZipCore</t>
+        </is>
+      </c>
       <c r="E12" t="n">
         <v>100.3</v>
       </c>
@@ -8582,8 +8682,16 @@
           <t>Wedge</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Cleveland</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>RTX 6 ZipCore</t>
+        </is>
+      </c>
       <c r="E13" t="n">
         <v>86.8</v>
       </c>
@@ -8612,8 +8720,16 @@
           <t>Wedge</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cleveland</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>RTX 6 ZipCore</t>
+        </is>
+      </c>
       <c r="E14" t="n">
         <v>80.7</v>
       </c>
@@ -8654,7 +8770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8703,6 +8819,29 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>27924130</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-20.4148</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-7.49223</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-4.95085</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-10.2852</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8714,7 +8853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -8745,6 +8884,9 @@
           <t>SG total</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>-23.7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8752,6 +8894,9 @@
           <t>SG driving</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>-1.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8759,6 +8904,9 @@
           <t>SG approach</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>-14.6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8766,6 +8914,9 @@
           <t>SG short</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>-6.1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8773,6 +8924,9 @@
           <t>SG putting</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>-1.8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -8791,6 +8945,9 @@
           <t>fairway_pct</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>64.3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8798,6 +8955,9 @@
           <t>gir_pct</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>27.8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8805,6 +8965,9 @@
           <t>scramble_chip_save_pct</t>
         </is>
       </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8812,6 +8975,9 @@
           <t>chip_down_pct</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>11.1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8819,6 +8985,9 @@
           <t>chip_error_rate</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>18.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8826,6 +8995,9 @@
           <t>sand_save_pct</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8833,6 +9005,9 @@
           <t>three_putt_pct</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>16.7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8840,6 +9015,9 @@
           <t>one_putt_pct</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8847,6 +9025,9 @@
           <t>putts_per_round</t>
         </is>
       </c>
+      <c r="B19" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -8869,36 +9050,1206 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>-- approach --</t>
-        </is>
+          <t>drive.noOfFairWaysHit</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>-- chip --</t>
-        </is>
+          <t>drive.noOfFairWaysRight</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>-- sand --</t>
-        </is>
+          <t>drive.noOfFairWaysLeft</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>-- putt --</t>
-        </is>
+          <t>drive.noOfFairwayAttempts</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>drive.noOfPlusOnePenalties</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>drive.noOfRecoveryShotsHit</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>drive.noOfPlusTwoPenalties</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>drive.noOfTimesRecoveryRequired</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>drive.totalDistance</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>3035.27</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>drive.maxDistance</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>247.29</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>drive.noOfDriveShotsNotIgnored</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>drive.noOfDriveShots</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>drive.deltaDistance</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>28.86</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>drive.noOfGreensHitInRegulation</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>drive.noOfShort</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>drive.noOfRecoveryShots</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>drive.noOfRecoveryShotsNotIgnored</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>drive.totalDistanceRecoveryShots</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>64.45999999999999</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>drive.maxDistanceRecoveryShots</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>35.59</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>drive.deltaDistanceRecoveryShots</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>drive.driveHcp</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>-7.49</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>drive.expectedDistance</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>drive.expectedDistanceRangeLow</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>drive.expectedDistanceRangeHigh</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>-- approach --</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>approach.noOfPlusOnePenalties</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>approach.noOfShotsInSand</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>approach.noOfPlusTwoPenalties</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>approach.noOfGreensHitInRegulation</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>approach.noOfGreens</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>approach.noOfHoles</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>approach.noOfGreensHit</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>approach.noOfRight</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>approach.noOfLong</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>approach.noOfLeft</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>approach.noOfShort</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>approach.noOfApproachShots</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>approach.noOfStrokesToGetDown</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>approach.totalDistanceToPin</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>816.3099999999999</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>approach.totalDistanceToPinOnGreensHit</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>115.97</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>approach.totalDistanceToPinOnGreensHitInRegulation</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>73.01000000000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>approach.noOfLayUpShots</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>approach.approachHcp</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>-- chip --</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>chip.noOfPlusOnePenalties</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>chip.noOfErrors</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>chip.noOfPlusTwoPenalties</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>chip.noOfZeroPutts</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>chip.noOfOnePutts</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>chip.noOfTwoPutts</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>chip.noOfThreePlusPutts</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>chip.noOfChipDownChances</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>chip.noOfChipDownSuccesses</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>chip.noOfChipSaveChances</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>chip.noOfChipSaveSuccesses</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>chip.noOfChipShots</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>chip.noOfStrokesToGetDown</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>chip.totalDistanceToPin</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>101.19</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>chip.totalDistanceToPinOnChipDownChances</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>79.17</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>chip.totalDistanceToPinOnChipSaveChances</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>65.29000000000001</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>chip.totalDistanceToPinOnChipDownSuccess</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>chip.totalDistanceToPinOnChipSaveSuccesses</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>chip.totalDistanceToPinOnGreensHitInRegulation</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>chip.noOfGreensHitInRegulation</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>chip.noOfRight</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>chip.noOfLong</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>chip.noOfLeft</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>chip.noOfShort</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>chip.chipHcp</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>-- sand --</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>sand.noOfPlusOnePenalties</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>sand.noOfErrors</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>sand.noOfPlusTwoPenalties</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>sand.noOfZeroPutts</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>sand.noOfOnePutts</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>sand.noOfTwoPutts</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>sand.noOfThreePlusPutts</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>sand.noOfSandDownChances</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>sand.noOfSandDownSuccesses</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>sand.noOfSandSaveChances</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>sand.noOfSandSaveSuccesses</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>sand.noOfSandShots</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>sand.noOfStrokesToGetDown</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>sand.totalDistanceToPin</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>sand.totalDistanceToPinOnSandSaveChances</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>sand.totalDistanceToPinOnSandDownChances</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>sand.totalDistanceToPinOnSandDownSuccesses</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>sand.totalDistanceToPinOnSandSaveSuccesses</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>sand.totalDistanceToPinOnGreensHitInRegulation</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>sand.noOfGreensHitInRegulation</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>sand.noOfRight</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>sand.noOfLong</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>sand.noOfLeft</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>sand.noOfShort</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>sand.sandHcp</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>-4.95</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>-- putt --</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>putt.zeroPutts</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>putt.onePutts</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>putt.twoPutts</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>putt.threePlusPutts</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>putt.totalPutts</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>putt.noOfHoles</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>putt.noOfPuttsAfterGir</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>putt.noOfGirsHit</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>putt.noOfPlusOnePenalites</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>putt.noOfPlusTwoPenalites</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>putt.strokesGained</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>putt.puttHcp</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>-10.29</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
           <t>-- overall --</t>
         </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>overall.noOfEagles</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>overall.noOfBirdies</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>overall.noOfPars</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>overall.noOfBogeys</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>overall.noOfDoubleBogeys</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>overall.noOfParThree</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>overall.parThreeTotalStrokes</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>overall.noOfParFour</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>overall.parFourTotalStrokes</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>overall.noOfParFive</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>overall.parFiveTotalStrokes</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>overall.noOfHoles</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>overall.userHcp</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>-20.41</v>
       </c>
     </row>
   </sheetData>
@@ -9168,10 +10519,8 @@
           <t>chipHcp (Arccos metric) — PRIORITY</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="B26" s="4" t="n">
+        <v>-30</v>
       </c>
     </row>
     <row r="27">
@@ -9180,10 +10529,8 @@
           <t>sandHcp (Arccos metric) — PRIORITY</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="B27" s="4" t="n">
+        <v>-4.95</v>
       </c>
     </row>
     <row r="29">
@@ -9204,10 +10551,8 @@
           <t>Chip/short-game save % — PRIORITY</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="B30" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -9216,10 +10561,8 @@
           <t>Chip 'get it close' % — PRIORITY</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="B31" s="4" t="n">
+        <v>11.1</v>
       </c>
     </row>
     <row r="32">
@@ -9228,10 +10571,8 @@
           <t>Chip error rate % — PRIORITY</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="B32" s="4" t="n">
+        <v>18.2</v>
       </c>
     </row>
     <row r="33">
@@ -9240,10 +10581,8 @@
           <t>Sand save % — PRIORITY</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="B33" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -9252,10 +10591,8 @@
           <t>GIR % (career)</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="B34" t="n">
+        <v>27.8</v>
       </c>
     </row>
     <row r="35">
@@ -9264,10 +10601,8 @@
           <t>Fairway % (career)</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="B35" t="n">
+        <v>64.3</v>
       </c>
     </row>
     <row r="36">
@@ -9276,10 +10611,8 @@
           <t>3-putt % (career)</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="B36" t="n">
+        <v>16.7</v>
       </c>
     </row>
     <row r="37">
@@ -9288,10 +10621,8 @@
           <t>1-putt % (career)</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="B37" t="n">
+        <v>5.6</v>
       </c>
     </row>
     <row r="38">
@@ -9300,10 +10631,8 @@
           <t>Putts / round (career)</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="B38" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="40">
@@ -9330,7 +10659,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-07 12:00 UTC  |  Rounds: 1  Shots: 95</t>
+          <t>Date pulled: 2026-06-07 16:46 UTC  |  Rounds: 1  Shots: 95</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -10659,7 +10659,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-07 16:46 UTC  |  Rounds: 1  Shots: 95</t>
+          <t>Date pulled: 2026-06-07 19:06 UTC  |  Rounds: 1  Shots: 95</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -887,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y19"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -912,9 +912,11 @@
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="23" customWidth="1" min="22" max="22"/>
-    <col width="17" customWidth="1" min="23" max="23"/>
-    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="17" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="17" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1030,15 +1032,25 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>pin_lat</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>pin_lng</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>scramble_chance</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>scramble_save</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>sg_hole_broadie</t>
         </is>
@@ -1118,12 +1130,18 @@
         <v>1.7</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>30.05543020345</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-95.511907947607</v>
       </c>
       <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
         <v>-1.448</v>
       </c>
     </row>
@@ -1199,12 +1217,18 @@
         <v>30.9</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>30.055686018177</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-95.51431251885499</v>
       </c>
       <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
         <v>-1.026</v>
       </c>
     </row>
@@ -1282,12 +1306,18 @@
         <v>4.1</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>30.054324853879</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-95.516679530392</v>
       </c>
       <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
         <v>-1.048</v>
       </c>
     </row>
@@ -1365,12 +1395,18 @@
         <v>24.9</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>30.059025352351</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-95.51503606089101</v>
       </c>
       <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
         <v>-0.322</v>
       </c>
     </row>
@@ -1448,12 +1484,18 @@
         <v>3.7</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>30.061721317373</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-95.51829300953101</v>
       </c>
       <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
         <v>-1.466</v>
       </c>
     </row>
@@ -1529,12 +1571,18 @@
         <v>13.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>30.059522686463</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-95.518652466506</v>
       </c>
       <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
         <v>-3.238</v>
       </c>
     </row>
@@ -1612,12 +1660,18 @@
         <v>8.800000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>30.0628754642</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-95.520645989927</v>
       </c>
       <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
         <v>-1.166</v>
       </c>
     </row>
@@ -1695,12 +1749,18 @@
         <v>14.9</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>30.064422996858</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-95.516318717817</v>
       </c>
       <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
         <v>-0.051</v>
       </c>
     </row>
@@ -1778,12 +1838,18 @@
         <v>5.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>30.061262285103</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-95.513687119046</v>
       </c>
       <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
         <v>-1.528</v>
       </c>
     </row>
@@ -1861,12 +1927,18 @@
         <v>23.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>30.057737365499</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-95.508897378239</v>
       </c>
       <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
         <v>-0.637</v>
       </c>
     </row>
@@ -1942,12 +2014,18 @@
         <v>4.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>30.05908509001</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-95.50688999502</v>
       </c>
       <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
         <v>-0.8090000000000001</v>
       </c>
     </row>
@@ -2025,12 +2103,18 @@
         <v>10.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>30.061896957281</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-95.50343808710301</v>
       </c>
       <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
         <v>-2.173</v>
       </c>
     </row>
@@ -2108,12 +2192,18 @@
         <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>30.061200620534</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-95.509263950274</v>
       </c>
       <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
         <v>-1.856</v>
       </c>
     </row>
@@ -2191,12 +2281,18 @@
         <v>20</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>30.065480564849</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-95.506726864749</v>
       </c>
       <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
         <v>-2.877</v>
       </c>
     </row>
@@ -2274,12 +2370,18 @@
         <v>12.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>30.063745308749</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-95.50954872469499</v>
       </c>
       <c r="Y16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
         <v>-0.6879999999999999</v>
       </c>
     </row>
@@ -2355,12 +2457,18 @@
         <v>17.9</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>30.066588271455</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-95.510353330615</v>
       </c>
       <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
         <v>-0.833</v>
       </c>
     </row>
@@ -2438,12 +2546,18 @@
         <v>4.3</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>30.064151585215</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-95.51128599349499</v>
       </c>
       <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
         <v>-1.631</v>
       </c>
     </row>
@@ -2521,12 +2635,18 @@
         <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>30.060546277607</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-95.51178746450201</v>
       </c>
       <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
         <v>0.033</v>
       </c>
     </row>
@@ -2541,7 +2661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O96"/>
+  <dimension ref="A1:S96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2553,12 +2673,16 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2609,30 +2733,50 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>start_lat</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>start_lng</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>end_lat</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>end_lng</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>lie_approx</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>is_tee</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>is_putt</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>penalties</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>category_approx</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>sg_shot_approx</t>
         </is>
@@ -2672,26 +2816,38 @@
       <c r="I2" t="n">
         <v>167.8</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="n">
+        <v>30.0578524</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-95.5136816</v>
+      </c>
+      <c r="L2" t="n">
+        <v>30.0567153</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-95.5124879</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="S2" t="n">
         <v>-0.133</v>
       </c>
     </row>
@@ -2729,26 +2885,38 @@
       <c r="I3" t="n">
         <v>136.3</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="n">
+        <v>30.0567153</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-95.5124879</v>
+      </c>
+      <c r="L3" t="n">
+        <v>30.056481922807</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-95.51235511929799</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="S3" t="n">
         <v>-0.638</v>
       </c>
     </row>
@@ -2786,26 +2954,38 @@
       <c r="I4" t="n">
         <v>24.2</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>30.056481922807</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-95.51235511929799</v>
+      </c>
+      <c r="L4" t="n">
+        <v>30.0554541</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-95.512136</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="S4" t="n">
         <v>-0.313</v>
       </c>
     </row>
@@ -2843,26 +3023,38 @@
       <c r="I5" t="n">
         <v>1.7</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>30.0554541</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-95.512136</v>
+      </c>
+      <c r="L5" t="n">
+        <v>30.0554316</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-95.5119237</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="S5" t="n">
         <v>0.37</v>
       </c>
     </row>
@@ -2900,26 +3092,38 @@
       <c r="I6" t="n">
         <v>0.7</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="n">
+        <v>30.0554316</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-95.5119237</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.055430762071</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-95.511914248564</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="S6" t="n">
         <v>-0.747</v>
       </c>
     </row>
@@ -2957,26 +3161,38 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>30.055430762071</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-95.511914248564</v>
+      </c>
+      <c r="L7" t="n">
+        <v>30.05543020345</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-95.511907947607</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="S7" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -3014,26 +3230,38 @@
       <c r="I8" t="n">
         <v>30.9</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>30.0547446</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-95.5141495</v>
+      </c>
+      <c r="L8" t="n">
+        <v>30.0554473</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-95.5142113</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="S8" t="n">
         <v>-0.405</v>
       </c>
     </row>
@@ -3071,26 +3299,38 @@
       <c r="I9" t="n">
         <v>2.3</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>30.0554473</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-95.5142113</v>
+      </c>
+      <c r="L9" t="n">
+        <v>30.055668004988</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-95.51430488106701</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="S9" t="n">
         <v>-0.055</v>
       </c>
     </row>
@@ -3128,26 +3368,38 @@
       <c r="I10" t="n">
         <v>0.7</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>30.055668004988</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-95.51430488106701</v>
+      </c>
+      <c r="L10" t="n">
+        <v>30.0556915</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-95.5143126</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="S10" t="n">
         <v>-0.579</v>
       </c>
     </row>
@@ -3185,26 +3437,38 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="n">
+        <v>30.0556915</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-95.5143126</v>
+      </c>
+      <c r="L11" t="n">
+        <v>30.055686018177</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-95.51431251885499</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="S11" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -3242,26 +3506,38 @@
       <c r="I12" t="n">
         <v>74.8</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="n">
+        <v>30.0563561</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-95.5148209</v>
+      </c>
+      <c r="L12" t="n">
+        <v>30.054549443084</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-95.51601782441099</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="O12" t="n">
+      <c r="S12" t="n">
         <v>0.036</v>
       </c>
     </row>
@@ -3299,26 +3575,38 @@
       <c r="I13" t="n">
         <v>27.6</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="n">
+        <v>30.054549443084</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-95.51601782441099</v>
+      </c>
+      <c r="L13" t="n">
+        <v>30.0543919</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-95.51692970000001</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="S13" t="n">
         <v>-0.757</v>
       </c>
     </row>
@@ -3356,26 +3644,38 @@
       <c r="I14" t="n">
         <v>4.1</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="n">
+        <v>30.0543919</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-95.51692970000001</v>
+      </c>
+      <c r="L14" t="n">
+        <v>30.0543469</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-95.5166495</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="O14" t="n">
+      <c r="S14" t="n">
         <v>-0.041</v>
       </c>
     </row>
@@ -3413,26 +3713,38 @@
       <c r="I15" t="n">
         <v>0.7</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="n">
+        <v>30.0543469</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-95.5166495</v>
+      </c>
+      <c r="L15" t="n">
+        <v>30.0543284</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-95.5166747</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O15" t="n">
+      <c r="S15" t="n">
         <v>-0.299</v>
       </c>
     </row>
@@ -3470,26 +3782,38 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="n">
+        <v>30.0543284</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-95.5166747</v>
+      </c>
+      <c r="L16" t="n">
+        <v>30.054324853879</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-95.516679530392</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O16" t="n">
+      <c r="S16" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -3527,26 +3851,38 @@
       <c r="I17" t="n">
         <v>263.5</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" t="n">
+        <v>30.0551638</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-95.51681910000001</v>
+      </c>
+      <c r="L17" t="n">
+        <v>30.056880575445</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-95.515391863883</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="O17" t="n">
+      <c r="S17" t="n">
         <v>-0.152</v>
       </c>
     </row>
@@ -3584,26 +3920,38 @@
       <c r="I18" t="n">
         <v>178.2</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" t="n">
+        <v>30.056880575445</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-95.515391863883</v>
+      </c>
+      <c r="L18" t="n">
+        <v>30.0575686</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-95.5152205</v>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O18" t="n">
+      <c r="S18" t="n">
         <v>-0.472</v>
       </c>
     </row>
@@ -3641,26 +3989,38 @@
       <c r="I19" t="n">
         <v>24.9</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="n">
+        <v>30.0575686</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-95.5152205</v>
+      </c>
+      <c r="L19" t="n">
+        <v>30.0588219</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-95.51501140000001</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O19" t="n">
+      <c r="S19" t="n">
         <v>-0.017</v>
       </c>
     </row>
@@ -3698,26 +4058,38 @@
       <c r="I20" t="n">
         <v>2</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" t="n">
+        <v>30.0588219</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-95.51501140000001</v>
+      </c>
+      <c r="L20" t="n">
+        <v>30.059008995299</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-95.515034078214</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O20" t="n">
+      <c r="S20" t="n">
         <v>-0.038</v>
       </c>
     </row>
@@ -3755,26 +4127,38 @@
       <c r="I21" t="n">
         <v>0</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" t="n">
+        <v>30.059008995299</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-95.515034078214</v>
+      </c>
+      <c r="L21" t="n">
+        <v>30.059025352351</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-95.51503606089101</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O21" t="n">
+      <c r="S21" t="n">
         <v>0.357</v>
       </c>
     </row>
@@ -3812,26 +4196,38 @@
       <c r="I22" t="n">
         <v>193.7</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" t="n">
+        <v>30.0603722</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-95.5153981</v>
+      </c>
+      <c r="L22" t="n">
+        <v>30.0608966</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-95.5167184</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="O22" t="n">
+      <c r="S22" t="n">
         <v>-0.277</v>
       </c>
     </row>
@@ -3869,26 +4265,38 @@
       <c r="I23" t="n">
         <v>154.8</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" t="n">
+        <v>30.0608966</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-95.5167184</v>
+      </c>
+      <c r="L23" t="n">
+        <v>30.061074185294</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-95.51702590588199</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O23" t="n">
+      <c r="S23" t="n">
         <v>-0.577</v>
       </c>
     </row>
@@ -3926,26 +4334,38 @@
       <c r="I24" t="n">
         <v>16.5</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" t="n">
+        <v>30.061074185294</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-95.51702590588199</v>
+      </c>
+      <c r="L24" t="n">
+        <v>30.0616279</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-95.5184067</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O24" t="n">
+      <c r="S24" t="n">
         <v>-0.114</v>
       </c>
     </row>
@@ -3983,26 +4403,38 @@
       <c r="I25" t="n">
         <v>3.7</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" t="n">
+        <v>30.0616279</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-95.5184067</v>
+      </c>
+      <c r="L25" t="n">
+        <v>30.0617098</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-95.51832570000001</v>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="O25" t="n">
+      <c r="S25" t="n">
         <v>-0.17</v>
       </c>
     </row>
@@ -4040,26 +4472,38 @@
       <c r="I26" t="n">
         <v>0.7</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" t="n">
+        <v>30.0617098</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-95.51832570000001</v>
+      </c>
+      <c r="L26" t="n">
+        <v>30.061719250386</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-95.518298876389</v>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O26" t="n">
+      <c r="S26" t="n">
         <v>-0.341</v>
       </c>
     </row>
@@ -4097,26 +4541,38 @@
       <c r="I27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" t="n">
+        <v>30.061719250386</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-95.518298876389</v>
+      </c>
+      <c r="L27" t="n">
+        <v>30.061721317373</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-95.51829300953101</v>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O27" t="n">
+      <c r="S27" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -4154,26 +4610,38 @@
       <c r="I28" t="n">
         <v>86.40000000000001</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" t="n">
+        <v>30.0607101</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-95.5181101</v>
+      </c>
+      <c r="L28" t="n">
+        <v>30.0601402</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-95.5182464</v>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O28" t="n">
+      <c r="S28" t="n">
         <v>-0.777</v>
       </c>
     </row>
@@ -4211,26 +4679,38 @@
       <c r="I29" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" t="n">
+        <v>30.0601402</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-95.5182464</v>
+      </c>
+      <c r="L29" t="n">
+        <v>30.059931577778</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-95.518252538889</v>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O29" t="n">
+      <c r="S29" t="n">
         <v>-0.731</v>
       </c>
     </row>
@@ -4268,26 +4748,38 @@
       <c r="I30" t="n">
         <v>29.7</v>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" t="n">
+        <v>30.059931577778</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-95.518252538889</v>
+      </c>
+      <c r="L30" t="n">
+        <v>30.059279</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-95.5186757</v>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O30" t="n">
+      <c r="S30" t="n">
         <v>-0.596</v>
       </c>
     </row>
@@ -4325,26 +4817,38 @@
       <c r="I31" t="n">
         <v>13.2</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" t="n">
+        <v>30.059279</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-95.5186757</v>
+      </c>
+      <c r="L31" t="n">
+        <v>30.0594157</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-95.51867470000001</v>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="O31" t="n">
+      <c r="S31" t="n">
         <v>-0.554</v>
       </c>
     </row>
@@ -4382,26 +4886,38 @@
       <c r="I32" t="n">
         <v>13.6</v>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" t="n">
+        <v>30.0594157</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-95.51867470000001</v>
+      </c>
+      <c r="L32" t="n">
+        <v>30.05941229</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-95.51867372</v>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="O32" t="n">
+      <c r="S32" t="n">
         <v>-0.641</v>
       </c>
     </row>
@@ -4439,26 +4955,38 @@
       <c r="I33" t="n">
         <v>0.7</v>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" t="n">
+        <v>30.05941229</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-95.51867372</v>
+      </c>
+      <c r="L33" t="n">
+        <v>30.059517278747</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-95.518653507599</v>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O33" t="n">
+      <c r="S33" t="n">
         <v>0.048</v>
       </c>
     </row>
@@ -4496,26 +5024,38 @@
       <c r="I34" t="n">
         <v>0</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" t="n">
+        <v>30.059517278747</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-95.518653507599</v>
+      </c>
+      <c r="L34" t="n">
+        <v>30.059522686463</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-95.518652466506</v>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O34" t="n">
+      <c r="S34" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -4553,26 +5093,38 @@
       <c r="I35" t="n">
         <v>50.1</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" t="n">
+        <v>30.0607294</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-95.51966659999999</v>
+      </c>
+      <c r="L35" t="n">
+        <v>30.062609361936</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-95.520282201469</v>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="O35" t="n">
+      <c r="S35" t="n">
         <v>-0.008999999999999999</v>
       </c>
     </row>
@@ -4610,26 +5162,38 @@
       <c r="I36" t="n">
         <v>17.7</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" t="n">
+        <v>30.062609361936</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-95.520282201469</v>
+      </c>
+      <c r="L36" t="n">
+        <v>30.0628921</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-95.52047899999999</v>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O36" t="n">
+      <c r="S36" t="n">
         <v>-0.6889999999999999</v>
       </c>
     </row>
@@ -4667,26 +5231,38 @@
       <c r="I37" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" t="n">
+        <v>30.0628921</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-95.52047899999999</v>
+      </c>
+      <c r="L37" t="n">
+        <v>30.0628601</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-95.5205643</v>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="O37" t="n">
+      <c r="S37" t="n">
         <v>-0.414</v>
       </c>
     </row>
@@ -4724,26 +5300,38 @@
       <c r="I38" t="n">
         <v>0.7</v>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" t="n">
+        <v>30.0628601</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-95.5205643</v>
+      </c>
+      <c r="L38" t="n">
+        <v>30.0628743</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-95.5206398</v>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O38" t="n">
+      <c r="S38" t="n">
         <v>-0.067</v>
       </c>
     </row>
@@ -4781,26 +5369,38 @@
       <c r="I39" t="n">
         <v>0</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" t="n">
+        <v>30.0628743</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-95.5206398</v>
+      </c>
+      <c r="L39" t="n">
+        <v>30.0628754642</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-95.520645989927</v>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O39" t="n">
+      <c r="S39" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -4838,26 +5438,38 @@
       <c r="I40" t="n">
         <v>116.9</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" t="n">
+        <v>30.0641497</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-95.5198642</v>
+      </c>
+      <c r="L40" t="n">
+        <v>30.063984198151</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-95.51730662584301</v>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K40" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="O40" t="n">
+      <c r="S40" t="n">
         <v>0.107</v>
       </c>
     </row>
@@ -4895,26 +5507,38 @@
       <c r="I41" t="n">
         <v>14.9</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" t="n">
+        <v>30.063984198151</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-95.51730662584301</v>
+      </c>
+      <c r="L41" t="n">
+        <v>30.0643281</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-95.51622860000001</v>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O41" t="n">
+      <c r="S41" t="n">
         <v>-0.249</v>
       </c>
     </row>
@@ -4952,26 +5576,38 @@
       <c r="I42" t="n">
         <v>0.7</v>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" t="n">
+        <v>30.0643281</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-95.51622860000001</v>
+      </c>
+      <c r="L42" t="n">
+        <v>30.064418761496</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-95.516314695745</v>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O42" t="n">
+      <c r="S42" t="n">
         <v>0.078</v>
       </c>
     </row>
@@ -5009,26 +5645,38 @@
       <c r="I43" t="n">
         <v>0</v>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" t="n">
+        <v>30.064418761496</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-95.516314695745</v>
+      </c>
+      <c r="L43" t="n">
+        <v>30.064422996858</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-95.516318717817</v>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>1</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O43" t="n">
+      <c r="S43" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -5066,26 +5714,38 @@
       <c r="I44" t="n">
         <v>189.5</v>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" t="n">
+        <v>30.0645873</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-95.51511429999999</v>
+      </c>
+      <c r="L44" t="n">
+        <v>30.062686258092</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-95.514417551458</v>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K44" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="O44" t="n">
+      <c r="S44" t="n">
         <v>-0.078</v>
       </c>
     </row>
@@ -5123,26 +5783,38 @@
       <c r="I45" t="n">
         <v>122.6</v>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" t="n">
+        <v>30.062686258092</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-95.514417551458</v>
+      </c>
+      <c r="L45" t="n">
+        <v>30.0622658</v>
+      </c>
+      <c r="M45" t="n">
+        <v>-95.5138019</v>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O45" t="n">
+      <c r="S45" t="n">
         <v>-0.726</v>
       </c>
     </row>
@@ -5180,26 +5852,38 @@
       <c r="I46" t="n">
         <v>42.5</v>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" t="n">
+        <v>30.0622658</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-95.5138019</v>
+      </c>
+      <c r="L46" t="n">
+        <v>30.0614594</v>
+      </c>
+      <c r="M46" t="n">
+        <v>-95.5140202</v>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O46" t="n">
+      <c r="S46" t="n">
         <v>-0.526</v>
       </c>
     </row>
@@ -5237,26 +5921,38 @@
       <c r="I47" t="n">
         <v>5.2</v>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" t="n">
+        <v>30.0614594</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-95.5140202</v>
+      </c>
+      <c r="L47" t="n">
+        <v>30.061220761111</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-95.513674477778</v>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O47" t="n">
+      <c r="S47" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -5294,26 +5990,38 @@
       <c r="I48" t="n">
         <v>0.7</v>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" t="n">
+        <v>30.061220761111</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-95.513674477778</v>
+      </c>
+      <c r="L48" t="n">
+        <v>30.061256983762</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-95.513685505143</v>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O48" t="n">
+      <c r="S48" t="n">
         <v>-0.211</v>
       </c>
     </row>
@@ -5351,26 +6059,38 @@
       <c r="I49" t="n">
         <v>0</v>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" t="n">
+        <v>30.061256983762</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-95.513685505143</v>
+      </c>
+      <c r="L49" t="n">
+        <v>30.061262285103</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-95.513687119046</v>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>1</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O49" t="n">
+      <c r="S49" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -5408,26 +6128,38 @@
       <c r="I50" t="n">
         <v>111</v>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50" t="n">
+        <v>30.0591246</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-95.51195869999999</v>
+      </c>
+      <c r="L50" t="n">
+        <v>30.0584496</v>
+      </c>
+      <c r="M50" t="n">
+        <v>-95.5095563</v>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K50" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="O50" t="n">
+      <c r="S50" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5465,26 +6197,38 @@
       <c r="I51" t="n">
         <v>57.7</v>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" t="n">
+        <v>30.0584496</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-95.5095563</v>
+      </c>
+      <c r="L51" t="n">
+        <v>30.0580498</v>
+      </c>
+      <c r="M51" t="n">
+        <v>-95.50930940000001</v>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O51" t="n">
+      <c r="S51" t="n">
         <v>-0.638</v>
       </c>
     </row>
@@ -5522,26 +6266,38 @@
       <c r="I52" t="n">
         <v>23.8</v>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" t="n">
+        <v>30.0580498</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-95.50930940000001</v>
+      </c>
+      <c r="L52" t="n">
+        <v>30.0579055</v>
+      </c>
+      <c r="M52" t="n">
+        <v>-95.5087817</v>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O52" t="n">
+      <c r="S52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -5579,26 +6335,38 @@
       <c r="I53" t="n">
         <v>1.7</v>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53" t="n">
+        <v>30.0579055</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-95.5087817</v>
+      </c>
+      <c r="L53" t="n">
+        <v>30.057749141411</v>
+      </c>
+      <c r="M53" t="n">
+        <v>-95.508889276307</v>
+      </c>
+      <c r="N53" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O53" t="n">
+      <c r="S53" t="n">
         <v>0.035</v>
       </c>
     </row>
@@ -5636,26 +6404,38 @@
       <c r="I54" t="n">
         <v>0</v>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J54" t="n">
+        <v>30.057749141411</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-95.508889276307</v>
+      </c>
+      <c r="L54" t="n">
+        <v>30.057737365499</v>
+      </c>
+      <c r="M54" t="n">
+        <v>-95.508897378239</v>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O54" t="n">
+      <c r="S54" t="n">
         <v>0.266</v>
       </c>
     </row>
@@ -5693,26 +6473,38 @@
       <c r="I55" t="n">
         <v>27.4</v>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J55" t="n">
+        <v>30.0578485</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-95.5075647</v>
+      </c>
+      <c r="L55" t="n">
+        <v>30.0591333</v>
+      </c>
+      <c r="M55" t="n">
+        <v>-95.5071447</v>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K55" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O55" t="n">
+      <c r="S55" t="n">
         <v>-0.48</v>
       </c>
     </row>
@@ -5750,26 +6542,38 @@
       <c r="I56" t="n">
         <v>4.5</v>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J56" t="n">
+        <v>30.0591333</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-95.5071447</v>
+      </c>
+      <c r="L56" t="n">
+        <v>30.0591097</v>
+      </c>
+      <c r="M56" t="n">
+        <v>-95.5069223</v>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="O56" t="n">
+      <c r="S56" t="n">
         <v>-0.08</v>
       </c>
     </row>
@@ -5807,26 +6611,38 @@
       <c r="I57" t="n">
         <v>0.7</v>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J57" t="n">
+        <v>30.0591097</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-95.5069223</v>
+      </c>
+      <c r="L57" t="n">
+        <v>30.059088712165</v>
+      </c>
+      <c r="M57" t="n">
+        <v>-95.506894749739</v>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O57" t="n">
+      <c r="S57" t="n">
         <v>-0.262</v>
       </c>
     </row>
@@ -5864,26 +6680,38 @@
       <c r="I58" t="n">
         <v>0</v>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J58" t="n">
+        <v>30.059088712165</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-95.506894749739</v>
+      </c>
+      <c r="L58" t="n">
+        <v>30.05908509001</v>
+      </c>
+      <c r="M58" t="n">
+        <v>-95.50688999502</v>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>1</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O58" t="n">
+      <c r="S58" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -5921,26 +6749,38 @@
       <c r="I59" t="n">
         <v>181.1</v>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J59" t="n">
+        <v>30.058724</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-95.5049729</v>
+      </c>
+      <c r="L59" t="n">
+        <v>30.0605306</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-95.5041234</v>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K59" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="O59" t="n">
+      <c r="S59" t="n">
         <v>-0.06900000000000001</v>
       </c>
     </row>
@@ -5978,26 +6818,38 @@
       <c r="I60" t="n">
         <v>76.40000000000001</v>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J60" t="n">
+        <v>30.0605306</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-95.5041234</v>
+      </c>
+      <c r="L60" t="n">
+        <v>30.0614103</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-95.5038969</v>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O60" t="n">
+      <c r="S60" t="n">
         <v>-0.423</v>
       </c>
     </row>
@@ -6035,26 +6887,38 @@
       <c r="I61" t="n">
         <v>28.3</v>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J61" t="n">
+        <v>30.0614103</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-95.5038969</v>
+      </c>
+      <c r="L61" t="n">
+        <v>30.0620619</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-95.50324809999999</v>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O61" t="n">
+      <c r="S61" t="n">
         <v>-0.55</v>
       </c>
     </row>
@@ -6092,26 +6956,38 @@
       <c r="I62" t="n">
         <v>22.1</v>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J62" t="n">
+        <v>30.0620619</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-95.50324809999999</v>
+      </c>
+      <c r="L62" t="n">
+        <v>30.0617459</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-95.5035556</v>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="O62" t="n">
+      <c r="S62" t="n">
         <v>-0.744</v>
       </c>
     </row>
@@ -6149,26 +7025,38 @@
       <c r="I63" t="n">
         <v>10.5</v>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J63" t="n">
+        <v>30.0617459</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-95.5035556</v>
+      </c>
+      <c r="L63" t="n">
+        <v>30.061831070588</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-95.50350280588199</v>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="O63" t="n">
+      <c r="S63" t="n">
         <v>-0.376</v>
       </c>
     </row>
@@ -6206,26 +7094,38 @@
       <c r="I64" t="n">
         <v>0.7</v>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J64" t="n">
+        <v>30.061831070588</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-95.50350280588199</v>
+      </c>
+      <c r="L64" t="n">
+        <v>30.061892780418</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-95.50344218993</v>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>1</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O64" t="n">
+      <c r="S64" t="n">
         <v>-0.024</v>
       </c>
     </row>
@@ -6263,26 +7163,38 @@
       <c r="I65" t="n">
         <v>0</v>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J65" t="n">
+        <v>30.061892780418</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-95.50344218993</v>
+      </c>
+      <c r="L65" t="n">
+        <v>30.061896957281</v>
+      </c>
+      <c r="M65" t="n">
+        <v>-95.50343808710301</v>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>1</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O65" t="n">
+      <c r="S65" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -6320,26 +7232,38 @@
       <c r="I66" t="n">
         <v>151.6</v>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J66" t="n">
+        <v>30.0619641</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-95.5057339</v>
+      </c>
+      <c r="L66" t="n">
+        <v>30.061143680771</v>
+      </c>
+      <c r="M66" t="n">
+        <v>-95.507825352252</v>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K66" t="n">
-        <v>1</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="O66" t="n">
+      <c r="S66" t="n">
         <v>0.014</v>
       </c>
     </row>
@@ -6377,26 +7301,38 @@
       <c r="I67" t="n">
         <v>32.3</v>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J67" t="n">
+        <v>30.061143680771</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-95.507825352252</v>
+      </c>
+      <c r="L67" t="n">
+        <v>30.061383</v>
+      </c>
+      <c r="M67" t="n">
+        <v>-95.5090403</v>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O67" t="n">
+      <c r="S67" t="n">
         <v>-0.588</v>
       </c>
     </row>
@@ -6434,26 +7370,38 @@
       <c r="I68" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J68" t="n">
+        <v>30.061383</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-95.5090403</v>
+      </c>
+      <c r="L68" t="n">
+        <v>30.0612595</v>
+      </c>
+      <c r="M68" t="n">
+        <v>-95.5092171</v>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O68" t="n">
+      <c r="S68" t="n">
         <v>-0.225</v>
       </c>
     </row>
@@ -6491,26 +7439,38 @@
       <c r="I69" t="n">
         <v>2.3</v>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J69" t="n">
+        <v>30.0612595</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-95.5092171</v>
+      </c>
+      <c r="L69" t="n">
+        <v>30.061216423586</v>
+      </c>
+      <c r="M69" t="n">
+        <v>-95.50925137582399</v>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>1</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O69" t="n">
+      <c r="S69" t="n">
         <v>-0.491</v>
       </c>
     </row>
@@ -6548,26 +7508,38 @@
       <c r="I70" t="n">
         <v>0.7</v>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J70" t="n">
+        <v>30.061216423586</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-95.50925137582399</v>
+      </c>
+      <c r="L70" t="n">
+        <v>30.061203662866</v>
+      </c>
+      <c r="M70" t="n">
+        <v>-95.509258680835</v>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>1</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O70" t="n">
+      <c r="S70" t="n">
         <v>-0.579</v>
       </c>
     </row>
@@ -6605,26 +7577,38 @@
       <c r="I71" t="n">
         <v>0</v>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J71" t="n">
+        <v>30.061203662866</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-95.509258680835</v>
+      </c>
+      <c r="L71" t="n">
+        <v>30.061200620534</v>
+      </c>
+      <c r="M71" t="n">
+        <v>-95.509263950274</v>
+      </c>
+      <c r="N71" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>1</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O71" t="n">
+      <c r="S71" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -6662,26 +7646,38 @@
       <c r="I72" t="n">
         <v>260</v>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J72" t="n">
+        <v>30.0625288</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-95.5096626</v>
+      </c>
+      <c r="L72" t="n">
+        <v>30.063966787934</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-95.50847176462401</v>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K72" t="n">
-        <v>1</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="O72" t="n">
+      <c r="S72" t="n">
         <v>-0.335</v>
       </c>
     </row>
@@ -6719,26 +7715,38 @@
       <c r="I73" t="n">
         <v>196.6</v>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J73" t="n">
+        <v>30.063966787934</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-95.50847176462401</v>
+      </c>
+      <c r="L73" t="n">
+        <v>30.0644037</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-95.5081204</v>
+      </c>
+      <c r="N73" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O73" t="n">
+      <c r="S73" t="n">
         <v>-0.591</v>
       </c>
     </row>
@@ -6776,26 +7784,38 @@
       <c r="I74" t="n">
         <v>142.9</v>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J74" t="n">
+        <v>30.0644037</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-95.5081204</v>
+      </c>
+      <c r="L74" t="n">
+        <v>30.06453</v>
+      </c>
+      <c r="M74" t="n">
+        <v>-95.5075255</v>
+      </c>
+      <c r="N74" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O74" t="n">
+      <c r="S74" t="n">
         <v>-0.519</v>
       </c>
     </row>
@@ -6833,26 +7853,38 @@
       <c r="I75" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="J75" t="n">
+        <v>30.06453</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-95.5075255</v>
+      </c>
+      <c r="L75" t="n">
+        <v>30.0648562</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-95.50732530000001</v>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O75" t="n">
+      <c r="S75" t="n">
         <v>-0.634</v>
       </c>
     </row>
@@ -6890,26 +7922,38 @@
       <c r="I76" t="n">
         <v>23.3</v>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="J76" t="n">
+        <v>30.0648562</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-95.50732530000001</v>
+      </c>
+      <c r="L76" t="n">
+        <v>30.06566107785</v>
+      </c>
+      <c r="M76" t="n">
+        <v>-95.506800748408</v>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O76" t="n">
+      <c r="S76" t="n">
         <v>-0.424</v>
       </c>
     </row>
@@ -6947,26 +7991,38 @@
       <c r="I77" t="n">
         <v>20</v>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J77" t="n">
+        <v>30.06566107785</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-95.506800748408</v>
+      </c>
+      <c r="L77" t="n">
+        <v>30.065638154785</v>
+      </c>
+      <c r="M77" t="n">
+        <v>-95.506673678756</v>
+      </c>
+      <c r="N77" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="O77" t="n">
+      <c r="S77" t="n">
         <v>-0.592</v>
       </c>
     </row>
@@ -7004,26 +8060,38 @@
       <c r="I78" t="n">
         <v>0</v>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J78" t="n">
+        <v>30.065638154785</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-95.506673678756</v>
+      </c>
+      <c r="L78" t="n">
+        <v>30.065480564849</v>
+      </c>
+      <c r="M78" t="n">
+        <v>-95.506726864749</v>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>1</v>
-      </c>
-      <c r="M78" t="n">
-        <v>1</v>
-      </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1</v>
+      </c>
+      <c r="R78" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O78" t="n">
+      <c r="S78" t="n">
         <v>0.218</v>
       </c>
     </row>
@@ -7061,26 +8129,38 @@
       <c r="I79" t="n">
         <v>102.3</v>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J79" t="n">
+        <v>30.0659154</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-95.5072768</v>
+      </c>
+      <c r="L79" t="n">
+        <v>30.064406394972</v>
+      </c>
+      <c r="M79" t="n">
+        <v>-95.50894718617199</v>
+      </c>
+      <c r="N79" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K79" t="n">
-        <v>1</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="O79" t="n">
+      <c r="S79" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -7118,26 +8198,38 @@
       <c r="I80" t="n">
         <v>40.4</v>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J80" t="n">
+        <v>30.064406394972</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-95.50894718617199</v>
+      </c>
+      <c r="L80" t="n">
+        <v>30.0639957</v>
+      </c>
+      <c r="M80" t="n">
+        <v>-95.5092968</v>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O80" t="n">
+      <c r="S80" t="n">
         <v>-0.575</v>
       </c>
     </row>
@@ -7175,26 +8267,38 @@
       <c r="I81" t="n">
         <v>12.9</v>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J81" t="n">
+        <v>30.0639957</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-95.5092968</v>
+      </c>
+      <c r="L81" t="n">
+        <v>30.0636485</v>
+      </c>
+      <c r="M81" t="n">
+        <v>-95.5095985</v>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O81" t="n">
+      <c r="S81" t="n">
         <v>-0.261</v>
       </c>
     </row>
@@ -7232,26 +8336,38 @@
       <c r="I82" t="n">
         <v>0.7</v>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J82" t="n">
+        <v>30.0636485</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-95.5095985</v>
+      </c>
+      <c r="L82" t="n">
+        <v>30.0637403</v>
+      </c>
+      <c r="M82" t="n">
+        <v>-95.5095513</v>
+      </c>
+      <c r="N82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
-        <v>1</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O82" t="n">
+      <c r="S82" t="n">
         <v>0.032</v>
       </c>
     </row>
@@ -7289,26 +8405,38 @@
       <c r="I83" t="n">
         <v>0</v>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="J83" t="n">
+        <v>30.0637403</v>
+      </c>
+      <c r="K83" t="n">
+        <v>-95.5095513</v>
+      </c>
+      <c r="L83" t="n">
+        <v>30.063745308749</v>
+      </c>
+      <c r="M83" t="n">
+        <v>-95.50954872469499</v>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>1</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O83" t="n">
+      <c r="S83" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -7346,26 +8474,38 @@
       <c r="I84" t="n">
         <v>29</v>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="J84" t="n">
+        <v>30.0656724</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-95.5099512</v>
+      </c>
+      <c r="L84" t="n">
+        <v>30.0667617</v>
+      </c>
+      <c r="M84" t="n">
+        <v>-95.51054310000001</v>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K84" t="n">
-        <v>1</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O84" t="n">
+      <c r="S84" t="n">
         <v>-0.521</v>
       </c>
     </row>
@@ -7403,26 +8543,38 @@
       <c r="I85" t="n">
         <v>17.9</v>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J85" t="n">
+        <v>30.0667617</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-95.51054310000001</v>
+      </c>
+      <c r="L85" t="n">
+        <v>30.066710205405</v>
+      </c>
+      <c r="M85" t="n">
+        <v>-95.51044804054099</v>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="O85" t="n">
+      <c r="S85" t="n">
         <v>-0.477</v>
       </c>
     </row>
@@ -7460,26 +8612,38 @@
       <c r="I86" t="n">
         <v>0.7</v>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="J86" t="n">
+        <v>30.066710205405</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-95.51044804054099</v>
+      </c>
+      <c r="L86" t="n">
+        <v>30.066592821294</v>
+      </c>
+      <c r="M86" t="n">
+        <v>-95.510356864613</v>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
-        <v>1</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O86" t="n">
+      <c r="S86" t="n">
         <v>0.152</v>
       </c>
     </row>
@@ -7517,26 +8681,38 @@
       <c r="I87" t="n">
         <v>0</v>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="J87" t="n">
+        <v>30.066592821294</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-95.510356864613</v>
+      </c>
+      <c r="L87" t="n">
+        <v>30.066588271455</v>
+      </c>
+      <c r="M87" t="n">
+        <v>-95.510353330615</v>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>1</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="inlineStr">
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O87" t="n">
+      <c r="S87" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -7574,26 +8750,38 @@
       <c r="I88" t="n">
         <v>24</v>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J88" t="n">
+        <v>30.066162482285</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-95.511866100132</v>
+      </c>
+      <c r="L88" t="n">
+        <v>30.064209660182</v>
+      </c>
+      <c r="M88" t="n">
+        <v>-95.511504001915</v>
+      </c>
+      <c r="N88" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K88" t="n">
-        <v>1</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="inlineStr">
+      <c r="O88" t="n">
+        <v>1</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="O88" t="n">
+      <c r="S88" t="n">
         <v>-0.078</v>
       </c>
     </row>
@@ -7631,26 +8819,38 @@
       <c r="I89" t="n">
         <v>4.3</v>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="J89" t="n">
+        <v>30.064209660182</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-95.511504001915</v>
+      </c>
+      <c r="L89" t="n">
+        <v>30.0641854</v>
+      </c>
+      <c r="M89" t="n">
+        <v>-95.5112743</v>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="inlineStr">
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="O89" t="n">
+      <c r="S89" t="n">
         <v>-0.286</v>
       </c>
     </row>
@@ -7688,26 +8888,38 @@
       <c r="I90" t="n">
         <v>2.3</v>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="J90" t="n">
+        <v>30.0641854</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-95.5112743</v>
+      </c>
+      <c r="L90" t="n">
+        <v>30.06416996755</v>
+      </c>
+      <c r="M90" t="n">
+        <v>-95.51127963669801</v>
+      </c>
+      <c r="N90" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>1</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="inlineStr">
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O90" t="n">
+      <c r="S90" t="n">
         <v>-0.701</v>
       </c>
     </row>
@@ -7745,26 +8957,38 @@
       <c r="I91" t="n">
         <v>0.7</v>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="J91" t="n">
+        <v>30.06416996755</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-95.51127963669801</v>
+      </c>
+      <c r="L91" t="n">
+        <v>30.064156837311</v>
+      </c>
+      <c r="M91" t="n">
+        <v>-95.511284177268</v>
+      </c>
+      <c r="N91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>1</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="inlineStr">
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O91" t="n">
+      <c r="S91" t="n">
         <v>-0.579</v>
       </c>
     </row>
@@ -7802,26 +9026,38 @@
       <c r="I92" t="n">
         <v>0</v>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="J92" t="n">
+        <v>30.064156837311</v>
+      </c>
+      <c r="K92" t="n">
+        <v>-95.511284177268</v>
+      </c>
+      <c r="L92" t="n">
+        <v>30.064151585215</v>
+      </c>
+      <c r="M92" t="n">
+        <v>-95.51128599349499</v>
+      </c>
+      <c r="N92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K92" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="n">
-        <v>1</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="inlineStr">
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O92" t="n">
+      <c r="S92" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -7859,26 +9095,38 @@
       <c r="I93" t="n">
         <v>156.8</v>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="J93" t="n">
+        <v>30.063699250551</v>
+      </c>
+      <c r="K93" t="n">
+        <v>-95.510058291256</v>
+      </c>
+      <c r="L93" t="n">
+        <v>30.061683701639</v>
+      </c>
+      <c r="M93" t="n">
+        <v>-95.511086247861</v>
+      </c>
+      <c r="N93" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="K93" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="inlineStr">
+      <c r="O93" t="n">
+        <v>1</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="O93" t="n">
+      <c r="S93" t="n">
         <v>0.064</v>
       </c>
     </row>
@@ -7916,26 +9164,38 @@
       <c r="I94" t="n">
         <v>5</v>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="J94" t="n">
+        <v>30.061683701639</v>
+      </c>
+      <c r="K94" t="n">
+        <v>-95.511086247861</v>
+      </c>
+      <c r="L94" t="n">
+        <v>30.060582912364</v>
+      </c>
+      <c r="M94" t="n">
+        <v>-95.511765895002</v>
+      </c>
+      <c r="N94" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="inlineStr">
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="O94" t="n">
+      <c r="S94" t="n">
         <v>0.179</v>
       </c>
     </row>
@@ -7973,26 +9233,38 @@
       <c r="I95" t="n">
         <v>0.7</v>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="J95" t="n">
+        <v>30.060582912364</v>
+      </c>
+      <c r="K95" t="n">
+        <v>-95.511765895002</v>
+      </c>
+      <c r="L95" t="n">
+        <v>30.060551162242</v>
+      </c>
+      <c r="M95" t="n">
+        <v>-95.51178458856999</v>
+      </c>
+      <c r="N95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
-        <v>1</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" t="inlineStr">
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O95" t="n">
+      <c r="S95" t="n">
         <v>-0.223</v>
       </c>
     </row>
@@ -8030,26 +9302,38 @@
       <c r="I96" t="n">
         <v>0</v>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="J96" t="n">
+        <v>30.060551162242</v>
+      </c>
+      <c r="K96" t="n">
+        <v>-95.51178458856999</v>
+      </c>
+      <c r="L96" t="n">
+        <v>30.060546277607</v>
+      </c>
+      <c r="M96" t="n">
+        <v>-95.51178746450201</v>
+      </c>
+      <c r="N96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
-        <v>1</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="inlineStr">
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="O96" t="n">
+      <c r="S96" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -10263,7 +11547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -10659,7 +11943,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-07 19:06 UTC  |  Rounds: 1  Shots: 95</t>
+          <t>Date pulled: 2026-06-07 19:48 UTC  |  Rounds: 1  Shots: 95</t>
         </is>
       </c>
     </row>
@@ -10756,7 +12040,14 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GPS coordinates, names, email, DOB are EXCLUDED from all outputs.</t>
+          <t>Shot GPS coordinates ARE included (shots.csv/holes.csv/maps) per owner request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Identity (name, email, DOB, GHIN#) is still excluded from all outputs.</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -11943,7 +11943,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-07 19:48 UTC  |  Rounds: 1  Shots: 95</t>
+          <t>Date pulled: 2026-06-08 01:48 UTC  |  Rounds: 1  Shots: 95</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -11943,7 +11943,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-08 01:48 UTC  |  Rounds: 1  Shots: 95</t>
+          <t>Date pulled: 2026-06-10 04:58 UTC  |  Rounds: 1  Shots: 95</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -11943,7 +11943,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-10 04:58 UTC  |  Rounds: 1  Shots: 95</t>
+          <t>Date pulled: 2026-06-10 12:00 UTC  |  Rounds: 1  Shots: 95</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -11943,7 +11943,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-10 12:00 UTC  |  Rounds: 1  Shots: 95</t>
+          <t>Date pulled: 2026-06-11 12:00 UTC  |  Rounds: 1  Shots: 95</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -2868,7 +2868,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4 Iron</t>
+          <t>5 Iron</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6 Iron</t>
+          <t>7 Iron</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>54 Wedge</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8 Iron</t>
+          <t>9 Iron</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>50 Wedge</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>58 Wedge</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4 Iron</t>
+          <t>5 Iron</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4 Iron</t>
+          <t>5 Iron</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4 Iron</t>
+          <t>5 Iron</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5 Iron</t>
+          <t>6 Iron</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>54 Wedge</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>5 Iron</t>
+          <t>6 Iron</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>50 Wedge</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>58 Wedge</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>50 Wedge</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>50 Wedge</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>9 Iron</t>
+          <t>Pitching Wedge</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9 Iron</t>
+          <t>Pitching Wedge</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7 Iron</t>
+          <t>8 Iron</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4 Iron</t>
+          <t>5 Iron</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>54 Wedge</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>50 Wedge</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>58 Wedge</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>6 Iron</t>
+          <t>7 Iron</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>54 Wedge</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>4 Iron</t>
+          <t>5 Iron</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>50 Wedge</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>50 Wedge</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>50 Wedge</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>4 Iron</t>
+          <t>5 Iron</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>54 Wedge</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>4 Iron</t>
+          <t>5 Iron</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>4 Iron</t>
+          <t>5 Iron</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>9 Iron</t>
+          <t>Pitching Wedge</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>58 Wedge</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>6 Iron</t>
+          <t>7 Iron</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>58 Wedge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>8 Iron</t>
+          <t>9 Iron</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>54 Wedge</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>58 Wedge</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>6 Iron</t>
+          <t>7 Iron</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -9620,7 +9620,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6 Iron</t>
+          <t>7 Iron</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9676,7 +9676,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5 Iron</t>
+          <t>6 Iron</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -9716,7 +9716,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7 Iron</t>
+          <t>8 Iron</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -9758,7 +9758,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4 Iron</t>
+          <t>5 Iron</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -9812,7 +9812,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8 Iron</t>
+          <t>9 Iron</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -9854,12 +9854,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9 Iron</t>
+          <t>Pitching Wedge</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Wedge</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -9904,7 +9904,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>50 Wedge</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -9958,7 +9958,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>54 Wedge</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -9996,7 +9996,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Wedge</t>
+          <t>58 Wedge</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -11943,7 +11943,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-11 12:00 UTC  |  Rounds: 1  Shots: 95</t>
+          <t>Date pulled: 2026-06-11 23:42 UTC  |  Rounds: 1  Shots: 95</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -11943,7 +11943,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-11 23:42 UTC  |  Rounds: 1  Shots: 95</t>
+          <t>Date pulled: 2026-06-12 12:00 UTC  |  Rounds: 1  Shots: 95</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -11943,7 +11943,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-12 12:00 UTC  |  Rounds: 1  Shots: 95</t>
+          <t>Date pulled: 2026-06-13 12:00 UTC  |  Rounds: 1  Shots: 95</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -11943,7 +11943,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-13 12:00 UTC  |  Rounds: 1  Shots: 95</t>
+          <t>Date pulled: 2026-06-14 12:00 UTC  |  Rounds: 1  Shots: 95</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT2"/>
+  <dimension ref="A1:AT3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -876,6 +876,154 @@
         <v>-10.2852</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6586</v>
+      </c>
+      <c r="F3" t="n">
+        <v>133</v>
+      </c>
+      <c r="G3" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I3" t="n">
+        <v>94</v>
+      </c>
+      <c r="J3" t="n">
+        <v>72</v>
+      </c>
+      <c r="K3" t="n">
+        <v>22</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>04:28:03</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>36</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>14</v>
+      </c>
+      <c r="U3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="V3" t="n">
+        <v>13</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>200.1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-20.1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-18.28</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-3.17</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-18.0783</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-18.7461</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-27.3459</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-18.5154</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-2.47542</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-8.83972</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -887,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AA37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2650,6 +2798,1600 @@
         <v>0.033</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="U20" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>30.055389806647</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-95.511873113416</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-1.674</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>30.055765568762</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-95.51444253951099</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.017</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>359.8</v>
+      </c>
+      <c r="U22" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>30.054353477852</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-95.516658354329</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-1.667</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>543.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>30.05908200417</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-95.51500609964501</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-1.718</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>357.8</v>
+      </c>
+      <c r="U24" t="n">
+        <v>276.9</v>
+      </c>
+      <c r="V24" t="n">
+        <v>24</v>
+      </c>
+      <c r="W24" t="n">
+        <v>30.06179343257</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-95.51822695304899</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-0.868</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>164.7</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="W25" t="n">
+        <v>30.059612021262</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-95.51860311448699</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-1.617</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>352.8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>76</v>
+      </c>
+      <c r="V26" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>30.062893350155</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-95.52077577513001</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-1.567</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>210.6</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W27" t="n">
+        <v>30.064421115021</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-95.51634137024401</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-0.342</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>438.8</v>
+      </c>
+      <c r="U28" t="n">
+        <v>261.2</v>
+      </c>
+      <c r="V28" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W28" t="n">
+        <v>30.0613222672</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-95.51365555265799</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-0.484</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>269.1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>30.0578214022</v>
+      </c>
+      <c r="X29" t="n">
+        <v>-95.508913475274</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-0.847</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>160.4</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>30.059005195483</v>
+      </c>
+      <c r="X30" t="n">
+        <v>-95.50677836126999</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-1.799</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>428.4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>265.2</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W31" t="n">
+        <v>30.061806918002</v>
+      </c>
+      <c r="X31" t="n">
+        <v>-95.50344991160399</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>418.5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W32" t="n">
+        <v>30.061140995627</v>
+      </c>
+      <c r="X32" t="n">
+        <v>-95.509252118997</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-1.429</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>14</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>499.2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>178.6</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W33" t="n">
+        <v>30.065480564849</v>
+      </c>
+      <c r="X33" t="n">
+        <v>-95.506726864749</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-0.9389999999999999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>370</v>
+      </c>
+      <c r="U34" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="V34" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W34" t="n">
+        <v>30.063751735931</v>
+      </c>
+      <c r="X34" t="n">
+        <v>-95.509564284218</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-0.6919999999999999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>16</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>166.6</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="n">
+        <v>5</v>
+      </c>
+      <c r="W35" t="n">
+        <v>30.066613157199</v>
+      </c>
+      <c r="X35" t="n">
+        <v>-95.51034311068101</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>17</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>271.9</v>
+      </c>
+      <c r="U36" t="n">
+        <v>236</v>
+      </c>
+      <c r="V36" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="W36" t="n">
+        <v>30.064025150648</v>
+      </c>
+      <c r="X36" t="n">
+        <v>-95.511237708325</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-0.196</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>18</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>418.9</v>
+      </c>
+      <c r="U37" t="n">
+        <v>230.6</v>
+      </c>
+      <c r="V37" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="W37" t="n">
+        <v>30.060634822692</v>
+      </c>
+      <c r="X37" t="n">
+        <v>-95.51179681363099</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-1.363</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2661,7 +4403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S96"/>
+  <dimension ref="A1:S190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9334,6 +11076,6492 @@
         </is>
       </c>
       <c r="S96" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="H97" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="I97" t="n">
+        <v>261.1</v>
+      </c>
+      <c r="J97" t="n">
+        <v>30.0578917</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-95.5136962</v>
+      </c>
+      <c r="L97" t="n">
+        <v>30.057158366667</v>
+      </c>
+      <c r="M97" t="n">
+        <v>-95.513280166667</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O97" t="n">
+        <v>1</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="S97" t="n">
+        <v>-0.667</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>3 Wood</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H98" t="n">
+        <v>261.1</v>
+      </c>
+      <c r="I98" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="J98" t="n">
+        <v>30.057158366667</v>
+      </c>
+      <c r="K98" t="n">
+        <v>-95.513280166667</v>
+      </c>
+      <c r="L98" t="n">
+        <v>30.0569558</v>
+      </c>
+      <c r="M98" t="n">
+        <v>-95.5131428</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S98" t="n">
+        <v>-0.8159999999999999</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="n">
+        <v>3</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>169.8</v>
+      </c>
+      <c r="H99" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="I99" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="J99" t="n">
+        <v>30.0569558</v>
+      </c>
+      <c r="K99" t="n">
+        <v>-95.5131428</v>
+      </c>
+      <c r="L99" t="n">
+        <v>30.055870917143</v>
+      </c>
+      <c r="M99" t="n">
+        <v>-95.51212641714299</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S99" t="n">
+        <v>-0.109</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="H100" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="I100" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J100" t="n">
+        <v>30.055870917143</v>
+      </c>
+      <c r="K100" t="n">
+        <v>-95.51212641714299</v>
+      </c>
+      <c r="L100" t="n">
+        <v>30.055503</v>
+      </c>
+      <c r="M100" t="n">
+        <v>-95.5117566</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S100" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="n">
+        <v>5</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H101" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I101" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J101" t="n">
+        <v>30.055503</v>
+      </c>
+      <c r="K101" t="n">
+        <v>-95.5117566</v>
+      </c>
+      <c r="L101" t="n">
+        <v>30.055404133393</v>
+      </c>
+      <c r="M101" t="n">
+        <v>-95.511858366474</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S101" t="n">
+        <v>-0.256</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>6</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>30.055404133393</v>
+      </c>
+      <c r="K102" t="n">
+        <v>-95.511858366474</v>
+      </c>
+      <c r="L102" t="n">
+        <v>30.055389806647</v>
+      </c>
+      <c r="M102" t="n">
+        <v>-95.511873113416</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S102" t="n">
+        <v>0.434</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Pitching Wedge</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="H103" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="I103" t="n">
+        <v>5</v>
+      </c>
+      <c r="J103" t="n">
+        <v>30.0547575</v>
+      </c>
+      <c r="K103" t="n">
+        <v>-95.5141338</v>
+      </c>
+      <c r="L103" t="n">
+        <v>30.0557996</v>
+      </c>
+      <c r="M103" t="n">
+        <v>-95.51446919999999</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O103" t="n">
+        <v>1</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S103" t="n">
+        <v>0.193</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H104" t="n">
+        <v>5</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J104" t="n">
+        <v>30.0557996</v>
+      </c>
+      <c r="K104" t="n">
+        <v>-95.51446919999999</v>
+      </c>
+      <c r="L104" t="n">
+        <v>30.055770106261</v>
+      </c>
+      <c r="M104" t="n">
+        <v>-95.514446094242</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S104" t="n">
+        <v>-0.223</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" t="n">
+        <v>3</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>30.055770106261</v>
+      </c>
+      <c r="K105" t="n">
+        <v>-95.514446094242</v>
+      </c>
+      <c r="L105" t="n">
+        <v>30.055765568762</v>
+      </c>
+      <c r="M105" t="n">
+        <v>-95.51444253951099</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S105" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>3</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="H106" t="n">
+        <v>359.8</v>
+      </c>
+      <c r="I106" t="n">
+        <v>226</v>
+      </c>
+      <c r="J106" t="n">
+        <v>30.0567604</v>
+      </c>
+      <c r="K106" t="n">
+        <v>-95.5146709</v>
+      </c>
+      <c r="L106" t="n">
+        <v>30.0554215</v>
+      </c>
+      <c r="M106" t="n">
+        <v>-95.5149014</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O106" t="n">
+        <v>1</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="S106" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>3</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>148.9</v>
+      </c>
+      <c r="H107" t="n">
+        <v>226</v>
+      </c>
+      <c r="I107" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="J107" t="n">
+        <v>30.0554215</v>
+      </c>
+      <c r="K107" t="n">
+        <v>-95.5149014</v>
+      </c>
+      <c r="L107" t="n">
+        <v>30.054829</v>
+      </c>
+      <c r="M107" t="n">
+        <v>-95.5161392</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S107" t="n">
+        <v>-0.186</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" t="n">
+        <v>3</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>58 Wedge</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>85</v>
+      </c>
+      <c r="H108" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I108" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J108" t="n">
+        <v>30.054829</v>
+      </c>
+      <c r="K108" t="n">
+        <v>-95.5161392</v>
+      </c>
+      <c r="L108" t="n">
+        <v>30.054292</v>
+      </c>
+      <c r="M108" t="n">
+        <v>-95.5166555</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S108" t="n">
+        <v>0.053</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" t="n">
+        <v>4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H109" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I109" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J109" t="n">
+        <v>30.054292</v>
+      </c>
+      <c r="K109" t="n">
+        <v>-95.5166555</v>
+      </c>
+      <c r="L109" t="n">
+        <v>30.05433430537</v>
+      </c>
+      <c r="M109" t="n">
+        <v>-95.516657464178</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S109" t="n">
+        <v>-0.528</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" t="n">
+        <v>5</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J110" t="n">
+        <v>30.05433430537</v>
+      </c>
+      <c r="K110" t="n">
+        <v>-95.516657464178</v>
+      </c>
+      <c r="L110" t="n">
+        <v>30.054348</v>
+      </c>
+      <c r="M110" t="n">
+        <v>-95.5166581</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S110" t="n">
+        <v>-0.579</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>3</v>
+      </c>
+      <c r="D111" t="n">
+        <v>6</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>30.054348</v>
+      </c>
+      <c r="K111" t="n">
+        <v>-95.5166581</v>
+      </c>
+      <c r="L111" t="n">
+        <v>30.054353477852</v>
+      </c>
+      <c r="M111" t="n">
+        <v>-95.516658354329</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S111" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>4</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="H112" t="n">
+        <v>543.1</v>
+      </c>
+      <c r="I112" t="n">
+        <v>276.6</v>
+      </c>
+      <c r="J112" t="n">
+        <v>30.0548809</v>
+      </c>
+      <c r="K112" t="n">
+        <v>-95.51675830000001</v>
+      </c>
+      <c r="L112" t="n">
+        <v>30.0568145</v>
+      </c>
+      <c r="M112" t="n">
+        <v>-95.5152176</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O112" t="n">
+        <v>1</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="S112" t="n">
+        <v>-0.007</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>4</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="H113" t="n">
+        <v>276.6</v>
+      </c>
+      <c r="I113" t="n">
+        <v>146.6</v>
+      </c>
+      <c r="J113" t="n">
+        <v>30.0568145</v>
+      </c>
+      <c r="K113" t="n">
+        <v>-95.5152176</v>
+      </c>
+      <c r="L113" t="n">
+        <v>30.0578998</v>
+      </c>
+      <c r="M113" t="n">
+        <v>-95.5152813</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S113" t="n">
+        <v>-0.262</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>4</v>
+      </c>
+      <c r="D114" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>9 Iron</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>152.4</v>
+      </c>
+      <c r="H114" t="n">
+        <v>146.6</v>
+      </c>
+      <c r="I114" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="J114" t="n">
+        <v>30.0578998</v>
+      </c>
+      <c r="K114" t="n">
+        <v>-95.5152813</v>
+      </c>
+      <c r="L114" t="n">
+        <v>30.0591489</v>
+      </c>
+      <c r="M114" t="n">
+        <v>-95.5154017</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S114" t="n">
+        <v>-0.438</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>4</v>
+      </c>
+      <c r="D115" t="n">
+        <v>4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>58 Wedge</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>22</v>
+      </c>
+      <c r="H115" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="I115" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="J115" t="n">
+        <v>30.0591489</v>
+      </c>
+      <c r="K115" t="n">
+        <v>-95.5154017</v>
+      </c>
+      <c r="L115" t="n">
+        <v>30.0591668</v>
+      </c>
+      <c r="M115" t="n">
+        <v>-95.5151939</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S115" t="n">
+        <v>-0.626</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>4</v>
+      </c>
+      <c r="D116" t="n">
+        <v>5</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>58 Wedge</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H116" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J116" t="n">
+        <v>30.0591668</v>
+      </c>
+      <c r="K116" t="n">
+        <v>-95.5151939</v>
+      </c>
+      <c r="L116" t="n">
+        <v>30.0590957</v>
+      </c>
+      <c r="M116" t="n">
+        <v>-95.5150067</v>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="S116" t="n">
+        <v>0.349</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D117" t="n">
+        <v>6</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J117" t="n">
+        <v>30.0590957</v>
+      </c>
+      <c r="K117" t="n">
+        <v>-95.5150067</v>
+      </c>
+      <c r="L117" t="n">
+        <v>30.059087482502</v>
+      </c>
+      <c r="M117" t="n">
+        <v>-95.51500633978701</v>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S117" t="n">
+        <v>-0.747</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>4</v>
+      </c>
+      <c r="D118" t="n">
+        <v>7</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>30.059087482502</v>
+      </c>
+      <c r="K118" t="n">
+        <v>-95.51500633978701</v>
+      </c>
+      <c r="L118" t="n">
+        <v>30.05908200417</v>
+      </c>
+      <c r="M118" t="n">
+        <v>-95.51500609964501</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S118" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>5</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>276.9</v>
+      </c>
+      <c r="H119" t="n">
+        <v>357.8</v>
+      </c>
+      <c r="I119" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="J119" t="n">
+        <v>30.0603288</v>
+      </c>
+      <c r="K119" t="n">
+        <v>-95.5152781</v>
+      </c>
+      <c r="L119" t="n">
+        <v>30.061214</v>
+      </c>
+      <c r="M119" t="n">
+        <v>-95.5177023</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O119" t="n">
+        <v>1</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="S119" t="n">
+        <v>0.144</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>5</v>
+      </c>
+      <c r="D120" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="H120" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="I120" t="n">
+        <v>24</v>
+      </c>
+      <c r="J120" t="n">
+        <v>30.061214</v>
+      </c>
+      <c r="K120" t="n">
+        <v>-95.5177023</v>
+      </c>
+      <c r="L120" t="n">
+        <v>30.061707</v>
+      </c>
+      <c r="M120" t="n">
+        <v>-95.5180221</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S120" t="n">
+        <v>-0.316</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>5</v>
+      </c>
+      <c r="D121" t="n">
+        <v>3</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H121" t="n">
+        <v>24</v>
+      </c>
+      <c r="I121" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J121" t="n">
+        <v>30.061707</v>
+      </c>
+      <c r="K121" t="n">
+        <v>-95.5180221</v>
+      </c>
+      <c r="L121" t="n">
+        <v>30.061785024374</v>
+      </c>
+      <c r="M121" t="n">
+        <v>-95.51820702481</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S121" t="n">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>5</v>
+      </c>
+      <c r="D122" t="n">
+        <v>4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H122" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J122" t="n">
+        <v>30.061785024374</v>
+      </c>
+      <c r="K122" t="n">
+        <v>-95.51820702481</v>
+      </c>
+      <c r="L122" t="n">
+        <v>30.0617918</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-95.518233</v>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S122" t="n">
+        <v>-0.579</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>5</v>
+      </c>
+      <c r="D123" t="n">
+        <v>5</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>30.0617918</v>
+      </c>
+      <c r="K123" t="n">
+        <v>-95.518233</v>
+      </c>
+      <c r="L123" t="n">
+        <v>30.06179343257</v>
+      </c>
+      <c r="M123" t="n">
+        <v>-95.51822695304899</v>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S123" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>6</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>5 Wood</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>141.9</v>
+      </c>
+      <c r="H124" t="n">
+        <v>164.7</v>
+      </c>
+      <c r="I124" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="J124" t="n">
+        <v>30.060949250909</v>
+      </c>
+      <c r="K124" t="n">
+        <v>-95.51835292181801</v>
+      </c>
+      <c r="L124" t="n">
+        <v>30.0597872</v>
+      </c>
+      <c r="M124" t="n">
+        <v>-95.51822730000001</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O124" t="n">
+        <v>1</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S124" t="n">
+        <v>-0.625</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>6</v>
+      </c>
+      <c r="D125" t="n">
+        <v>2</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>58 Wedge</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="I125" t="n">
+        <v>26</v>
+      </c>
+      <c r="J125" t="n">
+        <v>30.0597872</v>
+      </c>
+      <c r="K125" t="n">
+        <v>-95.51822730000001</v>
+      </c>
+      <c r="L125" t="n">
+        <v>30.0594939</v>
+      </c>
+      <c r="M125" t="n">
+        <v>-95.5188095</v>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S125" t="n">
+        <v>-0.648</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>6</v>
+      </c>
+      <c r="D126" t="n">
+        <v>3</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>58 Wedge</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H126" t="n">
+        <v>26</v>
+      </c>
+      <c r="I126" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="J126" t="n">
+        <v>30.0594939</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-95.5188095</v>
+      </c>
+      <c r="L126" t="n">
+        <v>30.0595196</v>
+      </c>
+      <c r="M126" t="n">
+        <v>-95.5187648</v>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="S126" t="n">
+        <v>-0.571</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>6</v>
+      </c>
+      <c r="D127" t="n">
+        <v>4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H127" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J127" t="n">
+        <v>30.0595196</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-95.5187648</v>
+      </c>
+      <c r="L127" t="n">
+        <v>30.059609</v>
+      </c>
+      <c r="M127" t="n">
+        <v>-95.51860840000001</v>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S127" t="n">
+        <v>0.214</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>6</v>
+      </c>
+      <c r="D128" t="n">
+        <v>5</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>30.059609</v>
+      </c>
+      <c r="K128" t="n">
+        <v>-95.51860840000001</v>
+      </c>
+      <c r="L128" t="n">
+        <v>30.059612021262</v>
+      </c>
+      <c r="M128" t="n">
+        <v>-95.51860311448699</v>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S128" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>7</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>76</v>
+      </c>
+      <c r="H129" t="n">
+        <v>352.8</v>
+      </c>
+      <c r="I129" t="n">
+        <v>281.3</v>
+      </c>
+      <c r="J129" t="n">
+        <v>30.0602103</v>
+      </c>
+      <c r="K129" t="n">
+        <v>-95.51950170000001</v>
+      </c>
+      <c r="L129" t="n">
+        <v>30.0608329</v>
+      </c>
+      <c r="M129" t="n">
+        <v>-95.5195617</v>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O129" t="n">
+        <v>1</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="S129" t="n">
+        <v>-0.797</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>7</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>220.9</v>
+      </c>
+      <c r="H130" t="n">
+        <v>281.3</v>
+      </c>
+      <c r="I130" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="J130" t="n">
+        <v>30.0608329</v>
+      </c>
+      <c r="K130" t="n">
+        <v>-95.5195617</v>
+      </c>
+      <c r="L130" t="n">
+        <v>30.0624278</v>
+      </c>
+      <c r="M130" t="n">
+        <v>-95.5205663</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S130" t="n">
+        <v>0.133</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>7</v>
+      </c>
+      <c r="D131" t="n">
+        <v>3</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="H131" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="I131" t="n">
+        <v>42</v>
+      </c>
+      <c r="J131" t="n">
+        <v>30.0624278</v>
+      </c>
+      <c r="K131" t="n">
+        <v>-95.5205663</v>
+      </c>
+      <c r="L131" t="n">
+        <v>30.063199</v>
+      </c>
+      <c r="M131" t="n">
+        <v>-95.5209617</v>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S131" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>7</v>
+      </c>
+      <c r="D132" t="n">
+        <v>4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="H132" t="n">
+        <v>42</v>
+      </c>
+      <c r="I132" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>30.063199</v>
+      </c>
+      <c r="K132" t="n">
+        <v>-95.5209617</v>
+      </c>
+      <c r="L132" t="n">
+        <v>30.0629967</v>
+      </c>
+      <c r="M132" t="n">
+        <v>-95.5208117</v>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S132" t="n">
+        <v>-0.252</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>7</v>
+      </c>
+      <c r="D133" t="n">
+        <v>5</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H133" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J133" t="n">
+        <v>30.0629967</v>
+      </c>
+      <c r="K133" t="n">
+        <v>-95.5208117</v>
+      </c>
+      <c r="L133" t="n">
+        <v>30.0628986</v>
+      </c>
+      <c r="M133" t="n">
+        <v>-95.5207776</v>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S133" t="n">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>7</v>
+      </c>
+      <c r="D134" t="n">
+        <v>6</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>30.0628986</v>
+      </c>
+      <c r="K134" t="n">
+        <v>-95.5207776</v>
+      </c>
+      <c r="L134" t="n">
+        <v>30.062893350155</v>
+      </c>
+      <c r="M134" t="n">
+        <v>-95.52077577513001</v>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S134" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>8</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>210.6</v>
+      </c>
+      <c r="H135" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="I135" t="n">
+        <v>209</v>
+      </c>
+      <c r="J135" t="n">
+        <v>30.0642385</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-95.52030310000001</v>
+      </c>
+      <c r="L135" t="n">
+        <v>30.0641607</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-95.5183045</v>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O135" t="n">
+        <v>1</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.232</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>8</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>7 Iron</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="H136" t="n">
+        <v>209</v>
+      </c>
+      <c r="I136" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="J136" t="n">
+        <v>30.0641607</v>
+      </c>
+      <c r="K136" t="n">
+        <v>-95.5183045</v>
+      </c>
+      <c r="L136" t="n">
+        <v>30.0638076</v>
+      </c>
+      <c r="M136" t="n">
+        <v>-95.5173234</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.403</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>8</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>7 Iron</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>137.3</v>
+      </c>
+      <c r="H137" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="I137" t="n">
+        <v>23</v>
+      </c>
+      <c r="J137" t="n">
+        <v>30.0638076</v>
+      </c>
+      <c r="K137" t="n">
+        <v>-95.5173234</v>
+      </c>
+      <c r="L137" t="n">
+        <v>30.06460386</v>
+      </c>
+      <c r="M137" t="n">
+        <v>-95.516398396</v>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>8</v>
+      </c>
+      <c r="D138" t="n">
+        <v>4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H138" t="n">
+        <v>23</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J138" t="n">
+        <v>30.06460386</v>
+      </c>
+      <c r="K138" t="n">
+        <v>-95.516398396</v>
+      </c>
+      <c r="L138" t="n">
+        <v>30.0644332</v>
+      </c>
+      <c r="M138" t="n">
+        <v>-95.51633390000001</v>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="S138" t="n">
+        <v>0.357</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>8</v>
+      </c>
+      <c r="D139" t="n">
+        <v>5</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>30.0644332</v>
+      </c>
+      <c r="K139" t="n">
+        <v>-95.51633390000001</v>
+      </c>
+      <c r="L139" t="n">
+        <v>30.064421115021</v>
+      </c>
+      <c r="M139" t="n">
+        <v>-95.51634137024401</v>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S139" t="n">
+        <v>0.266</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>9</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>261.2</v>
+      </c>
+      <c r="H140" t="n">
+        <v>438.8</v>
+      </c>
+      <c r="I140" t="n">
+        <v>200</v>
+      </c>
+      <c r="J140" t="n">
+        <v>30.0647206</v>
+      </c>
+      <c r="K140" t="n">
+        <v>-95.51505880000001</v>
+      </c>
+      <c r="L140" t="n">
+        <v>30.062578232432</v>
+      </c>
+      <c r="M140" t="n">
+        <v>-95.514882691892</v>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O140" t="n">
+        <v>1</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="S140" t="n">
+        <v>-0.114</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>9</v>
+      </c>
+      <c r="D141" t="n">
+        <v>2</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="H141" t="n">
+        <v>200</v>
+      </c>
+      <c r="I141" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="J141" t="n">
+        <v>30.062578232432</v>
+      </c>
+      <c r="K141" t="n">
+        <v>-95.514882691892</v>
+      </c>
+      <c r="L141" t="n">
+        <v>30.0611914</v>
+      </c>
+      <c r="M141" t="n">
+        <v>-95.5141737</v>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.267</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>9</v>
+      </c>
+      <c r="D142" t="n">
+        <v>3</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>58 Wedge</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="H142" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="I142" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="J142" t="n">
+        <v>30.0611914</v>
+      </c>
+      <c r="K142" t="n">
+        <v>-95.5141737</v>
+      </c>
+      <c r="L142" t="n">
+        <v>30.0611579</v>
+      </c>
+      <c r="M142" t="n">
+        <v>-95.51382719999999</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S142" t="n">
+        <v>-0.454</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>9</v>
+      </c>
+      <c r="D143" t="n">
+        <v>4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="H143" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J143" t="n">
+        <v>30.0611579</v>
+      </c>
+      <c r="K143" t="n">
+        <v>-95.51382719999999</v>
+      </c>
+      <c r="L143" t="n">
+        <v>30.0613182</v>
+      </c>
+      <c r="M143" t="n">
+        <v>-95.5136598</v>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S143" t="n">
+        <v>0.338</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>9</v>
+      </c>
+      <c r="D144" t="n">
+        <v>5</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>30.0613182</v>
+      </c>
+      <c r="K144" t="n">
+        <v>-95.5136598</v>
+      </c>
+      <c r="L144" t="n">
+        <v>30.0613222672</v>
+      </c>
+      <c r="M144" t="n">
+        <v>-95.51365555265799</v>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S144" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>10</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>269.1</v>
+      </c>
+      <c r="H145" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="I145" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="J145" t="n">
+        <v>30.0592576</v>
+      </c>
+      <c r="K145" t="n">
+        <v>-95.5122191</v>
+      </c>
+      <c r="L145" t="n">
+        <v>30.0581218</v>
+      </c>
+      <c r="M145" t="n">
+        <v>-95.5100248</v>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O145" t="n">
+        <v>1</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="S145" t="n">
+        <v>0.117</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>10</v>
+      </c>
+      <c r="D146" t="n">
+        <v>2</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Pitching Wedge</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="H146" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="I146" t="n">
+        <v>39</v>
+      </c>
+      <c r="J146" t="n">
+        <v>30.0581218</v>
+      </c>
+      <c r="K146" t="n">
+        <v>-95.5100248</v>
+      </c>
+      <c r="L146" t="n">
+        <v>30.057934</v>
+      </c>
+      <c r="M146" t="n">
+        <v>-95.5092606</v>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S146" t="n">
+        <v>-0.735</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>10</v>
+      </c>
+      <c r="D147" t="n">
+        <v>3</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>58 Wedge</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="H147" t="n">
+        <v>39</v>
+      </c>
+      <c r="I147" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J147" t="n">
+        <v>30.057934</v>
+      </c>
+      <c r="K147" t="n">
+        <v>-95.5092606</v>
+      </c>
+      <c r="L147" t="n">
+        <v>30.0578238</v>
+      </c>
+      <c r="M147" t="n">
+        <v>-95.5089644</v>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S147" t="n">
+        <v>-0.043</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>10</v>
+      </c>
+      <c r="D148" t="n">
+        <v>4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H148" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J148" t="n">
+        <v>30.0578238</v>
+      </c>
+      <c r="K148" t="n">
+        <v>-95.5089644</v>
+      </c>
+      <c r="L148" t="n">
+        <v>30.0578217</v>
+      </c>
+      <c r="M148" t="n">
+        <v>-95.5089198</v>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S148" t="n">
+        <v>-0.199</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>10</v>
+      </c>
+      <c r="D149" t="n">
+        <v>5</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>30.0578217</v>
+      </c>
+      <c r="K149" t="n">
+        <v>-95.5089198</v>
+      </c>
+      <c r="L149" t="n">
+        <v>30.0578214022</v>
+      </c>
+      <c r="M149" t="n">
+        <v>-95.508913475274</v>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S149" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>11</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>6 Iron</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="H150" t="n">
+        <v>160.4</v>
+      </c>
+      <c r="I150" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="J150" t="n">
+        <v>30.0582509</v>
+      </c>
+      <c r="K150" t="n">
+        <v>-95.50802880000001</v>
+      </c>
+      <c r="L150" t="n">
+        <v>30.058967</v>
+      </c>
+      <c r="M150" t="n">
+        <v>-95.5073623</v>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O150" t="n">
+        <v>1</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S150" t="n">
+        <v>-0.712</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>11</v>
+      </c>
+      <c r="D151" t="n">
+        <v>2</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>58 Wedge</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="H151" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="I151" t="n">
+        <v>5</v>
+      </c>
+      <c r="J151" t="n">
+        <v>30.058967</v>
+      </c>
+      <c r="K151" t="n">
+        <v>-95.5073623</v>
+      </c>
+      <c r="L151" t="n">
+        <v>30.059002097034</v>
+      </c>
+      <c r="M151" t="n">
+        <v>-95.506825732343</v>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S151" t="n">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>11</v>
+      </c>
+      <c r="D152" t="n">
+        <v>3</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H152" t="n">
+        <v>5</v>
+      </c>
+      <c r="I152" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J152" t="n">
+        <v>30.059002097034</v>
+      </c>
+      <c r="K152" t="n">
+        <v>-95.506825732343</v>
+      </c>
+      <c r="L152" t="n">
+        <v>30.059003749542</v>
+      </c>
+      <c r="M152" t="n">
+        <v>-95.506800467771</v>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S152" t="n">
+        <v>-0.644</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>11</v>
+      </c>
+      <c r="D153" t="n">
+        <v>4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H153" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J153" t="n">
+        <v>30.059003749542</v>
+      </c>
+      <c r="K153" t="n">
+        <v>-95.506800467771</v>
+      </c>
+      <c r="L153" t="n">
+        <v>30.059004782357</v>
+      </c>
+      <c r="M153" t="n">
+        <v>-95.50678467741299</v>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S153" t="n">
+        <v>-0.579</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>11</v>
+      </c>
+      <c r="D154" t="n">
+        <v>5</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>30.059004782357</v>
+      </c>
+      <c r="K154" t="n">
+        <v>-95.50678467741299</v>
+      </c>
+      <c r="L154" t="n">
+        <v>30.059005195483</v>
+      </c>
+      <c r="M154" t="n">
+        <v>-95.50677836126999</v>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S154" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>12</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>265.2</v>
+      </c>
+      <c r="H155" t="n">
+        <v>428.4</v>
+      </c>
+      <c r="I155" t="n">
+        <v>205</v>
+      </c>
+      <c r="J155" t="n">
+        <v>30.0586049</v>
+      </c>
+      <c r="K155" t="n">
+        <v>-95.5051462</v>
+      </c>
+      <c r="L155" t="n">
+        <v>30.0601241</v>
+      </c>
+      <c r="M155" t="n">
+        <v>-95.50333860000001</v>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O155" t="n">
+        <v>1</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="S155" t="n">
+        <v>-0.177</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>12</v>
+      </c>
+      <c r="D156" t="n">
+        <v>2</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="H156" t="n">
+        <v>205</v>
+      </c>
+      <c r="I156" t="n">
+        <v>157</v>
+      </c>
+      <c r="J156" t="n">
+        <v>30.0601241</v>
+      </c>
+      <c r="K156" t="n">
+        <v>-95.50333860000001</v>
+      </c>
+      <c r="L156" t="n">
+        <v>30.060517214815</v>
+      </c>
+      <c r="M156" t="n">
+        <v>-95.503373188889</v>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S156" t="n">
+        <v>-0.522</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>12</v>
+      </c>
+      <c r="D157" t="n">
+        <v>3</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>5 Wood</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="H157" t="n">
+        <v>157</v>
+      </c>
+      <c r="I157" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="J157" t="n">
+        <v>30.060517214815</v>
+      </c>
+      <c r="K157" t="n">
+        <v>-95.503373188889</v>
+      </c>
+      <c r="L157" t="n">
+        <v>30.0611584</v>
+      </c>
+      <c r="M157" t="n">
+        <v>-95.5034579</v>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S157" t="n">
+        <v>-0.529</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>12</v>
+      </c>
+      <c r="D158" t="n">
+        <v>4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>58 Wedge</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="H158" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="I158" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="J158" t="n">
+        <v>30.0611584</v>
+      </c>
+      <c r="K158" t="n">
+        <v>-95.5034579</v>
+      </c>
+      <c r="L158" t="n">
+        <v>30.0618265</v>
+      </c>
+      <c r="M158" t="n">
+        <v>-95.5030021</v>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S158" t="n">
+        <v>-0.6870000000000001</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>12</v>
+      </c>
+      <c r="D159" t="n">
+        <v>5</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>50 Wedge</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="H159" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="I159" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J159" t="n">
+        <v>30.0618265</v>
+      </c>
+      <c r="K159" t="n">
+        <v>-95.5030021</v>
+      </c>
+      <c r="L159" t="n">
+        <v>30.0617933</v>
+      </c>
+      <c r="M159" t="n">
+        <v>-95.5034517</v>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S159" t="n">
+        <v>0.579</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>12</v>
+      </c>
+      <c r="D160" t="n">
+        <v>6</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H160" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>30.0617933</v>
+      </c>
+      <c r="K160" t="n">
+        <v>-95.5034517</v>
+      </c>
+      <c r="L160" t="n">
+        <v>30.061806918002</v>
+      </c>
+      <c r="M160" t="n">
+        <v>-95.50344991160399</v>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S160" t="n">
+        <v>0.266</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>13</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="H161" t="n">
+        <v>418.5</v>
+      </c>
+      <c r="I161" t="n">
+        <v>294.3</v>
+      </c>
+      <c r="J161" t="n">
+        <v>30.0620974</v>
+      </c>
+      <c r="K161" t="n">
+        <v>-95.50543209999999</v>
+      </c>
+      <c r="L161" t="n">
+        <v>30.0612803</v>
+      </c>
+      <c r="M161" t="n">
+        <v>-95.50646020000001</v>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O161" t="n">
+        <v>1</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="S161" t="n">
+        <v>-0.737</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>13</v>
+      </c>
+      <c r="D162" t="n">
+        <v>2</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>152.2</v>
+      </c>
+      <c r="H162" t="n">
+        <v>294.3</v>
+      </c>
+      <c r="I162" t="n">
+        <v>142.2</v>
+      </c>
+      <c r="J162" t="n">
+        <v>30.0612803</v>
+      </c>
+      <c r="K162" t="n">
+        <v>-95.50646020000001</v>
+      </c>
+      <c r="L162" t="n">
+        <v>30.0611792</v>
+      </c>
+      <c r="M162" t="n">
+        <v>-95.50790189999999</v>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S162" t="n">
+        <v>-0.038</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>13</v>
+      </c>
+      <c r="D163" t="n">
+        <v>3</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>7 Iron</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>149.8</v>
+      </c>
+      <c r="H163" t="n">
+        <v>142.2</v>
+      </c>
+      <c r="I163" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="J163" t="n">
+        <v>30.0611792</v>
+      </c>
+      <c r="K163" t="n">
+        <v>-95.50790189999999</v>
+      </c>
+      <c r="L163" t="n">
+        <v>30.060955886667</v>
+      </c>
+      <c r="M163" t="n">
+        <v>-95.509301576667</v>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S163" t="n">
+        <v>-0.278</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>13</v>
+      </c>
+      <c r="D164" t="n">
+        <v>4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="H164" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I164" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J164" t="n">
+        <v>30.060955886667</v>
+      </c>
+      <c r="K164" t="n">
+        <v>-95.509301576667</v>
+      </c>
+      <c r="L164" t="n">
+        <v>30.0611547</v>
+      </c>
+      <c r="M164" t="n">
+        <v>-95.5092519</v>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="S164" t="n">
+        <v>0.358</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>13</v>
+      </c>
+      <c r="D165" t="n">
+        <v>5</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J165" t="n">
+        <v>30.0611547</v>
+      </c>
+      <c r="K165" t="n">
+        <v>-95.5092519</v>
+      </c>
+      <c r="L165" t="n">
+        <v>30.061146477376</v>
+      </c>
+      <c r="M165" t="n">
+        <v>-95.509252031399</v>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S165" t="n">
+        <v>-0.747</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>13</v>
+      </c>
+      <c r="D166" t="n">
+        <v>6</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>30.061146477376</v>
+      </c>
+      <c r="K166" t="n">
+        <v>-95.509252031399</v>
+      </c>
+      <c r="L166" t="n">
+        <v>30.061140995627</v>
+      </c>
+      <c r="M166" t="n">
+        <v>-95.509252118997</v>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S166" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>14</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>178.6</v>
+      </c>
+      <c r="H167" t="n">
+        <v>499.2</v>
+      </c>
+      <c r="I167" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="J167" t="n">
+        <v>30.0623639</v>
+      </c>
+      <c r="K167" t="n">
+        <v>-95.5098136</v>
+      </c>
+      <c r="L167" t="n">
+        <v>30.0636755</v>
+      </c>
+      <c r="M167" t="n">
+        <v>-95.5090495</v>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O167" t="n">
+        <v>1</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="S167" t="n">
+        <v>-0.452</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>14</v>
+      </c>
+      <c r="D168" t="n">
+        <v>2</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="H168" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="I168" t="n">
+        <v>299.4</v>
+      </c>
+      <c r="J168" t="n">
+        <v>30.0636755</v>
+      </c>
+      <c r="K168" t="n">
+        <v>-95.5090495</v>
+      </c>
+      <c r="L168" t="n">
+        <v>30.0637801625</v>
+      </c>
+      <c r="M168" t="n">
+        <v>-95.50878413333299</v>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S168" t="n">
+        <v>-0.797</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>14</v>
+      </c>
+      <c r="D169" t="n">
+        <v>3</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>3 Wood</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="H169" t="n">
+        <v>299.4</v>
+      </c>
+      <c r="I169" t="n">
+        <v>186.8</v>
+      </c>
+      <c r="J169" t="n">
+        <v>30.0637801625</v>
+      </c>
+      <c r="K169" t="n">
+        <v>-95.50878413333299</v>
+      </c>
+      <c r="L169" t="n">
+        <v>30.0646632</v>
+      </c>
+      <c r="M169" t="n">
+        <v>-95.5082294</v>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S169" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>14</v>
+      </c>
+      <c r="D170" t="n">
+        <v>4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>170.8</v>
+      </c>
+      <c r="H170" t="n">
+        <v>186.8</v>
+      </c>
+      <c r="I170" t="n">
+        <v>41</v>
+      </c>
+      <c r="J170" t="n">
+        <v>30.0646632</v>
+      </c>
+      <c r="K170" t="n">
+        <v>-95.5082294</v>
+      </c>
+      <c r="L170" t="n">
+        <v>30.0656437</v>
+      </c>
+      <c r="M170" t="n">
+        <v>-95.5070678</v>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S170" t="n">
+        <v>-0.259</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>14</v>
+      </c>
+      <c r="D171" t="n">
+        <v>5</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="H171" t="n">
+        <v>41</v>
+      </c>
+      <c r="I171" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J171" t="n">
+        <v>30.0656437</v>
+      </c>
+      <c r="K171" t="n">
+        <v>-95.5070678</v>
+      </c>
+      <c r="L171" t="n">
+        <v>30.065487196414</v>
+      </c>
+      <c r="M171" t="n">
+        <v>-95.506740723962</v>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>0</v>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S171" t="n">
+        <v>0.523</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>14</v>
+      </c>
+      <c r="D172" t="n">
+        <v>6</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H172" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>30.065487196414</v>
+      </c>
+      <c r="K172" t="n">
+        <v>-95.506740723962</v>
+      </c>
+      <c r="L172" t="n">
+        <v>30.065480564849</v>
+      </c>
+      <c r="M172" t="n">
+        <v>-95.506726864749</v>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>0</v>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S172" t="n">
+        <v>0.266</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>15</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="H173" t="n">
+        <v>370</v>
+      </c>
+      <c r="I173" t="n">
+        <v>271.8</v>
+      </c>
+      <c r="J173" t="n">
+        <v>30.0661751</v>
+      </c>
+      <c r="K173" t="n">
+        <v>-95.5074382</v>
+      </c>
+      <c r="L173" t="n">
+        <v>30.0656156</v>
+      </c>
+      <c r="M173" t="n">
+        <v>-95.50813890000001</v>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O173" t="n">
+        <v>1</v>
+      </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="S173" t="n">
+        <v>-0.705</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>15</v>
+      </c>
+      <c r="D174" t="n">
+        <v>2</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="H174" t="n">
+        <v>271.8</v>
+      </c>
+      <c r="I174" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="J174" t="n">
+        <v>30.0656156</v>
+      </c>
+      <c r="K174" t="n">
+        <v>-95.50813890000001</v>
+      </c>
+      <c r="L174" t="n">
+        <v>30.0644833</v>
+      </c>
+      <c r="M174" t="n">
+        <v>-95.5092935</v>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>0</v>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S174" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>15</v>
+      </c>
+      <c r="D175" t="n">
+        <v>3</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Pitching Wedge</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="H175" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="I175" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J175" t="n">
+        <v>30.0644833</v>
+      </c>
+      <c r="K175" t="n">
+        <v>-95.5092935</v>
+      </c>
+      <c r="L175" t="n">
+        <v>30.063825</v>
+      </c>
+      <c r="M175" t="n">
+        <v>-95.5095712</v>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>0</v>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S175" t="n">
+        <v>0.051</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>15</v>
+      </c>
+      <c r="D176" t="n">
+        <v>4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H176" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J176" t="n">
+        <v>30.063825</v>
+      </c>
+      <c r="K176" t="n">
+        <v>-95.5095712</v>
+      </c>
+      <c r="L176" t="n">
+        <v>30.0637572</v>
+      </c>
+      <c r="M176" t="n">
+        <v>-95.50956480000001</v>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>0</v>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S176" t="n">
+        <v>-0.064</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>15</v>
+      </c>
+      <c r="D177" t="n">
+        <v>5</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>30.0637572</v>
+      </c>
+      <c r="K177" t="n">
+        <v>-95.50956480000001</v>
+      </c>
+      <c r="L177" t="n">
+        <v>30.063751735931</v>
+      </c>
+      <c r="M177" t="n">
+        <v>-95.509564284218</v>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>0</v>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S177" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>16</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>8 Iron</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>170.8</v>
+      </c>
+      <c r="H178" t="n">
+        <v>166.6</v>
+      </c>
+      <c r="I178" t="n">
+        <v>5</v>
+      </c>
+      <c r="J178" t="n">
+        <v>30.0652784</v>
+      </c>
+      <c r="K178" t="n">
+        <v>-95.5099881</v>
+      </c>
+      <c r="L178" t="n">
+        <v>30.0666519</v>
+      </c>
+      <c r="M178" t="n">
+        <v>-95.51032720000001</v>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O178" t="n">
+        <v>1</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>0</v>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S178" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>16</v>
+      </c>
+      <c r="D179" t="n">
+        <v>2</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H179" t="n">
+        <v>5</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J179" t="n">
+        <v>30.0666519</v>
+      </c>
+      <c r="K179" t="n">
+        <v>-95.51032720000001</v>
+      </c>
+      <c r="L179" t="n">
+        <v>30.066618322906</v>
+      </c>
+      <c r="M179" t="n">
+        <v>-95.510340989257</v>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>0</v>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S179" t="n">
+        <v>-0.223</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>16</v>
+      </c>
+      <c r="D180" t="n">
+        <v>3</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>30.066618322906</v>
+      </c>
+      <c r="K180" t="n">
+        <v>-95.510340989257</v>
+      </c>
+      <c r="L180" t="n">
+        <v>30.066613157199</v>
+      </c>
+      <c r="M180" t="n">
+        <v>-95.51034311068101</v>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S180" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>17</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>236</v>
+      </c>
+      <c r="H181" t="n">
+        <v>271.9</v>
+      </c>
+      <c r="I181" t="n">
+        <v>129.1</v>
+      </c>
+      <c r="J181" t="n">
+        <v>30.0661919</v>
+      </c>
+      <c r="K181" t="n">
+        <v>-95.5118746</v>
+      </c>
+      <c r="L181" t="n">
+        <v>30.0643092</v>
+      </c>
+      <c r="M181" t="n">
+        <v>-95.5124199</v>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O181" t="n">
+        <v>1</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>0</v>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="S181" t="n">
+        <v>-0.308</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>17</v>
+      </c>
+      <c r="D182" t="n">
+        <v>2</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>9 Iron</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="H182" t="n">
+        <v>129.1</v>
+      </c>
+      <c r="I182" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="J182" t="n">
+        <v>30.0643092</v>
+      </c>
+      <c r="K182" t="n">
+        <v>-95.5124199</v>
+      </c>
+      <c r="L182" t="n">
+        <v>30.0641973</v>
+      </c>
+      <c r="M182" t="n">
+        <v>-95.5112342</v>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S182" t="n">
+        <v>-0.126</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>17</v>
+      </c>
+      <c r="D183" t="n">
+        <v>3</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="H183" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J183" t="n">
+        <v>30.0641973</v>
+      </c>
+      <c r="K183" t="n">
+        <v>-95.5112342</v>
+      </c>
+      <c r="L183" t="n">
+        <v>30.064030632069</v>
+      </c>
+      <c r="M183" t="n">
+        <v>-95.511237596616</v>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>0</v>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S183" t="n">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>17</v>
+      </c>
+      <c r="D184" t="n">
+        <v>4</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="n">
+        <v>30.064030632069</v>
+      </c>
+      <c r="K184" t="n">
+        <v>-95.511237596616</v>
+      </c>
+      <c r="L184" t="n">
+        <v>30.064025150648</v>
+      </c>
+      <c r="M184" t="n">
+        <v>-95.511237708325</v>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>0</v>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S184" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>18</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>230.6</v>
+      </c>
+      <c r="H185" t="n">
+        <v>418.9</v>
+      </c>
+      <c r="I185" t="n">
+        <v>190.9</v>
+      </c>
+      <c r="J185" t="n">
+        <v>30.063719190722</v>
+      </c>
+      <c r="K185" t="n">
+        <v>-95.510024776289</v>
+      </c>
+      <c r="L185" t="n">
+        <v>30.0621145</v>
+      </c>
+      <c r="M185" t="n">
+        <v>-95.51119199999999</v>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="O185" t="n">
+        <v>1</v>
+      </c>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="S185" t="n">
+        <v>-0.122</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>18</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>124.6</v>
+      </c>
+      <c r="H186" t="n">
+        <v>190.9</v>
+      </c>
+      <c r="I186" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="J186" t="n">
+        <v>30.0621145</v>
+      </c>
+      <c r="K186" t="n">
+        <v>-95.51119199999999</v>
+      </c>
+      <c r="L186" t="n">
+        <v>30.0611149</v>
+      </c>
+      <c r="M186" t="n">
+        <v>-95.5114501</v>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>0</v>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S186" t="n">
+        <v>-0.348</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>18</v>
+      </c>
+      <c r="D187" t="n">
+        <v>3</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>58 Wedge</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="H187" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="I187" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="J187" t="n">
+        <v>30.0611149</v>
+      </c>
+      <c r="K187" t="n">
+        <v>-95.5114501</v>
+      </c>
+      <c r="L187" t="n">
+        <v>30.0609215</v>
+      </c>
+      <c r="M187" t="n">
+        <v>-95.51171859999999</v>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>0</v>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S187" t="n">
+        <v>-0.639</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>18</v>
+      </c>
+      <c r="D188" t="n">
+        <v>4</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>58 Wedge</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="H188" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I188" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="J188" t="n">
+        <v>30.0609215</v>
+      </c>
+      <c r="K188" t="n">
+        <v>-95.51171859999999</v>
+      </c>
+      <c r="L188" t="n">
+        <v>30.0607386</v>
+      </c>
+      <c r="M188" t="n">
+        <v>-95.51170639999999</v>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>0</v>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="S188" t="n">
+        <v>-0.367</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>18</v>
+      </c>
+      <c r="D189" t="n">
+        <v>5</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H189" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J189" t="n">
+        <v>30.0607386</v>
+      </c>
+      <c r="K189" t="n">
+        <v>-95.51170639999999</v>
+      </c>
+      <c r="L189" t="n">
+        <v>30.0606392</v>
+      </c>
+      <c r="M189" t="n">
+        <v>-95.511793</v>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>0</v>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S189" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>18</v>
+      </c>
+      <c r="D190" t="n">
+        <v>6</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>30.0606392</v>
+      </c>
+      <c r="K190" t="n">
+        <v>-95.511793</v>
+      </c>
+      <c r="L190" t="n">
+        <v>30.060634822692</v>
+      </c>
+      <c r="M190" t="n">
+        <v>-95.51179681363099</v>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>0</v>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="S190" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -9473,32 +17701,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>262.8</v>
+        <v>263.8</v>
       </c>
       <c r="F2" t="n">
-        <v>262.8</v>
+        <v>263.8</v>
       </c>
       <c r="G2" t="n">
-        <v>266.8</v>
+        <v>268.1</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>270.4</v>
+        <v>285.2</v>
       </c>
       <c r="L2" t="n">
-        <v>257.023</v>
+        <v>262.253</v>
       </c>
       <c r="M2" t="n">
-        <v>267.043</v>
+        <v>269.271</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -9523,33 +17751,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>203.7</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+        <v>229</v>
+      </c>
+      <c r="F3" t="n">
+        <v>229</v>
+      </c>
+      <c r="G3" t="n">
+        <v>239</v>
+      </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>122</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
         <v>239.8</v>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>225.476</v>
+      </c>
+      <c r="M3" t="n">
+        <v>238.387</v>
+      </c>
+      <c r="N3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5 Wood</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9563,31 +17805,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>184</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>207.4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>207.4</v>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>220.5</v>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>220.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>220.471</v>
+      </c>
+      <c r="M4" t="n">
+        <v>220.471</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>5 Wood</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9601,26 +17857,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>172.9</v>
+        <v>203.2</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>141.5</v>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7 Iron</t>
+          <t>6 Iron</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9639,44 +17899,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>155.8</v>
+        <v>158.4</v>
       </c>
       <c r="F6" t="n">
-        <v>155.8</v>
-      </c>
-      <c r="G6" t="n">
-        <v>161.9</v>
-      </c>
+        <v>158.4</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>151.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>126.7</v>
-      </c>
+        <v>160.3</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>161.9</v>
+        <v>160.3</v>
       </c>
       <c r="L6" t="n">
-        <v>149.003</v>
+        <v>160.338</v>
       </c>
       <c r="M6" t="n">
-        <v>156.705</v>
+        <v>160.338</v>
       </c>
       <c r="N6" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O6" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6 Iron</t>
+          <t>5 Iron</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -9695,28 +17949,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>143.7</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+        <v>155.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H7" t="n">
+        <v>160</v>
+      </c>
+      <c r="I7" t="n">
+        <v>172</v>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>160.3</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+        <v>184</v>
+      </c>
+      <c r="L7" t="n">
+        <v>152.576</v>
+      </c>
+      <c r="M7" t="n">
+        <v>170.43</v>
+      </c>
+      <c r="N7" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>16.7</v>
+      </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8 Iron</t>
+          <t>7 Iron</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -9735,30 +18005,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>133.6</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+        <v>149</v>
+      </c>
+      <c r="F8" t="n">
+        <v>149</v>
+      </c>
+      <c r="G8" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>151.1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>134.1</v>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>121.1</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+        <v>161.9</v>
+      </c>
+      <c r="L8" t="n">
+        <v>147.497</v>
+      </c>
+      <c r="M8" t="n">
+        <v>151.478</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4</v>
+      </c>
       <c r="O8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5 Iron</t>
+          <t>8 Iron</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -9777,36 +18061,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>126.2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>126.2</v>
-      </c>
+        <v>140.5</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="I9" t="n">
-        <v>106.6</v>
-      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>153.5</v>
-      </c>
-      <c r="L9" t="n">
-        <v>117.015</v>
-      </c>
-      <c r="M9" t="n">
-        <v>136.906</v>
-      </c>
-      <c r="N9" t="n">
-        <v>19.9</v>
-      </c>
+        <v>170.3</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="P9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -9831,24 +18103,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>122</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+        <v>137</v>
+      </c>
+      <c r="F10" t="n">
+        <v>137</v>
+      </c>
+      <c r="G10" t="n">
+        <v>127.9</v>
+      </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>144.1</v>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>146.1</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+        <v>152</v>
+      </c>
+      <c r="L10" t="n">
+        <v>132.87</v>
+      </c>
+      <c r="M10" t="n">
+        <v>147.537</v>
+      </c>
+      <c r="N10" t="n">
+        <v>14.7</v>
+      </c>
       <c r="O10" t="n">
         <v>50</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -9873,32 +18157,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>108.1</v>
+        <v>111.7</v>
       </c>
       <c r="F11" t="n">
-        <v>108.1</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
+        <v>111.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>131.2</v>
+      </c>
       <c r="H11" t="n">
         <v>112.2</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>85</v>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>112.2</v>
+        <v>131.2</v>
       </c>
       <c r="L11" t="n">
-        <v>112.163</v>
+        <v>109.448</v>
       </c>
       <c r="M11" t="n">
-        <v>112.163</v>
+        <v>121.677</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
+        <v>12.2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>100</v>
+      </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -9952,13 +18242,13 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>54 Wedge</t>
+          <t>58 Wedge</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -9977,26 +18267,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>88.8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>88.8</v>
+      </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>71.3</v>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>79.5625</v>
+      </c>
+      <c r="M13" t="n">
+        <v>90.8301</v>
+      </c>
+      <c r="N13" t="n">
+        <v>11.3</v>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>58 Wedge</t>
+          <t>54 Wedge</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -10015,32 +18319,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>80.7</v>
+        <v>72.2</v>
       </c>
       <c r="F14" t="n">
-        <v>80.7</v>
+        <v>72.2</v>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>59.2</v>
+      </c>
       <c r="I14" t="n">
-        <v>81.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>90.8</v>
+        <v>102.4</v>
       </c>
       <c r="L14" t="n">
-        <v>72.9575</v>
+        <v>67.6871</v>
       </c>
       <c r="M14" t="n">
-        <v>82.7062</v>
+        <v>85.49679999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
+        <v>17.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>100</v>
+      </c>
       <c r="P14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -10054,7 +18362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10105,24 +18413,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-18.0783</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-18.7461</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-27.3459</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-18.5154</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-2.47542</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-8.83972</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>27924130</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B3" t="n">
         <v>-20.4148</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C3" t="n">
         <v>-7.49223</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
         <v>-30</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>-30</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F3" t="n">
         <v>-4.95085</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G3" t="n">
         <v>-10.2852</v>
       </c>
     </row>
@@ -10169,7 +18500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-23.7</v>
+        <v>-21.9</v>
       </c>
     </row>
     <row r="5">
@@ -10179,7 +18510,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.2</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="6">
@@ -10189,7 +18520,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-14.6</v>
+        <v>-12.1</v>
       </c>
     </row>
     <row r="7">
@@ -10199,7 +18530,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-6.1</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="8">
@@ -10209,7 +18540,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.8</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="9">
@@ -10230,7 +18561,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>64.3</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="12">
@@ -10260,7 +18591,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11.1</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="15">
@@ -10300,7 +18631,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.6</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="19">
@@ -10310,7 +18641,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -10338,7 +18669,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -10348,7 +18679,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -10358,7 +18689,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -10368,7 +18699,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
@@ -10388,7 +18719,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -10408,7 +18739,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -10418,7 +18749,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3035.27</v>
+        <v>5593.9</v>
       </c>
     </row>
     <row r="32">
@@ -10428,7 +18759,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>247.29</v>
+        <v>260.8</v>
       </c>
     </row>
     <row r="33">
@@ -10438,7 +18769,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34">
@@ -10448,7 +18779,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35">
@@ -10458,7 +18789,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28.86</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="36">
@@ -10478,7 +18809,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -10488,7 +18819,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -10498,7 +18829,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
@@ -10508,7 +18839,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>64.45999999999999</v>
+        <v>795.7</v>
       </c>
     </row>
     <row r="41">
@@ -10518,7 +18849,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>35.59</v>
+        <v>167.78</v>
       </c>
     </row>
     <row r="42">
@@ -10528,7 +18859,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.36</v>
+        <v>51.63</v>
       </c>
     </row>
     <row r="43">
@@ -10538,7 +18869,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-7.49</v>
+        <v>-18.75</v>
       </c>
     </row>
     <row r="44">
@@ -10615,7 +18946,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
@@ -10625,7 +18956,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53">
@@ -10635,7 +18966,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54">
@@ -10645,7 +18976,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
@@ -10675,7 +19006,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -10685,7 +19016,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
@@ -10695,7 +19026,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60">
@@ -10705,7 +19036,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>96</v>
+        <v>188</v>
       </c>
     </row>
     <row r="61">
@@ -10715,7 +19046,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>816.3099999999999</v>
+        <v>1862.75</v>
       </c>
     </row>
     <row r="62">
@@ -10725,7 +19056,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>115.97</v>
+        <v>227.14</v>
       </c>
     </row>
     <row r="63">
@@ -10735,7 +19066,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>73.01000000000001</v>
+        <v>147.79</v>
       </c>
     </row>
     <row r="64">
@@ -10745,7 +19076,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -10755,7 +19086,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-30</v>
+        <v>-27.35</v>
       </c>
     </row>
     <row r="66">
@@ -10782,7 +19113,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -10812,7 +19143,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -10822,7 +19153,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73">
@@ -10842,7 +19173,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75">
@@ -10852,7 +19183,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -10862,7 +19193,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77">
@@ -10882,7 +19213,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79">
@@ -10892,7 +19223,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
     </row>
     <row r="80">
@@ -10902,7 +19233,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>101.19</v>
+        <v>203</v>
       </c>
     </row>
     <row r="81">
@@ -10912,7 +19243,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>79.17</v>
+        <v>160.81</v>
       </c>
     </row>
     <row r="82">
@@ -10922,7 +19253,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>65.29000000000001</v>
+        <v>146.93</v>
       </c>
     </row>
     <row r="83">
@@ -10932,7 +19263,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1.83</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="84">
@@ -11012,7 +19343,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-30</v>
+        <v>-18.52</v>
       </c>
     </row>
     <row r="92">
@@ -11269,7 +19600,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-4.95</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="118">
@@ -11296,7 +19627,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121">
@@ -11306,7 +19637,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122">
@@ -11316,7 +19647,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123">
@@ -11326,7 +19657,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>38</v>
+        <v>74</v>
       </c>
     </row>
     <row r="124">
@@ -11336,7 +19667,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="125">
@@ -11346,7 +19677,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="126">
@@ -11356,7 +19687,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127">
@@ -11386,7 +19717,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-3.1</v>
+        <v>-5.67</v>
       </c>
     </row>
     <row r="130">
@@ -11396,7 +19727,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-10.29</v>
+        <v>-8.84</v>
       </c>
     </row>
     <row r="131">
@@ -11433,7 +19764,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135">
@@ -11443,7 +19774,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="136">
@@ -11453,7 +19784,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="137">
@@ -11463,7 +19794,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138">
@@ -11473,7 +19804,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="139">
@@ -11483,7 +19814,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140">
@@ -11493,7 +19824,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>51</v>
+        <v>105</v>
       </c>
     </row>
     <row r="141">
@@ -11503,7 +19834,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142">
@@ -11513,7 +19844,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
     <row r="143">
@@ -11523,7 +19854,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="144">
@@ -11533,7 +19864,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-20.41</v>
+        <v>-18.08</v>
       </c>
     </row>
   </sheetData>
@@ -11568,7 +19899,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -11579,7 +19910,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18 / 95</t>
+          <t>36 / 189</t>
         </is>
       </c>
     </row>
@@ -11591,7 +19922,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-06 -&gt; 2026-06-06</t>
+          <t>2026-06-06 -&gt; 2026-06-14</t>
         </is>
       </c>
     </row>
@@ -11614,7 +19945,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -11624,7 +19955,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -11634,7 +19965,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-23.7</v>
+        <v>-21.9</v>
       </c>
     </row>
     <row r="10">
@@ -11644,7 +19975,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.2</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="11">
@@ -11654,7 +19985,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-14.6</v>
+        <v>-12.15</v>
       </c>
     </row>
     <row r="12">
@@ -11664,7 +19995,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>-6.1</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="13">
@@ -11674,7 +20005,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1.8</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="14">
@@ -11684,7 +20015,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-22.76</v>
+        <v>-20.52</v>
       </c>
     </row>
     <row r="15">
@@ -11704,7 +20035,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>64.3</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="17">
@@ -11724,7 +20055,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>12</v>
+        <v>11.15</v>
       </c>
     </row>
     <row r="19">
@@ -11734,7 +20065,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -11744,7 +20075,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -11764,7 +20095,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="23">
@@ -11774,7 +20105,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>237.3</v>
+        <v>218.7</v>
       </c>
     </row>
     <row r="24">
@@ -11784,7 +20115,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>269.9</v>
+        <v>277.75</v>
       </c>
     </row>
     <row r="25">
@@ -11794,7 +20125,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26">
@@ -11804,7 +20135,7 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>-30</v>
+        <v>-24.26</v>
       </c>
     </row>
     <row r="27">
@@ -11814,7 +20145,7 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>-4.95</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="29">
@@ -11846,7 +20177,7 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>11.1</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="32">
@@ -11886,7 +20217,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>64.3</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="36">
@@ -11906,7 +20237,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5.6</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="38">
@@ -11916,7 +20247,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40">
@@ -11943,7 +20274,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-14 12:00 UTC  |  Rounds: 1  Shots: 95</t>
+          <t>Date pulled: 2026-06-14 18:21 UTC  |  Rounds: 2  Shots: 189</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT3"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -494,6 +494,11 @@
     <col width="10" customWidth="1" min="44" max="44"/>
     <col width="10" customWidth="1" min="45" max="45"/>
     <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="10" customWidth="1" min="47" max="47"/>
+    <col width="10" customWidth="1" min="48" max="48"/>
+    <col width="14" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="10" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -727,6 +732,31 @@
           <t>putt_hcp</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>temp_f</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>wind_mph</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>wind_dir_deg</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>wind_dir</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -875,6 +905,25 @@
       <c r="AT2" t="n">
         <v>-10.2852</v>
       </c>
+      <c r="AU2" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>109</v>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Drizzle</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1022,6 +1071,25 @@
       </c>
       <c r="AT3" t="n">
         <v>-8.83972</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>129</v>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Drizzle</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -20274,7 +20342,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-14 18:21 UTC  |  Rounds: 2  Shots: 189</t>
+          <t>Date pulled: 2026-06-14 21:32 UTC  |  Rounds: 2  Shots: 189</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -4471,7 +4471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S190"/>
+  <dimension ref="A1:V190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4487,12 +4487,15 @@
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="17" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4563,30 +4566,45 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>start_alt</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>end_alt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>is_half_swing</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>lie_approx</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>is_tee</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>is_putt</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>penalties</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>category_approx</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>sg_shot_approx</t>
         </is>
@@ -4638,26 +4656,31 @@
       <c r="M2" t="n">
         <v>-95.5124879</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>-0.133</v>
       </c>
     </row>
@@ -4707,26 +4730,31 @@
       <c r="M3" t="n">
         <v>-95.51235511929799</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
         <v>-0.638</v>
       </c>
     </row>
@@ -4776,26 +4804,31 @@
       <c r="M4" t="n">
         <v>-95.512136</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="V4" t="n">
         <v>-0.313</v>
       </c>
     </row>
@@ -4845,26 +4878,31 @@
       <c r="M5" t="n">
         <v>-95.5119237</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="S5" t="n">
+      <c r="V5" t="n">
         <v>0.37</v>
       </c>
     </row>
@@ -4914,26 +4952,31 @@
       <c r="M6" t="n">
         <v>-95.511914248564</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
         <v>-0.747</v>
       </c>
     </row>
@@ -4983,26 +5026,31 @@
       <c r="M7" t="n">
         <v>-95.511907947607</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -5052,26 +5100,31 @@
       <c r="M8" t="n">
         <v>-95.5142113</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="V8" t="n">
         <v>-0.405</v>
       </c>
     </row>
@@ -5121,26 +5174,31 @@
       <c r="M9" t="n">
         <v>-95.51430488106701</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S9" t="n">
+      <c r="V9" t="n">
         <v>-0.055</v>
       </c>
     </row>
@@ -5190,26 +5248,31 @@
       <c r="M10" t="n">
         <v>-95.5143126</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="V10" t="n">
         <v>-0.579</v>
       </c>
     </row>
@@ -5259,26 +5322,31 @@
       <c r="M11" t="n">
         <v>-95.51431251885499</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="V11" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -5328,26 +5396,31 @@
       <c r="M12" t="n">
         <v>-95.51601782441099</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S12" t="n">
+      <c r="V12" t="n">
         <v>0.036</v>
       </c>
     </row>
@@ -5397,26 +5470,31 @@
       <c r="M13" t="n">
         <v>-95.51692970000001</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S13" t="n">
+      <c r="V13" t="n">
         <v>-0.757</v>
       </c>
     </row>
@@ -5466,26 +5544,31 @@
       <c r="M14" t="n">
         <v>-95.5166495</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
         <v>-0.041</v>
       </c>
     </row>
@@ -5535,26 +5618,31 @@
       <c r="M15" t="n">
         <v>-95.5166747</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="inlineStr">
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S15" t="n">
+      <c r="V15" t="n">
         <v>-0.299</v>
       </c>
     </row>
@@ -5604,26 +5692,31 @@
       <c r="M16" t="n">
         <v>-95.516679530392</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S16" t="n">
+      <c r="V16" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -5673,26 +5766,31 @@
       <c r="M17" t="n">
         <v>-95.515391863883</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="inlineStr">
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S17" t="n">
+      <c r="V17" t="n">
         <v>-0.152</v>
       </c>
     </row>
@@ -5742,26 +5840,31 @@
       <c r="M18" t="n">
         <v>-95.5152205</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S18" t="n">
+      <c r="V18" t="n">
         <v>-0.472</v>
       </c>
     </row>
@@ -5811,26 +5914,31 @@
       <c r="M19" t="n">
         <v>-95.51501140000001</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S19" t="n">
+      <c r="V19" t="n">
         <v>-0.017</v>
       </c>
     </row>
@@ -5880,26 +5988,31 @@
       <c r="M20" t="n">
         <v>-95.515034078214</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S20" t="n">
+      <c r="V20" t="n">
         <v>-0.038</v>
       </c>
     </row>
@@ -5949,26 +6062,31 @@
       <c r="M21" t="n">
         <v>-95.51503606089101</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="inlineStr">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S21" t="n">
+      <c r="V21" t="n">
         <v>0.357</v>
       </c>
     </row>
@@ -6018,26 +6136,31 @@
       <c r="M22" t="n">
         <v>-95.5167184</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="inlineStr">
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S22" t="n">
+      <c r="V22" t="n">
         <v>-0.277</v>
       </c>
     </row>
@@ -6087,26 +6210,31 @@
       <c r="M23" t="n">
         <v>-95.51702590588199</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="inlineStr">
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S23" t="n">
+      <c r="V23" t="n">
         <v>-0.577</v>
       </c>
     </row>
@@ -6156,26 +6284,31 @@
       <c r="M24" t="n">
         <v>-95.5184067</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="inlineStr">
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S24" t="n">
+      <c r="V24" t="n">
         <v>-0.114</v>
       </c>
     </row>
@@ -6225,26 +6358,31 @@
       <c r="M25" t="n">
         <v>-95.51832570000001</v>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="S25" t="n">
+      <c r="V25" t="n">
         <v>-0.17</v>
       </c>
     </row>
@@ -6294,26 +6432,31 @@
       <c r="M26" t="n">
         <v>-95.518298876389</v>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S26" t="n">
+      <c r="V26" t="n">
         <v>-0.341</v>
       </c>
     </row>
@@ -6363,26 +6506,31 @@
       <c r="M27" t="n">
         <v>-95.51829300953101</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="inlineStr">
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S27" t="n">
+      <c r="V27" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -6432,26 +6580,31 @@
       <c r="M28" t="n">
         <v>-95.5182464</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O28" t="n">
-        <v>1</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S28" t="n">
+      <c r="V28" t="n">
         <v>-0.777</v>
       </c>
     </row>
@@ -6501,26 +6654,31 @@
       <c r="M29" t="n">
         <v>-95.518252538889</v>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="inlineStr">
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S29" t="n">
+      <c r="V29" t="n">
         <v>-0.731</v>
       </c>
     </row>
@@ -6570,26 +6728,31 @@
       <c r="M30" t="n">
         <v>-95.5186757</v>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="inlineStr">
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S30" t="n">
+      <c r="V30" t="n">
         <v>-0.596</v>
       </c>
     </row>
@@ -6639,26 +6802,31 @@
       <c r="M31" t="n">
         <v>-95.51867470000001</v>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="inlineStr">
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="S31" t="n">
+      <c r="V31" t="n">
         <v>-0.554</v>
       </c>
     </row>
@@ -6708,26 +6876,31 @@
       <c r="M32" t="n">
         <v>-95.51867372</v>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="inlineStr">
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="S32" t="n">
+      <c r="V32" t="n">
         <v>-0.641</v>
       </c>
     </row>
@@ -6777,26 +6950,31 @@
       <c r="M33" t="n">
         <v>-95.518653507599</v>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="inlineStr">
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S33" t="n">
+      <c r="V33" t="n">
         <v>0.048</v>
       </c>
     </row>
@@ -6846,26 +7024,31 @@
       <c r="M34" t="n">
         <v>-95.518652466506</v>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="inlineStr">
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S34" t="n">
+      <c r="V34" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -6915,26 +7098,31 @@
       <c r="M35" t="n">
         <v>-95.520282201469</v>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O35" t="n">
-        <v>1</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="inlineStr">
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S35" t="n">
+      <c r="V35" t="n">
         <v>-0.008999999999999999</v>
       </c>
     </row>
@@ -6984,26 +7172,31 @@
       <c r="M36" t="n">
         <v>-95.52047899999999</v>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="inlineStr">
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S36" t="n">
+      <c r="V36" t="n">
         <v>-0.6889999999999999</v>
       </c>
     </row>
@@ -7053,26 +7246,31 @@
       <c r="M37" t="n">
         <v>-95.5205643</v>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="inlineStr">
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="S37" t="n">
+      <c r="V37" t="n">
         <v>-0.414</v>
       </c>
     </row>
@@ -7122,26 +7320,31 @@
       <c r="M38" t="n">
         <v>-95.5206398</v>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="inlineStr">
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S38" t="n">
+      <c r="V38" t="n">
         <v>-0.067</v>
       </c>
     </row>
@@ -7191,26 +7394,31 @@
       <c r="M39" t="n">
         <v>-95.520645989927</v>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="inlineStr">
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S39" t="n">
+      <c r="V39" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -7260,26 +7468,31 @@
       <c r="M40" t="n">
         <v>-95.51730662584301</v>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O40" t="n">
-        <v>1</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="inlineStr">
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S40" t="n">
+      <c r="V40" t="n">
         <v>0.107</v>
       </c>
     </row>
@@ -7329,26 +7542,31 @@
       <c r="M41" t="n">
         <v>-95.51622860000001</v>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="inlineStr">
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S41" t="n">
+      <c r="V41" t="n">
         <v>-0.249</v>
       </c>
     </row>
@@ -7398,26 +7616,31 @@
       <c r="M42" t="n">
         <v>-95.516314695745</v>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="inlineStr">
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S42" t="n">
+      <c r="V42" t="n">
         <v>0.078</v>
       </c>
     </row>
@@ -7467,26 +7690,31 @@
       <c r="M43" t="n">
         <v>-95.516318717817</v>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="inlineStr">
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S43" t="n">
+      <c r="V43" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -7536,26 +7764,31 @@
       <c r="M44" t="n">
         <v>-95.514417551458</v>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O44" t="n">
-        <v>1</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="inlineStr">
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S44" t="n">
+      <c r="V44" t="n">
         <v>-0.078</v>
       </c>
     </row>
@@ -7605,26 +7838,31 @@
       <c r="M45" t="n">
         <v>-95.5138019</v>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="inlineStr">
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S45" t="n">
+      <c r="V45" t="n">
         <v>-0.726</v>
       </c>
     </row>
@@ -7674,26 +7912,31 @@
       <c r="M46" t="n">
         <v>-95.5140202</v>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="inlineStr">
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S46" t="n">
+      <c r="V46" t="n">
         <v>-0.526</v>
       </c>
     </row>
@@ -7743,26 +7986,31 @@
       <c r="M47" t="n">
         <v>-95.513674477778</v>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="inlineStr">
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S47" t="n">
+      <c r="V47" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -7812,26 +8060,31 @@
       <c r="M48" t="n">
         <v>-95.513685505143</v>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="inlineStr">
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S48" t="n">
+      <c r="V48" t="n">
         <v>-0.211</v>
       </c>
     </row>
@@ -7881,26 +8134,31 @@
       <c r="M49" t="n">
         <v>-95.513687119046</v>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="inlineStr">
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S49" t="n">
+      <c r="V49" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -7950,26 +8208,31 @@
       <c r="M50" t="n">
         <v>-95.5095563</v>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O50" t="n">
-        <v>1</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="inlineStr">
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S50" t="n">
+      <c r="V50" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -8019,26 +8282,31 @@
       <c r="M51" t="n">
         <v>-95.50930940000001</v>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="inlineStr">
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S51" t="n">
+      <c r="V51" t="n">
         <v>-0.638</v>
       </c>
     </row>
@@ -8088,26 +8356,31 @@
       <c r="M52" t="n">
         <v>-95.5087817</v>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="inlineStr">
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S52" t="n">
+      <c r="V52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -8157,26 +8430,31 @@
       <c r="M53" t="n">
         <v>-95.508889276307</v>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="inlineStr">
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S53" t="n">
+      <c r="V53" t="n">
         <v>0.035</v>
       </c>
     </row>
@@ -8226,26 +8504,31 @@
       <c r="M54" t="n">
         <v>-95.508897378239</v>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="inlineStr">
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S54" t="n">
+      <c r="V54" t="n">
         <v>0.266</v>
       </c>
     </row>
@@ -8295,26 +8578,31 @@
       <c r="M55" t="n">
         <v>-95.5071447</v>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O55" t="n">
-        <v>1</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="inlineStr">
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S55" t="n">
+      <c r="V55" t="n">
         <v>-0.48</v>
       </c>
     </row>
@@ -8364,26 +8652,31 @@
       <c r="M56" t="n">
         <v>-95.5069223</v>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="inlineStr">
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="S56" t="n">
+      <c r="V56" t="n">
         <v>-0.08</v>
       </c>
     </row>
@@ -8433,26 +8726,31 @@
       <c r="M57" t="n">
         <v>-95.506894749739</v>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="inlineStr">
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S57" t="n">
+      <c r="V57" t="n">
         <v>-0.262</v>
       </c>
     </row>
@@ -8502,26 +8800,31 @@
       <c r="M58" t="n">
         <v>-95.50688999502</v>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="inlineStr">
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S58" t="n">
+      <c r="V58" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -8571,26 +8874,31 @@
       <c r="M59" t="n">
         <v>-95.5041234</v>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O59" t="n">
-        <v>1</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="inlineStr">
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S59" t="n">
+      <c r="V59" t="n">
         <v>-0.06900000000000001</v>
       </c>
     </row>
@@ -8640,26 +8948,31 @@
       <c r="M60" t="n">
         <v>-95.5038969</v>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="inlineStr">
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S60" t="n">
+      <c r="V60" t="n">
         <v>-0.423</v>
       </c>
     </row>
@@ -8709,26 +9022,31 @@
       <c r="M61" t="n">
         <v>-95.50324809999999</v>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="inlineStr">
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S61" t="n">
+      <c r="V61" t="n">
         <v>-0.55</v>
       </c>
     </row>
@@ -8778,26 +9096,31 @@
       <c r="M62" t="n">
         <v>-95.5035556</v>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="inlineStr">
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="S62" t="n">
+      <c r="V62" t="n">
         <v>-0.744</v>
       </c>
     </row>
@@ -8847,26 +9170,31 @@
       <c r="M63" t="n">
         <v>-95.50350280588199</v>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="inlineStr">
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="S63" t="n">
+      <c r="V63" t="n">
         <v>-0.376</v>
       </c>
     </row>
@@ -8916,26 +9244,31 @@
       <c r="M64" t="n">
         <v>-95.50344218993</v>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="inlineStr">
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S64" t="n">
+      <c r="V64" t="n">
         <v>-0.024</v>
       </c>
     </row>
@@ -8985,26 +9318,31 @@
       <c r="M65" t="n">
         <v>-95.50343808710301</v>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="inlineStr">
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S65" t="n">
+      <c r="V65" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -9054,26 +9392,31 @@
       <c r="M66" t="n">
         <v>-95.507825352252</v>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O66" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="inlineStr">
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S66" t="n">
+      <c r="V66" t="n">
         <v>0.014</v>
       </c>
     </row>
@@ -9123,26 +9466,31 @@
       <c r="M67" t="n">
         <v>-95.5090403</v>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="inlineStr">
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S67" t="n">
+      <c r="V67" t="n">
         <v>-0.588</v>
       </c>
     </row>
@@ -9192,26 +9540,31 @@
       <c r="M68" t="n">
         <v>-95.5092171</v>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="inlineStr">
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S68" t="n">
+      <c r="V68" t="n">
         <v>-0.225</v>
       </c>
     </row>
@@ -9261,26 +9614,31 @@
       <c r="M69" t="n">
         <v>-95.50925137582399</v>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="inlineStr">
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S69" t="n">
+      <c r="V69" t="n">
         <v>-0.491</v>
       </c>
     </row>
@@ -9330,26 +9688,31 @@
       <c r="M70" t="n">
         <v>-95.509258680835</v>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="inlineStr">
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S70" t="n">
+      <c r="V70" t="n">
         <v>-0.579</v>
       </c>
     </row>
@@ -9399,26 +9762,31 @@
       <c r="M71" t="n">
         <v>-95.509263950274</v>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="inlineStr">
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S71" t="n">
+      <c r="V71" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -9468,26 +9836,31 @@
       <c r="M72" t="n">
         <v>-95.50847176462401</v>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O72" t="n">
-        <v>1</v>
-      </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="inlineStr">
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S72" t="n">
+      <c r="V72" t="n">
         <v>-0.335</v>
       </c>
     </row>
@@ -9537,26 +9910,31 @@
       <c r="M73" t="n">
         <v>-95.5081204</v>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="inlineStr">
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S73" t="n">
+      <c r="V73" t="n">
         <v>-0.591</v>
       </c>
     </row>
@@ -9606,26 +9984,31 @@
       <c r="M74" t="n">
         <v>-95.5075255</v>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="inlineStr">
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S74" t="n">
+      <c r="V74" t="n">
         <v>-0.519</v>
       </c>
     </row>
@@ -9675,26 +10058,31 @@
       <c r="M75" t="n">
         <v>-95.50732530000001</v>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="inlineStr">
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S75" t="n">
+      <c r="V75" t="n">
         <v>-0.634</v>
       </c>
     </row>
@@ -9744,26 +10132,31 @@
       <c r="M76" t="n">
         <v>-95.506800748408</v>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" t="inlineStr">
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S76" t="n">
+      <c r="V76" t="n">
         <v>-0.424</v>
       </c>
     </row>
@@ -9813,26 +10206,31 @@
       <c r="M77" t="n">
         <v>-95.506673678756</v>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="inlineStr">
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="S77" t="n">
+      <c r="V77" t="n">
         <v>-0.592</v>
       </c>
     </row>
@@ -9882,26 +10280,31 @@
       <c r="M78" t="n">
         <v>-95.506726864749</v>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1</v>
-      </c>
-      <c r="R78" t="inlineStr">
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S78" t="n">
+      <c r="V78" t="n">
         <v>0.218</v>
       </c>
     </row>
@@ -9951,26 +10354,31 @@
       <c r="M79" t="n">
         <v>-95.50894718617199</v>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O79" t="n">
-        <v>1</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="inlineStr">
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S79" t="n">
+      <c r="V79" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -10020,26 +10428,31 @@
       <c r="M80" t="n">
         <v>-95.5092968</v>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="inlineStr">
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S80" t="n">
+      <c r="V80" t="n">
         <v>-0.575</v>
       </c>
     </row>
@@ -10089,26 +10502,31 @@
       <c r="M81" t="n">
         <v>-95.5095985</v>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="inlineStr">
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S81" t="n">
+      <c r="V81" t="n">
         <v>-0.261</v>
       </c>
     </row>
@@ -10158,26 +10576,31 @@
       <c r="M82" t="n">
         <v>-95.5095513</v>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" t="inlineStr">
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S82" t="n">
+      <c r="V82" t="n">
         <v>0.032</v>
       </c>
     </row>
@@ -10227,26 +10650,31 @@
       <c r="M83" t="n">
         <v>-95.50954872469499</v>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="inlineStr">
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S83" t="n">
+      <c r="V83" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -10296,26 +10724,31 @@
       <c r="M84" t="n">
         <v>-95.51054310000001</v>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O84" t="n">
-        <v>1</v>
-      </c>
-      <c r="P84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" t="inlineStr">
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S84" t="n">
+      <c r="V84" t="n">
         <v>-0.521</v>
       </c>
     </row>
@@ -10365,26 +10798,31 @@
       <c r="M85" t="n">
         <v>-95.51044804054099</v>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" t="inlineStr">
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="S85" t="n">
+      <c r="V85" t="n">
         <v>-0.477</v>
       </c>
     </row>
@@ -10434,26 +10872,31 @@
       <c r="M86" t="n">
         <v>-95.510356864613</v>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" t="inlineStr">
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S86" t="n">
+      <c r="V86" t="n">
         <v>0.152</v>
       </c>
     </row>
@@ -10503,26 +10946,31 @@
       <c r="M87" t="n">
         <v>-95.510353330615</v>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="inlineStr">
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S87" t="n">
+      <c r="V87" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -10572,26 +11020,31 @@
       <c r="M88" t="n">
         <v>-95.511504001915</v>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O88" t="n">
-        <v>1</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" t="inlineStr">
+      <c r="R88" t="n">
+        <v>1</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S88" t="n">
+      <c r="V88" t="n">
         <v>-0.078</v>
       </c>
     </row>
@@ -10641,26 +11094,31 @@
       <c r="M89" t="n">
         <v>-95.5112743</v>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="inlineStr">
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="S89" t="n">
+      <c r="V89" t="n">
         <v>-0.286</v>
       </c>
     </row>
@@ -10710,26 +11168,31 @@
       <c r="M90" t="n">
         <v>-95.51127963669801</v>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="inlineStr">
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>1</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S90" t="n">
+      <c r="V90" t="n">
         <v>-0.701</v>
       </c>
     </row>
@@ -10779,26 +11242,31 @@
       <c r="M91" t="n">
         <v>-95.511284177268</v>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="inlineStr">
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S91" t="n">
+      <c r="V91" t="n">
         <v>-0.579</v>
       </c>
     </row>
@@ -10848,26 +11316,31 @@
       <c r="M92" t="n">
         <v>-95.51128599349499</v>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="inlineStr">
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>1</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S92" t="n">
+      <c r="V92" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -10917,26 +11390,31 @@
       <c r="M93" t="n">
         <v>-95.511086247861</v>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O93" t="n">
-        <v>1</v>
-      </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" t="inlineStr">
+      <c r="R93" t="n">
+        <v>1</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S93" t="n">
+      <c r="V93" t="n">
         <v>0.064</v>
       </c>
     </row>
@@ -10986,26 +11464,31 @@
       <c r="M94" t="n">
         <v>-95.511765895002</v>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" t="inlineStr">
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S94" t="n">
+      <c r="V94" t="n">
         <v>0.179</v>
       </c>
     </row>
@@ -11055,26 +11538,31 @@
       <c r="M95" t="n">
         <v>-95.51178458856999</v>
       </c>
-      <c r="N95" t="inlineStr">
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" t="inlineStr">
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>1</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S95" t="n">
+      <c r="V95" t="n">
         <v>-0.223</v>
       </c>
     </row>
@@ -11124,26 +11612,31 @@
       <c r="M96" t="n">
         <v>-95.51178746450201</v>
       </c>
-      <c r="N96" t="inlineStr">
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" t="inlineStr">
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>1</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S96" t="n">
+      <c r="V96" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -11193,26 +11686,31 @@
       <c r="M97" t="n">
         <v>-95.513280166667</v>
       </c>
-      <c r="N97" t="inlineStr">
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O97" t="n">
-        <v>1</v>
-      </c>
-      <c r="P97" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" t="inlineStr">
+      <c r="R97" t="n">
+        <v>1</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S97" t="n">
+      <c r="V97" t="n">
         <v>-0.667</v>
       </c>
     </row>
@@ -11262,26 +11760,31 @@
       <c r="M98" t="n">
         <v>-95.5131428</v>
       </c>
-      <c r="N98" t="inlineStr">
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" t="inlineStr">
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S98" t="n">
+      <c r="V98" t="n">
         <v>-0.8159999999999999</v>
       </c>
     </row>
@@ -11331,26 +11834,31 @@
       <c r="M99" t="n">
         <v>-95.51212641714299</v>
       </c>
-      <c r="N99" t="inlineStr">
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" t="inlineStr">
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S99" t="n">
+      <c r="V99" t="n">
         <v>-0.109</v>
       </c>
     </row>
@@ -11400,26 +11908,31 @@
       <c r="M100" t="n">
         <v>-95.5117566</v>
       </c>
-      <c r="N100" t="inlineStr">
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" t="inlineStr">
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S100" t="n">
+      <c r="V100" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -11469,26 +11982,31 @@
       <c r="M101" t="n">
         <v>-95.511858366474</v>
       </c>
-      <c r="N101" t="inlineStr">
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="inlineStr">
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>1</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S101" t="n">
+      <c r="V101" t="n">
         <v>-0.256</v>
       </c>
     </row>
@@ -11538,26 +12056,31 @@
       <c r="M102" t="n">
         <v>-95.511873113416</v>
       </c>
-      <c r="N102" t="inlineStr">
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" t="inlineStr">
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>1</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S102" t="n">
+      <c r="V102" t="n">
         <v>0.434</v>
       </c>
     </row>
@@ -11607,26 +12130,31 @@
       <c r="M103" t="n">
         <v>-95.51446919999999</v>
       </c>
-      <c r="N103" t="inlineStr">
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O103" t="n">
-        <v>1</v>
-      </c>
-      <c r="P103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
-      <c r="R103" t="inlineStr">
+      <c r="R103" t="n">
+        <v>1</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S103" t="n">
+      <c r="V103" t="n">
         <v>0.193</v>
       </c>
     </row>
@@ -11676,26 +12204,31 @@
       <c r="M104" t="n">
         <v>-95.514446094242</v>
       </c>
-      <c r="N104" t="inlineStr">
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" t="inlineStr">
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>1</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S104" t="n">
+      <c r="V104" t="n">
         <v>-0.223</v>
       </c>
     </row>
@@ -11745,26 +12278,31 @@
       <c r="M105" t="n">
         <v>-95.51444253951099</v>
       </c>
-      <c r="N105" t="inlineStr">
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" t="inlineStr">
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>1</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S105" t="n">
+      <c r="V105" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -11814,26 +12352,31 @@
       <c r="M106" t="n">
         <v>-95.5149014</v>
       </c>
-      <c r="N106" t="inlineStr">
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O106" t="n">
-        <v>1</v>
-      </c>
-      <c r="P106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" t="inlineStr">
+      <c r="R106" t="n">
+        <v>1</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S106" t="n">
+      <c r="V106" t="n">
         <v>-0.44</v>
       </c>
     </row>
@@ -11883,26 +12426,31 @@
       <c r="M107" t="n">
         <v>-95.5161392</v>
       </c>
-      <c r="N107" t="inlineStr">
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" t="inlineStr">
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S107" t="n">
+      <c r="V107" t="n">
         <v>-0.186</v>
       </c>
     </row>
@@ -11952,26 +12500,31 @@
       <c r="M108" t="n">
         <v>-95.5166555</v>
       </c>
-      <c r="N108" t="inlineStr">
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" t="inlineStr">
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S108" t="n">
+      <c r="V108" t="n">
         <v>0.053</v>
       </c>
     </row>
@@ -12021,26 +12574,31 @@
       <c r="M109" t="n">
         <v>-95.516657464178</v>
       </c>
-      <c r="N109" t="inlineStr">
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" t="inlineStr">
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>1</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S109" t="n">
+      <c r="V109" t="n">
         <v>-0.528</v>
       </c>
     </row>
@@ -12090,26 +12648,31 @@
       <c r="M110" t="n">
         <v>-95.5166581</v>
       </c>
-      <c r="N110" t="inlineStr">
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O110" t="n">
-        <v>0</v>
-      </c>
-      <c r="P110" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
-      <c r="R110" t="inlineStr">
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="n">
+        <v>1</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S110" t="n">
+      <c r="V110" t="n">
         <v>-0.579</v>
       </c>
     </row>
@@ -12159,26 +12722,31 @@
       <c r="M111" t="n">
         <v>-95.516658354329</v>
       </c>
-      <c r="N111" t="inlineStr">
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
-      <c r="R111" t="inlineStr">
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="n">
+        <v>1</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S111" t="n">
+      <c r="V111" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -12228,26 +12796,31 @@
       <c r="M112" t="n">
         <v>-95.5152176</v>
       </c>
-      <c r="N112" t="inlineStr">
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O112" t="n">
-        <v>1</v>
-      </c>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" t="inlineStr">
+      <c r="R112" t="n">
+        <v>1</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S112" t="n">
+      <c r="V112" t="n">
         <v>-0.007</v>
       </c>
     </row>
@@ -12297,26 +12870,31 @@
       <c r="M113" t="n">
         <v>-95.5152813</v>
       </c>
-      <c r="N113" t="inlineStr">
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" t="inlineStr">
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S113" t="n">
+      <c r="V113" t="n">
         <v>-0.262</v>
       </c>
     </row>
@@ -12366,26 +12944,31 @@
       <c r="M114" t="n">
         <v>-95.5154017</v>
       </c>
-      <c r="N114" t="inlineStr">
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O114" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
-      <c r="R114" t="inlineStr">
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S114" t="n">
+      <c r="V114" t="n">
         <v>-0.438</v>
       </c>
     </row>
@@ -12435,26 +13018,31 @@
       <c r="M115" t="n">
         <v>-95.5151939</v>
       </c>
-      <c r="N115" t="inlineStr">
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" t="inlineStr">
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S115" t="n">
+      <c r="V115" t="n">
         <v>-0.626</v>
       </c>
     </row>
@@ -12504,26 +13092,31 @@
       <c r="M116" t="n">
         <v>-95.5150067</v>
       </c>
-      <c r="N116" t="inlineStr">
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" t="inlineStr">
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="S116" t="n">
+      <c r="V116" t="n">
         <v>0.349</v>
       </c>
     </row>
@@ -12573,26 +13166,31 @@
       <c r="M117" t="n">
         <v>-95.51500633978701</v>
       </c>
-      <c r="N117" t="inlineStr">
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O117" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
-      <c r="R117" t="inlineStr">
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
+        <v>1</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S117" t="n">
+      <c r="V117" t="n">
         <v>-0.747</v>
       </c>
     </row>
@@ -12642,26 +13240,31 @@
       <c r="M118" t="n">
         <v>-95.51500609964501</v>
       </c>
-      <c r="N118" t="inlineStr">
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="inlineStr">
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>1</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S118" t="n">
+      <c r="V118" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -12711,26 +13314,31 @@
       <c r="M119" t="n">
         <v>-95.5177023</v>
       </c>
-      <c r="N119" t="inlineStr">
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O119" t="n">
-        <v>1</v>
-      </c>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" t="inlineStr">
+      <c r="R119" t="n">
+        <v>1</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S119" t="n">
+      <c r="V119" t="n">
         <v>0.144</v>
       </c>
     </row>
@@ -12780,26 +13388,31 @@
       <c r="M120" t="n">
         <v>-95.5180221</v>
       </c>
-      <c r="N120" t="inlineStr">
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O120" t="n">
-        <v>0</v>
-      </c>
-      <c r="P120" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
-      <c r="R120" t="inlineStr">
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S120" t="n">
+      <c r="V120" t="n">
         <v>-0.316</v>
       </c>
     </row>
@@ -12849,26 +13462,31 @@
       <c r="M121" t="n">
         <v>-95.51820702481</v>
       </c>
-      <c r="N121" t="inlineStr">
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="inlineStr">
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>1</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S121" t="n">
+      <c r="V121" t="n">
         <v>-0.13</v>
       </c>
     </row>
@@ -12918,26 +13536,31 @@
       <c r="M122" t="n">
         <v>-95.518233</v>
       </c>
-      <c r="N122" t="inlineStr">
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="inlineStr">
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S122" t="n">
+      <c r="V122" t="n">
         <v>-0.579</v>
       </c>
     </row>
@@ -12987,26 +13610,31 @@
       <c r="M123" t="n">
         <v>-95.51822695304899</v>
       </c>
-      <c r="N123" t="inlineStr">
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" t="inlineStr">
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>1</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S123" t="n">
+      <c r="V123" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -13056,26 +13684,31 @@
       <c r="M124" t="n">
         <v>-95.51822730000001</v>
       </c>
-      <c r="N124" t="inlineStr">
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O124" t="n">
-        <v>1</v>
-      </c>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
-      <c r="R124" t="inlineStr">
+      <c r="R124" t="n">
+        <v>1</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S124" t="n">
+      <c r="V124" t="n">
         <v>-0.625</v>
       </c>
     </row>
@@ -13125,26 +13758,31 @@
       <c r="M125" t="n">
         <v>-95.5188095</v>
       </c>
-      <c r="N125" t="inlineStr">
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O125" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" t="inlineStr">
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S125" t="n">
+      <c r="V125" t="n">
         <v>-0.648</v>
       </c>
     </row>
@@ -13194,26 +13832,31 @@
       <c r="M126" t="n">
         <v>-95.5187648</v>
       </c>
-      <c r="N126" t="inlineStr">
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="inlineStr">
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="S126" t="n">
+      <c r="V126" t="n">
         <v>-0.571</v>
       </c>
     </row>
@@ -13263,26 +13906,31 @@
       <c r="M127" t="n">
         <v>-95.51860840000001</v>
       </c>
-      <c r="N127" t="inlineStr">
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" t="inlineStr">
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>1</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S127" t="n">
+      <c r="V127" t="n">
         <v>0.214</v>
       </c>
     </row>
@@ -13332,26 +13980,31 @@
       <c r="M128" t="n">
         <v>-95.51860311448699</v>
       </c>
-      <c r="N128" t="inlineStr">
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O128" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
-      <c r="R128" t="inlineStr">
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>1</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S128" t="n">
+      <c r="V128" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -13401,26 +14054,31 @@
       <c r="M129" t="n">
         <v>-95.5195617</v>
       </c>
-      <c r="N129" t="inlineStr">
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O129" t="n">
-        <v>1</v>
-      </c>
-      <c r="P129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" t="inlineStr">
+      <c r="R129" t="n">
+        <v>1</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S129" t="n">
+      <c r="V129" t="n">
         <v>-0.797</v>
       </c>
     </row>
@@ -13470,26 +14128,31 @@
       <c r="M130" t="n">
         <v>-95.5205663</v>
       </c>
-      <c r="N130" t="inlineStr">
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O130" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
-      <c r="R130" t="inlineStr">
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S130" t="n">
+      <c r="V130" t="n">
         <v>0.133</v>
       </c>
     </row>
@@ -13539,26 +14202,31 @@
       <c r="M131" t="n">
         <v>-95.5209617</v>
       </c>
-      <c r="N131" t="inlineStr">
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R131" t="inlineStr">
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S131" t="n">
+      <c r="V131" t="n">
         <v>-0.7</v>
       </c>
     </row>
@@ -13608,26 +14276,31 @@
       <c r="M132" t="n">
         <v>-95.5208117</v>
       </c>
-      <c r="N132" t="inlineStr">
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O132" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" t="inlineStr">
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S132" t="n">
+      <c r="V132" t="n">
         <v>-0.252</v>
       </c>
     </row>
@@ -13677,26 +14350,31 @@
       <c r="M133" t="n">
         <v>-95.5207776</v>
       </c>
-      <c r="N133" t="inlineStr">
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" t="inlineStr">
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="n">
+        <v>1</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S133" t="n">
+      <c r="V133" t="n">
         <v>0.036</v>
       </c>
     </row>
@@ -13746,26 +14424,31 @@
       <c r="M134" t="n">
         <v>-95.52077577513001</v>
       </c>
-      <c r="N134" t="inlineStr">
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" t="inlineStr">
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>1</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S134" t="n">
+      <c r="V134" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -13815,26 +14498,31 @@
       <c r="M135" t="n">
         <v>-95.5183045</v>
       </c>
-      <c r="N135" t="inlineStr">
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O135" t="n">
-        <v>1</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" t="inlineStr">
+      <c r="R135" t="n">
+        <v>1</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S135" t="n">
+      <c r="V135" t="n">
         <v>-0.232</v>
       </c>
     </row>
@@ -13884,26 +14572,31 @@
       <c r="M136" t="n">
         <v>-95.5173234</v>
       </c>
-      <c r="N136" t="inlineStr">
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O136" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
-      <c r="R136" t="inlineStr">
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S136" t="n">
+      <c r="V136" t="n">
         <v>-0.403</v>
       </c>
     </row>
@@ -13953,26 +14646,31 @@
       <c r="M137" t="n">
         <v>-95.516398396</v>
       </c>
-      <c r="N137" t="inlineStr">
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O137" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
-      <c r="R137" t="inlineStr">
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S137" t="n">
+      <c r="V137" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -14022,26 +14720,31 @@
       <c r="M138" t="n">
         <v>-95.51633390000001</v>
       </c>
-      <c r="N138" t="inlineStr">
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" t="inlineStr">
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="S138" t="n">
+      <c r="V138" t="n">
         <v>0.357</v>
       </c>
     </row>
@@ -14091,26 +14794,31 @@
       <c r="M139" t="n">
         <v>-95.51634137024401</v>
       </c>
-      <c r="N139" t="inlineStr">
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="inlineStr">
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="n">
+        <v>1</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S139" t="n">
+      <c r="V139" t="n">
         <v>0.266</v>
       </c>
     </row>
@@ -14160,26 +14868,31 @@
       <c r="M140" t="n">
         <v>-95.514882691892</v>
       </c>
-      <c r="N140" t="inlineStr">
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O140" t="n">
-        <v>1</v>
-      </c>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" t="inlineStr">
+      <c r="R140" t="n">
+        <v>1</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S140" t="n">
+      <c r="V140" t="n">
         <v>-0.114</v>
       </c>
     </row>
@@ -14229,26 +14942,31 @@
       <c r="M141" t="n">
         <v>-95.5141737</v>
       </c>
-      <c r="N141" t="inlineStr">
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O141" t="n">
-        <v>0</v>
-      </c>
-      <c r="P141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
-      <c r="R141" t="inlineStr">
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S141" t="n">
+      <c r="V141" t="n">
         <v>-0.267</v>
       </c>
     </row>
@@ -14298,26 +15016,31 @@
       <c r="M142" t="n">
         <v>-95.51382719999999</v>
       </c>
-      <c r="N142" t="inlineStr">
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O142" t="n">
-        <v>0</v>
-      </c>
-      <c r="P142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" t="inlineStr">
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S142" t="n">
+      <c r="V142" t="n">
         <v>-0.454</v>
       </c>
     </row>
@@ -14367,26 +15090,31 @@
       <c r="M143" t="n">
         <v>-95.5136598</v>
       </c>
-      <c r="N143" t="inlineStr">
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="P143" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
-      <c r="R143" t="inlineStr">
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="n">
+        <v>1</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S143" t="n">
+      <c r="V143" t="n">
         <v>0.338</v>
       </c>
     </row>
@@ -14436,26 +15164,31 @@
       <c r="M144" t="n">
         <v>-95.51365555265799</v>
       </c>
-      <c r="N144" t="inlineStr">
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O144" t="n">
-        <v>0</v>
-      </c>
-      <c r="P144" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
-      <c r="R144" t="inlineStr">
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="n">
+        <v>1</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S144" t="n">
+      <c r="V144" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -14505,26 +15238,31 @@
       <c r="M145" t="n">
         <v>-95.5100248</v>
       </c>
-      <c r="N145" t="inlineStr">
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O145" t="n">
-        <v>1</v>
-      </c>
-      <c r="P145" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
-      <c r="R145" t="inlineStr">
+      <c r="R145" t="n">
+        <v>1</v>
+      </c>
+      <c r="S145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S145" t="n">
+      <c r="V145" t="n">
         <v>0.117</v>
       </c>
     </row>
@@ -14574,26 +15312,31 @@
       <c r="M146" t="n">
         <v>-95.5092606</v>
       </c>
-      <c r="N146" t="inlineStr">
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="inlineStr">
         <is>
           <t>fairway</t>
         </is>
       </c>
-      <c r="O146" t="n">
-        <v>0</v>
-      </c>
-      <c r="P146" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
-      <c r="R146" t="inlineStr">
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
+        <v>0</v>
+      </c>
+      <c r="U146" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S146" t="n">
+      <c r="V146" t="n">
         <v>-0.735</v>
       </c>
     </row>
@@ -14643,26 +15386,31 @@
       <c r="M147" t="n">
         <v>-95.5089644</v>
       </c>
-      <c r="N147" t="inlineStr">
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O147" t="n">
-        <v>0</v>
-      </c>
-      <c r="P147" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
-      <c r="R147" t="inlineStr">
+      <c r="R147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" t="n">
+        <v>0</v>
+      </c>
+      <c r="U147" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S147" t="n">
+      <c r="V147" t="n">
         <v>-0.043</v>
       </c>
     </row>
@@ -14712,26 +15460,31 @@
       <c r="M148" t="n">
         <v>-95.5089198</v>
       </c>
-      <c r="N148" t="inlineStr">
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q148" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O148" t="n">
-        <v>0</v>
-      </c>
-      <c r="P148" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
-      <c r="R148" t="inlineStr">
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="n">
+        <v>1</v>
+      </c>
+      <c r="T148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S148" t="n">
+      <c r="V148" t="n">
         <v>-0.199</v>
       </c>
     </row>
@@ -14781,26 +15534,31 @@
       <c r="M149" t="n">
         <v>-95.508913475274</v>
       </c>
-      <c r="N149" t="inlineStr">
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O149" t="n">
-        <v>0</v>
-      </c>
-      <c r="P149" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
-      <c r="R149" t="inlineStr">
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="n">
+        <v>1</v>
+      </c>
+      <c r="T149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S149" t="n">
+      <c r="V149" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -14850,26 +15608,31 @@
       <c r="M150" t="n">
         <v>-95.5073623</v>
       </c>
-      <c r="N150" t="inlineStr">
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O150" t="n">
-        <v>1</v>
-      </c>
-      <c r="P150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
-      <c r="R150" t="inlineStr">
+      <c r="R150" t="n">
+        <v>1</v>
+      </c>
+      <c r="S150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S150" t="n">
+      <c r="V150" t="n">
         <v>-0.712</v>
       </c>
     </row>
@@ -14919,26 +15682,31 @@
       <c r="M151" t="n">
         <v>-95.506825732343</v>
       </c>
-      <c r="N151" t="inlineStr">
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O151" t="n">
-        <v>0</v>
-      </c>
-      <c r="P151" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
-      <c r="R151" t="inlineStr">
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S151" t="n">
+      <c r="V151" t="n">
         <v>0.123</v>
       </c>
     </row>
@@ -14988,26 +15756,31 @@
       <c r="M152" t="n">
         <v>-95.506800467771</v>
       </c>
-      <c r="N152" t="inlineStr">
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O152" t="n">
-        <v>0</v>
-      </c>
-      <c r="P152" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
-      <c r="R152" t="inlineStr">
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="n">
+        <v>1</v>
+      </c>
+      <c r="T152" t="n">
+        <v>0</v>
+      </c>
+      <c r="U152" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S152" t="n">
+      <c r="V152" t="n">
         <v>-0.644</v>
       </c>
     </row>
@@ -15057,26 +15830,31 @@
       <c r="M153" t="n">
         <v>-95.50678467741299</v>
       </c>
-      <c r="N153" t="inlineStr">
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O153" t="n">
-        <v>0</v>
-      </c>
-      <c r="P153" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
-      <c r="R153" t="inlineStr">
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="n">
+        <v>1</v>
+      </c>
+      <c r="T153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S153" t="n">
+      <c r="V153" t="n">
         <v>-0.579</v>
       </c>
     </row>
@@ -15126,26 +15904,31 @@
       <c r="M154" t="n">
         <v>-95.50677836126999</v>
       </c>
-      <c r="N154" t="inlineStr">
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O154" t="n">
-        <v>0</v>
-      </c>
-      <c r="P154" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
-      <c r="R154" t="inlineStr">
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="n">
+        <v>1</v>
+      </c>
+      <c r="T154" t="n">
+        <v>0</v>
+      </c>
+      <c r="U154" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S154" t="n">
+      <c r="V154" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -15195,26 +15978,31 @@
       <c r="M155" t="n">
         <v>-95.50333860000001</v>
       </c>
-      <c r="N155" t="inlineStr">
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O155" t="n">
-        <v>1</v>
-      </c>
-      <c r="P155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
-      <c r="R155" t="inlineStr">
+      <c r="R155" t="n">
+        <v>1</v>
+      </c>
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S155" t="n">
+      <c r="V155" t="n">
         <v>-0.177</v>
       </c>
     </row>
@@ -15264,26 +16052,31 @@
       <c r="M156" t="n">
         <v>-95.503373188889</v>
       </c>
-      <c r="N156" t="inlineStr">
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O156" t="n">
-        <v>0</v>
-      </c>
-      <c r="P156" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
-      <c r="R156" t="inlineStr">
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="n">
+        <v>0</v>
+      </c>
+      <c r="T156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S156" t="n">
+      <c r="V156" t="n">
         <v>-0.522</v>
       </c>
     </row>
@@ -15333,26 +16126,31 @@
       <c r="M157" t="n">
         <v>-95.5034579</v>
       </c>
-      <c r="N157" t="inlineStr">
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O157" t="n">
-        <v>0</v>
-      </c>
-      <c r="P157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
-      <c r="R157" t="inlineStr">
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S157" t="n">
+      <c r="V157" t="n">
         <v>-0.529</v>
       </c>
     </row>
@@ -15402,26 +16200,31 @@
       <c r="M158" t="n">
         <v>-95.5030021</v>
       </c>
-      <c r="N158" t="inlineStr">
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O158" t="n">
-        <v>0</v>
-      </c>
-      <c r="P158" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
-      <c r="R158" t="inlineStr">
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" t="n">
+        <v>0</v>
+      </c>
+      <c r="U158" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S158" t="n">
+      <c r="V158" t="n">
         <v>-0.6870000000000001</v>
       </c>
     </row>
@@ -15471,26 +16274,31 @@
       <c r="M159" t="n">
         <v>-95.5034517</v>
       </c>
-      <c r="N159" t="inlineStr">
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q159" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O159" t="n">
-        <v>0</v>
-      </c>
-      <c r="P159" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
-      <c r="R159" t="inlineStr">
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S159" t="n">
+      <c r="V159" t="n">
         <v>0.579</v>
       </c>
     </row>
@@ -15540,26 +16348,31 @@
       <c r="M160" t="n">
         <v>-95.50344991160399</v>
       </c>
-      <c r="N160" t="inlineStr">
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O160" t="n">
-        <v>0</v>
-      </c>
-      <c r="P160" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
-      <c r="R160" t="inlineStr">
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="n">
+        <v>1</v>
+      </c>
+      <c r="T160" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S160" t="n">
+      <c r="V160" t="n">
         <v>0.266</v>
       </c>
     </row>
@@ -15609,26 +16422,31 @@
       <c r="M161" t="n">
         <v>-95.50646020000001</v>
       </c>
-      <c r="N161" t="inlineStr">
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O161" t="n">
-        <v>1</v>
-      </c>
-      <c r="P161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
-      <c r="R161" t="inlineStr">
+      <c r="R161" t="n">
+        <v>1</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
+        <v>0</v>
+      </c>
+      <c r="U161" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S161" t="n">
+      <c r="V161" t="n">
         <v>-0.737</v>
       </c>
     </row>
@@ -15678,26 +16496,31 @@
       <c r="M162" t="n">
         <v>-95.50790189999999</v>
       </c>
-      <c r="N162" t="inlineStr">
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O162" t="n">
-        <v>0</v>
-      </c>
-      <c r="P162" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
-      <c r="R162" t="inlineStr">
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S162" t="n">
+      <c r="V162" t="n">
         <v>-0.038</v>
       </c>
     </row>
@@ -15747,26 +16570,31 @@
       <c r="M163" t="n">
         <v>-95.509301576667</v>
       </c>
-      <c r="N163" t="inlineStr">
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O163" t="n">
-        <v>0</v>
-      </c>
-      <c r="P163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
-      <c r="R163" t="inlineStr">
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S163" t="n">
+      <c r="V163" t="n">
         <v>-0.278</v>
       </c>
     </row>
@@ -15816,26 +16644,31 @@
       <c r="M164" t="n">
         <v>-95.5092519</v>
       </c>
-      <c r="N164" t="inlineStr">
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O164" t="n">
-        <v>0</v>
-      </c>
-      <c r="P164" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
-      <c r="R164" t="inlineStr">
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" t="n">
+        <v>0</v>
+      </c>
+      <c r="U164" t="inlineStr">
         <is>
           <t>short_game</t>
         </is>
       </c>
-      <c r="S164" t="n">
+      <c r="V164" t="n">
         <v>0.358</v>
       </c>
     </row>
@@ -15885,26 +16718,31 @@
       <c r="M165" t="n">
         <v>-95.509252031399</v>
       </c>
-      <c r="N165" t="inlineStr">
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O165" t="n">
-        <v>0</v>
-      </c>
-      <c r="P165" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
-      <c r="R165" t="inlineStr">
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="n">
+        <v>1</v>
+      </c>
+      <c r="T165" t="n">
+        <v>0</v>
+      </c>
+      <c r="U165" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S165" t="n">
+      <c r="V165" t="n">
         <v>-0.747</v>
       </c>
     </row>
@@ -15954,26 +16792,31 @@
       <c r="M166" t="n">
         <v>-95.509252118997</v>
       </c>
-      <c r="N166" t="inlineStr">
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O166" t="n">
-        <v>0</v>
-      </c>
-      <c r="P166" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
-      <c r="R166" t="inlineStr">
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="n">
+        <v>1</v>
+      </c>
+      <c r="T166" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S166" t="n">
+      <c r="V166" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -16023,26 +16866,31 @@
       <c r="M167" t="n">
         <v>-95.5090495</v>
       </c>
-      <c r="N167" t="inlineStr">
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O167" t="n">
-        <v>1</v>
-      </c>
-      <c r="P167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
-      <c r="R167" t="inlineStr">
+      <c r="R167" t="n">
+        <v>1</v>
+      </c>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S167" t="n">
+      <c r="V167" t="n">
         <v>-0.452</v>
       </c>
     </row>
@@ -16092,26 +16940,31 @@
       <c r="M168" t="n">
         <v>-95.50878413333299</v>
       </c>
-      <c r="N168" t="inlineStr">
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O168" t="n">
-        <v>0</v>
-      </c>
-      <c r="P168" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
-      <c r="R168" t="inlineStr">
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" t="n">
+        <v>0</v>
+      </c>
+      <c r="U168" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S168" t="n">
+      <c r="V168" t="n">
         <v>-0.797</v>
       </c>
     </row>
@@ -16161,26 +17014,31 @@
       <c r="M169" t="n">
         <v>-95.5082294</v>
       </c>
-      <c r="N169" t="inlineStr">
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O169" t="n">
-        <v>0</v>
-      </c>
-      <c r="P169" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
-      <c r="R169" t="inlineStr">
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S169" t="n">
+      <c r="V169" t="n">
         <v>-0.22</v>
       </c>
     </row>
@@ -16230,26 +17088,31 @@
       <c r="M170" t="n">
         <v>-95.5070678</v>
       </c>
-      <c r="N170" t="inlineStr">
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O170" t="n">
-        <v>0</v>
-      </c>
-      <c r="P170" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
-      <c r="R170" t="inlineStr">
+      <c r="R170" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" t="n">
+        <v>0</v>
+      </c>
+      <c r="U170" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S170" t="n">
+      <c r="V170" t="n">
         <v>-0.259</v>
       </c>
     </row>
@@ -16299,26 +17162,31 @@
       <c r="M171" t="n">
         <v>-95.506740723962</v>
       </c>
-      <c r="N171" t="inlineStr">
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O171" t="n">
-        <v>0</v>
-      </c>
-      <c r="P171" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
-      <c r="R171" t="inlineStr">
+      <c r="R171" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" t="n">
+        <v>0</v>
+      </c>
+      <c r="T171" t="n">
+        <v>0</v>
+      </c>
+      <c r="U171" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S171" t="n">
+      <c r="V171" t="n">
         <v>0.523</v>
       </c>
     </row>
@@ -16368,26 +17236,31 @@
       <c r="M172" t="n">
         <v>-95.506726864749</v>
       </c>
-      <c r="N172" t="inlineStr">
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q172" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O172" t="n">
-        <v>0</v>
-      </c>
-      <c r="P172" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
-      <c r="R172" t="inlineStr">
+      <c r="R172" t="n">
+        <v>0</v>
+      </c>
+      <c r="S172" t="n">
+        <v>1</v>
+      </c>
+      <c r="T172" t="n">
+        <v>0</v>
+      </c>
+      <c r="U172" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S172" t="n">
+      <c r="V172" t="n">
         <v>0.266</v>
       </c>
     </row>
@@ -16437,26 +17310,31 @@
       <c r="M173" t="n">
         <v>-95.50813890000001</v>
       </c>
-      <c r="N173" t="inlineStr">
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q173" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O173" t="n">
-        <v>1</v>
-      </c>
-      <c r="P173" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
-      <c r="R173" t="inlineStr">
+      <c r="R173" t="n">
+        <v>1</v>
+      </c>
+      <c r="S173" t="n">
+        <v>0</v>
+      </c>
+      <c r="T173" t="n">
+        <v>0</v>
+      </c>
+      <c r="U173" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S173" t="n">
+      <c r="V173" t="n">
         <v>-0.705</v>
       </c>
     </row>
@@ -16506,26 +17384,31 @@
       <c r="M174" t="n">
         <v>-95.5092935</v>
       </c>
-      <c r="N174" t="inlineStr">
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O174" t="n">
-        <v>0</v>
-      </c>
-      <c r="P174" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
-      <c r="R174" t="inlineStr">
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
+      <c r="S174" t="n">
+        <v>0</v>
+      </c>
+      <c r="T174" t="n">
+        <v>0</v>
+      </c>
+      <c r="U174" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S174" t="n">
+      <c r="V174" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -16575,26 +17458,31 @@
       <c r="M175" t="n">
         <v>-95.5095712</v>
       </c>
-      <c r="N175" t="inlineStr">
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q175" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O175" t="n">
-        <v>0</v>
-      </c>
-      <c r="P175" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
-      <c r="R175" t="inlineStr">
+      <c r="R175" t="n">
+        <v>0</v>
+      </c>
+      <c r="S175" t="n">
+        <v>0</v>
+      </c>
+      <c r="T175" t="n">
+        <v>0</v>
+      </c>
+      <c r="U175" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S175" t="n">
+      <c r="V175" t="n">
         <v>0.051</v>
       </c>
     </row>
@@ -16644,26 +17532,31 @@
       <c r="M176" t="n">
         <v>-95.50956480000001</v>
       </c>
-      <c r="N176" t="inlineStr">
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q176" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O176" t="n">
-        <v>0</v>
-      </c>
-      <c r="P176" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
-      <c r="R176" t="inlineStr">
+      <c r="R176" t="n">
+        <v>0</v>
+      </c>
+      <c r="S176" t="n">
+        <v>1</v>
+      </c>
+      <c r="T176" t="n">
+        <v>0</v>
+      </c>
+      <c r="U176" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S176" t="n">
+      <c r="V176" t="n">
         <v>-0.064</v>
       </c>
     </row>
@@ -16713,26 +17606,31 @@
       <c r="M177" t="n">
         <v>-95.509564284218</v>
       </c>
-      <c r="N177" t="inlineStr">
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O177" t="n">
-        <v>0</v>
-      </c>
-      <c r="P177" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
-      <c r="R177" t="inlineStr">
+      <c r="R177" t="n">
+        <v>0</v>
+      </c>
+      <c r="S177" t="n">
+        <v>1</v>
+      </c>
+      <c r="T177" t="n">
+        <v>0</v>
+      </c>
+      <c r="U177" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S177" t="n">
+      <c r="V177" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -16782,26 +17680,31 @@
       <c r="M178" t="n">
         <v>-95.51032720000001</v>
       </c>
-      <c r="N178" t="inlineStr">
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O178" t="n">
-        <v>1</v>
-      </c>
-      <c r="P178" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
-      <c r="R178" t="inlineStr">
+      <c r="R178" t="n">
+        <v>1</v>
+      </c>
+      <c r="S178" t="n">
+        <v>0</v>
+      </c>
+      <c r="T178" t="n">
+        <v>0</v>
+      </c>
+      <c r="U178" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S178" t="n">
+      <c r="V178" t="n">
         <v>0.22</v>
       </c>
     </row>
@@ -16851,26 +17754,31 @@
       <c r="M179" t="n">
         <v>-95.510340989257</v>
       </c>
-      <c r="N179" t="inlineStr">
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O179" t="n">
-        <v>0</v>
-      </c>
-      <c r="P179" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
-      <c r="R179" t="inlineStr">
+      <c r="R179" t="n">
+        <v>0</v>
+      </c>
+      <c r="S179" t="n">
+        <v>1</v>
+      </c>
+      <c r="T179" t="n">
+        <v>0</v>
+      </c>
+      <c r="U179" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S179" t="n">
+      <c r="V179" t="n">
         <v>-0.223</v>
       </c>
     </row>
@@ -16920,26 +17828,31 @@
       <c r="M180" t="n">
         <v>-95.51034311068101</v>
       </c>
-      <c r="N180" t="inlineStr">
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O180" t="n">
-        <v>0</v>
-      </c>
-      <c r="P180" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
-      <c r="R180" t="inlineStr">
+      <c r="R180" t="n">
+        <v>0</v>
+      </c>
+      <c r="S180" t="n">
+        <v>1</v>
+      </c>
+      <c r="T180" t="n">
+        <v>0</v>
+      </c>
+      <c r="U180" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S180" t="n">
+      <c r="V180" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -16989,26 +17902,31 @@
       <c r="M181" t="n">
         <v>-95.5124199</v>
       </c>
-      <c r="N181" t="inlineStr">
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O181" t="n">
-        <v>1</v>
-      </c>
-      <c r="P181" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
-      <c r="R181" t="inlineStr">
+      <c r="R181" t="n">
+        <v>1</v>
+      </c>
+      <c r="S181" t="n">
+        <v>0</v>
+      </c>
+      <c r="T181" t="n">
+        <v>0</v>
+      </c>
+      <c r="U181" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S181" t="n">
+      <c r="V181" t="n">
         <v>-0.308</v>
       </c>
     </row>
@@ -17058,26 +17976,31 @@
       <c r="M182" t="n">
         <v>-95.5112342</v>
       </c>
-      <c r="N182" t="inlineStr">
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O182" t="n">
-        <v>0</v>
-      </c>
-      <c r="P182" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
-      <c r="R182" t="inlineStr">
+      <c r="R182" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" t="n">
+        <v>0</v>
+      </c>
+      <c r="T182" t="n">
+        <v>0</v>
+      </c>
+      <c r="U182" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S182" t="n">
+      <c r="V182" t="n">
         <v>-0.126</v>
       </c>
     </row>
@@ -17127,26 +18050,31 @@
       <c r="M183" t="n">
         <v>-95.511237596616</v>
       </c>
-      <c r="N183" t="inlineStr">
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O183" t="n">
-        <v>0</v>
-      </c>
-      <c r="P183" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
-      <c r="R183" t="inlineStr">
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" t="n">
+        <v>1</v>
+      </c>
+      <c r="T183" t="n">
+        <v>0</v>
+      </c>
+      <c r="U183" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S183" t="n">
+      <c r="V183" t="n">
         <v>0.225</v>
       </c>
     </row>
@@ -17196,26 +18124,31 @@
       <c r="M184" t="n">
         <v>-95.511237708325</v>
       </c>
-      <c r="N184" t="inlineStr">
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q184" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O184" t="n">
-        <v>0</v>
-      </c>
-      <c r="P184" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
-      <c r="R184" t="inlineStr">
+      <c r="R184" t="n">
+        <v>0</v>
+      </c>
+      <c r="S184" t="n">
+        <v>1</v>
+      </c>
+      <c r="T184" t="n">
+        <v>0</v>
+      </c>
+      <c r="U184" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S184" t="n">
+      <c r="V184" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -17265,26 +18198,31 @@
       <c r="M185" t="n">
         <v>-95.51119199999999</v>
       </c>
-      <c r="N185" t="inlineStr">
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q185" t="inlineStr">
         <is>
           <t>tee</t>
         </is>
       </c>
-      <c r="O185" t="n">
-        <v>1</v>
-      </c>
-      <c r="P185" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
-      <c r="R185" t="inlineStr">
+      <c r="R185" t="n">
+        <v>1</v>
+      </c>
+      <c r="S185" t="n">
+        <v>0</v>
+      </c>
+      <c r="T185" t="n">
+        <v>0</v>
+      </c>
+      <c r="U185" t="inlineStr">
         <is>
           <t>off_tee</t>
         </is>
       </c>
-      <c r="S185" t="n">
+      <c r="V185" t="n">
         <v>-0.122</v>
       </c>
     </row>
@@ -17334,26 +18272,31 @@
       <c r="M186" t="n">
         <v>-95.5114501</v>
       </c>
-      <c r="N186" t="inlineStr">
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q186" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O186" t="n">
-        <v>0</v>
-      </c>
-      <c r="P186" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
-      <c r="R186" t="inlineStr">
+      <c r="R186" t="n">
+        <v>0</v>
+      </c>
+      <c r="S186" t="n">
+        <v>0</v>
+      </c>
+      <c r="T186" t="n">
+        <v>0</v>
+      </c>
+      <c r="U186" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S186" t="n">
+      <c r="V186" t="n">
         <v>-0.348</v>
       </c>
     </row>
@@ -17403,26 +18346,31 @@
       <c r="M187" t="n">
         <v>-95.51171859999999</v>
       </c>
-      <c r="N187" t="inlineStr">
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q187" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O187" t="n">
-        <v>0</v>
-      </c>
-      <c r="P187" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
-      <c r="R187" t="inlineStr">
+      <c r="R187" t="n">
+        <v>0</v>
+      </c>
+      <c r="S187" t="n">
+        <v>0</v>
+      </c>
+      <c r="T187" t="n">
+        <v>0</v>
+      </c>
+      <c r="U187" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S187" t="n">
+      <c r="V187" t="n">
         <v>-0.639</v>
       </c>
     </row>
@@ -17472,26 +18420,31 @@
       <c r="M188" t="n">
         <v>-95.51170639999999</v>
       </c>
-      <c r="N188" t="inlineStr">
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q188" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="O188" t="n">
-        <v>0</v>
-      </c>
-      <c r="P188" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
-      <c r="R188" t="inlineStr">
+      <c r="R188" t="n">
+        <v>0</v>
+      </c>
+      <c r="S188" t="n">
+        <v>0</v>
+      </c>
+      <c r="T188" t="n">
+        <v>0</v>
+      </c>
+      <c r="U188" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="S188" t="n">
+      <c r="V188" t="n">
         <v>-0.367</v>
       </c>
     </row>
@@ -17541,26 +18494,31 @@
       <c r="M189" t="n">
         <v>-95.511793</v>
       </c>
-      <c r="N189" t="inlineStr">
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q189" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O189" t="n">
-        <v>0</v>
-      </c>
-      <c r="P189" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
-      <c r="R189" t="inlineStr">
+      <c r="R189" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" t="n">
+        <v>1</v>
+      </c>
+      <c r="T189" t="n">
+        <v>0</v>
+      </c>
+      <c r="U189" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S189" t="n">
+      <c r="V189" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -17610,26 +18568,31 @@
       <c r="M190" t="n">
         <v>-95.51179681363099</v>
       </c>
-      <c r="N190" t="inlineStr">
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q190" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O190" t="n">
-        <v>0</v>
-      </c>
-      <c r="P190" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
-      <c r="R190" t="inlineStr">
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" t="n">
+        <v>1</v>
+      </c>
+      <c r="T190" t="n">
+        <v>0</v>
+      </c>
+      <c r="U190" t="inlineStr">
         <is>
           <t>putting</t>
         </is>
       </c>
-      <c r="S190" t="n">
+      <c r="V190" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -20342,7 +21305,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-14 21:32 UTC  |  Rounds: 2  Shots: 189</t>
+          <t>Date pulled: 2026-06-14 22:23 UTC  |  Rounds: 2  Shots: 189</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -21305,7 +21305,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-14 22:23 UTC  |  Rounds: 2  Shots: 189</t>
+          <t>Date pulled: 2026-06-15 12:00 UTC  |  Rounds: 2  Shots: 189</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -21305,7 +21305,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-16 12:29 UTC  |  Rounds: 2  Shots: 189</t>
+          <t>Date pulled: 2026-06-16 13:08 UTC  |  Rounds: 2  Shots: 189</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1092,6 +1092,173 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Middle</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6042</v>
+      </c>
+      <c r="F4" t="n">
+        <v>127</v>
+      </c>
+      <c r="G4" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>47</v>
+      </c>
+      <c r="J4" t="n">
+        <v>36</v>
+      </c>
+      <c r="K4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>01:57:06</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>20</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>7</v>
+      </c>
+      <c r="U4" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>7</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>231.1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>285.7</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-9.91</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-5.44</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-18.0783</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-18.7461</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-27.3458</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-18.5154</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-2.47542</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-8.83972</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>153</v>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Rain</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1103,7 +1270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA37"/>
+  <dimension ref="A1:AA46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4460,6 +4627,803 @@
         <v>-1.363</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>356.5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>285.7</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W38" t="n">
+        <v>30.055421954976</v>
+      </c>
+      <c r="X38" t="n">
+        <v>-95.51181490930701</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-0.908</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="W39" t="n">
+        <v>30.055567246083</v>
+      </c>
+      <c r="X39" t="n">
+        <v>-95.51429596951</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-2.072</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>378.2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>225.2</v>
+      </c>
+      <c r="V40" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="W40" t="n">
+        <v>30.054246458561</v>
+      </c>
+      <c r="X40" t="n">
+        <v>-95.516713141632</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-0.838</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>8</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>546</v>
+      </c>
+      <c r="U41" t="n">
+        <v>146.5</v>
+      </c>
+      <c r="V41" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="W41" t="n">
+        <v>30.059133812742</v>
+      </c>
+      <c r="X41" t="n">
+        <v>-95.51501676661699</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-2.301</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>349.9</v>
+      </c>
+      <c r="U42" t="n">
+        <v>219.7</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W42" t="n">
+        <v>30.061643297522</v>
+      </c>
+      <c r="X42" t="n">
+        <v>-95.518202253605</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-0.695</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>4</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W43" t="n">
+        <v>30.059547429238</v>
+      </c>
+      <c r="X43" t="n">
+        <v>-95.518617174475</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-0.8090000000000001</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>7</v>
+      </c>
+      <c r="E44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>350.7</v>
+      </c>
+      <c r="U44" t="n">
+        <v>197.9</v>
+      </c>
+      <c r="V44" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W44" t="n">
+        <v>30.062949778059</v>
+      </c>
+      <c r="X44" t="n">
+        <v>-95.520704012778</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>-0.668</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>381.3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>270.2</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W45" t="n">
+        <v>30.064332338697</v>
+      </c>
+      <c r="X45" t="n">
+        <v>-95.516396246634</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>-0.851</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>9</v>
+      </c>
+      <c r="E46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>429.8</v>
+      </c>
+      <c r="U46" t="n">
+        <v>272.3</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W46" t="n">
+        <v>30.061262285103</v>
+      </c>
+      <c r="X46" t="n">
+        <v>-95.513687119046</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>-0.769</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4471,7 +5435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V190"/>
+  <dimension ref="A1:V237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18593,6 +19557,3484 @@
         </is>
       </c>
       <c r="V190" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>1</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>285.7</v>
+      </c>
+      <c r="H191" t="n">
+        <v>356.5</v>
+      </c>
+      <c r="I191" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J191" t="n">
+        <v>30.057856</v>
+      </c>
+      <c r="K191" t="n">
+        <v>-95.51370350000001</v>
+      </c>
+      <c r="L191" t="n">
+        <v>30.0557791</v>
+      </c>
+      <c r="M191" t="n">
+        <v>-95.51243409999999</v>
+      </c>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R191" t="n">
+        <v>1</v>
+      </c>
+      <c r="S191" t="n">
+        <v>0</v>
+      </c>
+      <c r="T191" t="n">
+        <v>0</v>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V191" t="n">
+        <v>0.165</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" t="n">
+        <v>2</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Pitching Wedge</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="H192" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="I192" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="J192" t="n">
+        <v>30.0557791</v>
+      </c>
+      <c r="K192" t="n">
+        <v>-95.51243409999999</v>
+      </c>
+      <c r="L192" t="n">
+        <v>30.0555035</v>
+      </c>
+      <c r="M192" t="n">
+        <v>-95.51143949999999</v>
+      </c>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="n">
+        <v>0</v>
+      </c>
+      <c r="T192" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V192" t="n">
+        <v>-0.859</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>1</v>
+      </c>
+      <c r="D193" t="n">
+        <v>3</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>50 Wedge</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H193" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="I193" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J193" t="n">
+        <v>30.0555035</v>
+      </c>
+      <c r="K193" t="n">
+        <v>-95.51143949999999</v>
+      </c>
+      <c r="L193" t="n">
+        <v>30.055425291125</v>
+      </c>
+      <c r="M193" t="n">
+        <v>-95.511799550766</v>
+      </c>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V193" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>1</v>
+      </c>
+      <c r="D194" t="n">
+        <v>4</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J194" t="n">
+        <v>30.055425291125</v>
+      </c>
+      <c r="K194" t="n">
+        <v>-95.511799550766</v>
+      </c>
+      <c r="L194" t="n">
+        <v>30.055423289436</v>
+      </c>
+      <c r="M194" t="n">
+        <v>-95.511808765891</v>
+      </c>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R194" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" t="n">
+        <v>1</v>
+      </c>
+      <c r="T194" t="n">
+        <v>0</v>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V194" t="n">
+        <v>-0.747</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>1</v>
+      </c>
+      <c r="D195" t="n">
+        <v>5</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>30.055423289436</v>
+      </c>
+      <c r="K195" t="n">
+        <v>-95.511808765891</v>
+      </c>
+      <c r="L195" t="n">
+        <v>30.055421954976</v>
+      </c>
+      <c r="M195" t="n">
+        <v>-95.51181490930701</v>
+      </c>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R195" t="n">
+        <v>0</v>
+      </c>
+      <c r="S195" t="n">
+        <v>1</v>
+      </c>
+      <c r="T195" t="n">
+        <v>0</v>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V195" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>2</v>
+      </c>
+      <c r="D196" t="n">
+        <v>1</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Pitching Wedge</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="H196" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="I196" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="J196" t="n">
+        <v>30.0547489</v>
+      </c>
+      <c r="K196" t="n">
+        <v>-95.51407039999999</v>
+      </c>
+      <c r="L196" t="n">
+        <v>30.0557584</v>
+      </c>
+      <c r="M196" t="n">
+        <v>-95.5142524</v>
+      </c>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R196" t="n">
+        <v>1</v>
+      </c>
+      <c r="S196" t="n">
+        <v>0</v>
+      </c>
+      <c r="T196" t="n">
+        <v>0</v>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V196" t="n">
+        <v>-0.371</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>2</v>
+      </c>
+      <c r="D197" t="n">
+        <v>2</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H197" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I197" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J197" t="n">
+        <v>30.0557584</v>
+      </c>
+      <c r="K197" t="n">
+        <v>-95.5142524</v>
+      </c>
+      <c r="L197" t="n">
+        <v>30.0555860712</v>
+      </c>
+      <c r="M197" t="n">
+        <v>-95.514291678728</v>
+      </c>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R197" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" t="n">
+        <v>1</v>
+      </c>
+      <c r="T197" t="n">
+        <v>0</v>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V197" t="n">
+        <v>-0.135</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>2</v>
+      </c>
+      <c r="D198" t="n">
+        <v>3</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H198" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J198" t="n">
+        <v>30.0555860712</v>
+      </c>
+      <c r="K198" t="n">
+        <v>-95.514291678728</v>
+      </c>
+      <c r="L198" t="n">
+        <v>30.0555637</v>
+      </c>
+      <c r="M198" t="n">
+        <v>-95.5143008</v>
+      </c>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="n">
+        <v>1</v>
+      </c>
+      <c r="T198" t="n">
+        <v>0</v>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V198" t="n">
+        <v>-0.579</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>2</v>
+      </c>
+      <c r="D199" t="n">
+        <v>4</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J199" t="n">
+        <v>30.0555637</v>
+      </c>
+      <c r="K199" t="n">
+        <v>-95.5143008</v>
+      </c>
+      <c r="L199" t="n">
+        <v>30.0555637</v>
+      </c>
+      <c r="M199" t="n">
+        <v>-95.5143008</v>
+      </c>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R199" t="n">
+        <v>0</v>
+      </c>
+      <c r="S199" t="n">
+        <v>1</v>
+      </c>
+      <c r="T199" t="n">
+        <v>0</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V199" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>2</v>
+      </c>
+      <c r="D200" t="n">
+        <v>5</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>30.0555637</v>
+      </c>
+      <c r="K200" t="n">
+        <v>-95.5143008</v>
+      </c>
+      <c r="L200" t="n">
+        <v>30.055567246083</v>
+      </c>
+      <c r="M200" t="n">
+        <v>-95.51429596951</v>
+      </c>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="n">
+        <v>1</v>
+      </c>
+      <c r="T200" t="n">
+        <v>0</v>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V200" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>3</v>
+      </c>
+      <c r="D201" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>225.2</v>
+      </c>
+      <c r="H201" t="n">
+        <v>378.2</v>
+      </c>
+      <c r="I201" t="n">
+        <v>162.3</v>
+      </c>
+      <c r="J201" t="n">
+        <v>30.0567789</v>
+      </c>
+      <c r="K201" t="n">
+        <v>-95.514628</v>
+      </c>
+      <c r="L201" t="n">
+        <v>30.0550981</v>
+      </c>
+      <c r="M201" t="n">
+        <v>-95.51552650000001</v>
+      </c>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R201" t="n">
+        <v>1</v>
+      </c>
+      <c r="S201" t="n">
+        <v>0</v>
+      </c>
+      <c r="T201" t="n">
+        <v>0</v>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V201" t="n">
+        <v>-0.035</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>3</v>
+      </c>
+      <c r="D202" t="n">
+        <v>2</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>7 Iron</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>160.4</v>
+      </c>
+      <c r="H202" t="n">
+        <v>162.3</v>
+      </c>
+      <c r="I202" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="J202" t="n">
+        <v>30.0550981</v>
+      </c>
+      <c r="K202" t="n">
+        <v>-95.51552650000001</v>
+      </c>
+      <c r="L202" t="n">
+        <v>30.0539917</v>
+      </c>
+      <c r="M202" t="n">
+        <v>-95.5163565</v>
+      </c>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="n">
+        <v>0</v>
+      </c>
+      <c r="T202" t="n">
+        <v>0</v>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V202" t="n">
+        <v>-0.661</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>3</v>
+      </c>
+      <c r="D203" t="n">
+        <v>3</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>58 Wedge</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>39</v>
+      </c>
+      <c r="H203" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="I203" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J203" t="n">
+        <v>30.0539917</v>
+      </c>
+      <c r="K203" t="n">
+        <v>-95.5163565</v>
+      </c>
+      <c r="L203" t="n">
+        <v>30.0541606</v>
+      </c>
+      <c r="M203" t="n">
+        <v>-95.5166717</v>
+      </c>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R203" t="n">
+        <v>0</v>
+      </c>
+      <c r="S203" t="n">
+        <v>0</v>
+      </c>
+      <c r="T203" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V203" t="n">
+        <v>-0.149</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>3</v>
+      </c>
+      <c r="D204" t="n">
+        <v>4</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H204" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I204" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J204" t="n">
+        <v>30.0541606</v>
+      </c>
+      <c r="K204" t="n">
+        <v>-95.5166717</v>
+      </c>
+      <c r="L204" t="n">
+        <v>30.0542414</v>
+      </c>
+      <c r="M204" t="n">
+        <v>-95.5167107</v>
+      </c>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R204" t="n">
+        <v>0</v>
+      </c>
+      <c r="S204" t="n">
+        <v>1</v>
+      </c>
+      <c r="T204" t="n">
+        <v>0</v>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V204" t="n">
+        <v>-0.006</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>3</v>
+      </c>
+      <c r="D205" t="n">
+        <v>5</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>30.0542414</v>
+      </c>
+      <c r="K205" t="n">
+        <v>-95.5167107</v>
+      </c>
+      <c r="L205" t="n">
+        <v>30.054246458561</v>
+      </c>
+      <c r="M205" t="n">
+        <v>-95.516713141632</v>
+      </c>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R205" t="n">
+        <v>0</v>
+      </c>
+      <c r="S205" t="n">
+        <v>1</v>
+      </c>
+      <c r="T205" t="n">
+        <v>0</v>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V205" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>4</v>
+      </c>
+      <c r="D206" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>146.5</v>
+      </c>
+      <c r="H206" t="n">
+        <v>546</v>
+      </c>
+      <c r="I206" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="J206" t="n">
+        <v>30.0548844</v>
+      </c>
+      <c r="K206" t="n">
+        <v>-95.5166928</v>
+      </c>
+      <c r="L206" t="n">
+        <v>30.0560446</v>
+      </c>
+      <c r="M206" t="n">
+        <v>-95.5163184</v>
+      </c>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R206" t="n">
+        <v>1</v>
+      </c>
+      <c r="S206" t="n">
+        <v>0</v>
+      </c>
+      <c r="T206" t="n">
+        <v>0</v>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V206" t="n">
+        <v>-0.433</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>4</v>
+      </c>
+      <c r="D207" t="n">
+        <v>2</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="H207" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="I207" t="n">
+        <v>241.7</v>
+      </c>
+      <c r="J207" t="n">
+        <v>30.0560446</v>
+      </c>
+      <c r="K207" t="n">
+        <v>-95.5163184</v>
+      </c>
+      <c r="L207" t="n">
+        <v>30.0571481</v>
+      </c>
+      <c r="M207" t="n">
+        <v>-95.51511960000001</v>
+      </c>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R207" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" t="n">
+        <v>0</v>
+      </c>
+      <c r="T207" t="n">
+        <v>0</v>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V207" t="n">
+        <v>-0.162</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>4</v>
+      </c>
+      <c r="D208" t="n">
+        <v>3</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="H208" t="n">
+        <v>241.7</v>
+      </c>
+      <c r="I208" t="n">
+        <v>188.2</v>
+      </c>
+      <c r="J208" t="n">
+        <v>30.0571481</v>
+      </c>
+      <c r="K208" t="n">
+        <v>-95.51511960000001</v>
+      </c>
+      <c r="L208" t="n">
+        <v>30.0575873</v>
+      </c>
+      <c r="M208" t="n">
+        <v>-95.51494409999999</v>
+      </c>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="n">
+        <v>0</v>
+      </c>
+      <c r="T208" t="n">
+        <v>0</v>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V208" t="n">
+        <v>-0.477</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>4</v>
+      </c>
+      <c r="D209" t="n">
+        <v>4</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>6 Iron</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="H209" t="n">
+        <v>188.2</v>
+      </c>
+      <c r="I209" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="J209" t="n">
+        <v>30.0575873</v>
+      </c>
+      <c r="K209" t="n">
+        <v>-95.51494409999999</v>
+      </c>
+      <c r="L209" t="n">
+        <v>30.058434828125</v>
+      </c>
+      <c r="M209" t="n">
+        <v>-95.514599184375</v>
+      </c>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="n">
+        <v>0</v>
+      </c>
+      <c r="T209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V209" t="n">
+        <v>-0.432</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>4</v>
+      </c>
+      <c r="D210" t="n">
+        <v>5</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>58 Wedge</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="H210" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I210" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="J210" t="n">
+        <v>30.058434828125</v>
+      </c>
+      <c r="K210" t="n">
+        <v>-95.514599184375</v>
+      </c>
+      <c r="L210" t="n">
+        <v>30.0588791</v>
+      </c>
+      <c r="M210" t="n">
+        <v>-95.5153337</v>
+      </c>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="n">
+        <v>0</v>
+      </c>
+      <c r="T210" t="n">
+        <v>0</v>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V210" t="n">
+        <v>-0.626</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>4</v>
+      </c>
+      <c r="D211" t="n">
+        <v>6</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>58 Wedge</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="H211" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="I211" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J211" t="n">
+        <v>30.0588791</v>
+      </c>
+      <c r="K211" t="n">
+        <v>-95.5153337</v>
+      </c>
+      <c r="L211" t="n">
+        <v>30.0590438</v>
+      </c>
+      <c r="M211" t="n">
+        <v>-95.5150735</v>
+      </c>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R211" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" t="n">
+        <v>0</v>
+      </c>
+      <c r="T211" t="n">
+        <v>0</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V211" t="n">
+        <v>-0.206</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>4</v>
+      </c>
+      <c r="D212" t="n">
+        <v>7</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H212" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J212" t="n">
+        <v>30.0590438</v>
+      </c>
+      <c r="K212" t="n">
+        <v>-95.5150735</v>
+      </c>
+      <c r="L212" t="n">
+        <v>30.059129</v>
+      </c>
+      <c r="M212" t="n">
+        <v>-95.5150198</v>
+      </c>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="n">
+        <v>1</v>
+      </c>
+      <c r="T212" t="n">
+        <v>0</v>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V212" t="n">
+        <v>0.022</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>4</v>
+      </c>
+      <c r="D213" t="n">
+        <v>8</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>30.059129</v>
+      </c>
+      <c r="K213" t="n">
+        <v>-95.5150198</v>
+      </c>
+      <c r="L213" t="n">
+        <v>30.059133812742</v>
+      </c>
+      <c r="M213" t="n">
+        <v>-95.51501676661699</v>
+      </c>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="n">
+        <v>1</v>
+      </c>
+      <c r="T213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V213" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>5</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>219.7</v>
+      </c>
+      <c r="H214" t="n">
+        <v>349.9</v>
+      </c>
+      <c r="I214" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="J214" t="n">
+        <v>30.0603278</v>
+      </c>
+      <c r="K214" t="n">
+        <v>-95.5152453</v>
+      </c>
+      <c r="L214" t="n">
+        <v>30.0610099</v>
+      </c>
+      <c r="M214" t="n">
+        <v>-95.51717840000001</v>
+      </c>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R214" t="n">
+        <v>1</v>
+      </c>
+      <c r="S214" t="n">
+        <v>0</v>
+      </c>
+      <c r="T214" t="n">
+        <v>0</v>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V214" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>5</v>
+      </c>
+      <c r="D215" t="n">
+        <v>2</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Pitching Wedge</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="H215" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="I215" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="J215" t="n">
+        <v>30.0610099</v>
+      </c>
+      <c r="K215" t="n">
+        <v>-95.51717840000001</v>
+      </c>
+      <c r="L215" t="n">
+        <v>30.0617101</v>
+      </c>
+      <c r="M215" t="n">
+        <v>-95.51789479999999</v>
+      </c>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R215" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" t="n">
+        <v>0</v>
+      </c>
+      <c r="T215" t="n">
+        <v>0</v>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V215" t="n">
+        <v>-0.424</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>5</v>
+      </c>
+      <c r="D216" t="n">
+        <v>3</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Pitching Wedge</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="H216" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="I216" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J216" t="n">
+        <v>30.0617101</v>
+      </c>
+      <c r="K216" t="n">
+        <v>-95.51789479999999</v>
+      </c>
+      <c r="L216" t="n">
+        <v>30.0616296</v>
+      </c>
+      <c r="M216" t="n">
+        <v>-95.5182028</v>
+      </c>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R216" t="n">
+        <v>0</v>
+      </c>
+      <c r="S216" t="n">
+        <v>0</v>
+      </c>
+      <c r="T216" t="n">
+        <v>0</v>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V216" t="n">
+        <v>0.461</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>5</v>
+      </c>
+      <c r="D217" t="n">
+        <v>4</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>1</v>
+      </c>
+      <c r="H217" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J217" t="n">
+        <v>30.0616296</v>
+      </c>
+      <c r="K217" t="n">
+        <v>-95.5182028</v>
+      </c>
+      <c r="L217" t="n">
+        <v>30.061637818513</v>
+      </c>
+      <c r="M217" t="n">
+        <v>-95.518202472163</v>
+      </c>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R217" t="n">
+        <v>0</v>
+      </c>
+      <c r="S217" t="n">
+        <v>1</v>
+      </c>
+      <c r="T217" t="n">
+        <v>0</v>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V217" t="n">
+        <v>-0.747</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>5</v>
+      </c>
+      <c r="D218" t="n">
+        <v>5</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>30.061637818513</v>
+      </c>
+      <c r="K218" t="n">
+        <v>-95.518202472163</v>
+      </c>
+      <c r="L218" t="n">
+        <v>30.061643297522</v>
+      </c>
+      <c r="M218" t="n">
+        <v>-95.518202253605</v>
+      </c>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R218" t="n">
+        <v>0</v>
+      </c>
+      <c r="S218" t="n">
+        <v>1</v>
+      </c>
+      <c r="T218" t="n">
+        <v>0</v>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V218" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>6</v>
+      </c>
+      <c r="D219" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>6 Iron</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="H219" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="I219" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="J219" t="n">
+        <v>30.0608968</v>
+      </c>
+      <c r="K219" t="n">
+        <v>-95.5183858</v>
+      </c>
+      <c r="L219" t="n">
+        <v>30.0595359</v>
+      </c>
+      <c r="M219" t="n">
+        <v>-95.5183689</v>
+      </c>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R219" t="n">
+        <v>1</v>
+      </c>
+      <c r="S219" t="n">
+        <v>0</v>
+      </c>
+      <c r="T219" t="n">
+        <v>0</v>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V219" t="n">
+        <v>-0.467</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>6</v>
+      </c>
+      <c r="D220" t="n">
+        <v>2</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="H220" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="I220" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J220" t="n">
+        <v>30.0595359</v>
+      </c>
+      <c r="K220" t="n">
+        <v>-95.5183689</v>
+      </c>
+      <c r="L220" t="n">
+        <v>30.0594778</v>
+      </c>
+      <c r="M220" t="n">
+        <v>-95.5187507</v>
+      </c>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R220" t="n">
+        <v>0</v>
+      </c>
+      <c r="S220" t="n">
+        <v>0</v>
+      </c>
+      <c r="T220" t="n">
+        <v>0</v>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="V220" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>6</v>
+      </c>
+      <c r="D221" t="n">
+        <v>3</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H221" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J221" t="n">
+        <v>30.0594778</v>
+      </c>
+      <c r="K221" t="n">
+        <v>-95.5187507</v>
+      </c>
+      <c r="L221" t="n">
+        <v>30.0595446</v>
+      </c>
+      <c r="M221" t="n">
+        <v>-95.5186226</v>
+      </c>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" t="n">
+        <v>1</v>
+      </c>
+      <c r="T221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V221" t="n">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>6</v>
+      </c>
+      <c r="D222" t="n">
+        <v>4</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>30.0595446</v>
+      </c>
+      <c r="K222" t="n">
+        <v>-95.5186226</v>
+      </c>
+      <c r="L222" t="n">
+        <v>30.059547429238</v>
+      </c>
+      <c r="M222" t="n">
+        <v>-95.518617174475</v>
+      </c>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="n">
+        <v>1</v>
+      </c>
+      <c r="T222" t="n">
+        <v>0</v>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V222" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>7</v>
+      </c>
+      <c r="D223" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>197.9</v>
+      </c>
+      <c r="H223" t="n">
+        <v>350.7</v>
+      </c>
+      <c r="I223" t="n">
+        <v>192.8</v>
+      </c>
+      <c r="J223" t="n">
+        <v>30.0602436</v>
+      </c>
+      <c r="K223" t="n">
+        <v>-95.5195523</v>
+      </c>
+      <c r="L223" t="n">
+        <v>30.0618633</v>
+      </c>
+      <c r="M223" t="n">
+        <v>-95.5193697</v>
+      </c>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R223" t="n">
+        <v>1</v>
+      </c>
+      <c r="S223" t="n">
+        <v>0</v>
+      </c>
+      <c r="T223" t="n">
+        <v>0</v>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V223" t="n">
+        <v>-0.258</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>7</v>
+      </c>
+      <c r="D224" t="n">
+        <v>2</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="H224" t="n">
+        <v>192.8</v>
+      </c>
+      <c r="I224" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="J224" t="n">
+        <v>30.0618633</v>
+      </c>
+      <c r="K224" t="n">
+        <v>-95.5193697</v>
+      </c>
+      <c r="L224" t="n">
+        <v>30.062563</v>
+      </c>
+      <c r="M224" t="n">
+        <v>-95.5203631</v>
+      </c>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="S224" t="n">
+        <v>0</v>
+      </c>
+      <c r="T224" t="n">
+        <v>0</v>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V224" t="n">
+        <v>-0.316</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>7</v>
+      </c>
+      <c r="D225" t="n">
+        <v>3</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>58 Wedge</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="H225" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="I225" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J225" t="n">
+        <v>30.062563</v>
+      </c>
+      <c r="K225" t="n">
+        <v>-95.5203631</v>
+      </c>
+      <c r="L225" t="n">
+        <v>30.0628274</v>
+      </c>
+      <c r="M225" t="n">
+        <v>-95.52066430000001</v>
+      </c>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="n">
+        <v>0</v>
+      </c>
+      <c r="T225" t="n">
+        <v>0</v>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V225" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>7</v>
+      </c>
+      <c r="D226" t="n">
+        <v>4</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H226" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J226" t="n">
+        <v>30.0628274</v>
+      </c>
+      <c r="K226" t="n">
+        <v>-95.52066430000001</v>
+      </c>
+      <c r="L226" t="n">
+        <v>30.0629445</v>
+      </c>
+      <c r="M226" t="n">
+        <v>-95.5207023</v>
+      </c>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R226" t="n">
+        <v>0</v>
+      </c>
+      <c r="S226" t="n">
+        <v>1</v>
+      </c>
+      <c r="T226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V226" t="n">
+        <v>0.093</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>7</v>
+      </c>
+      <c r="D227" t="n">
+        <v>5</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="n">
+        <v>30.0629445</v>
+      </c>
+      <c r="K227" t="n">
+        <v>-95.5207023</v>
+      </c>
+      <c r="L227" t="n">
+        <v>30.062949778059</v>
+      </c>
+      <c r="M227" t="n">
+        <v>-95.520704012778</v>
+      </c>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R227" t="n">
+        <v>0</v>
+      </c>
+      <c r="S227" t="n">
+        <v>1</v>
+      </c>
+      <c r="T227" t="n">
+        <v>0</v>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V227" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>8</v>
+      </c>
+      <c r="D228" t="n">
+        <v>1</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>270.2</v>
+      </c>
+      <c r="H228" t="n">
+        <v>381.3</v>
+      </c>
+      <c r="I228" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="J228" t="n">
+        <v>30.064010603641</v>
+      </c>
+      <c r="K228" t="n">
+        <v>-95.520000569522</v>
+      </c>
+      <c r="L228" t="n">
+        <v>30.064077052589</v>
+      </c>
+      <c r="M228" t="n">
+        <v>-95.517434030771</v>
+      </c>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R228" t="n">
+        <v>1</v>
+      </c>
+      <c r="S228" t="n">
+        <v>0</v>
+      </c>
+      <c r="T228" t="n">
+        <v>0</v>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V228" t="n">
+        <v>0.128</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>8</v>
+      </c>
+      <c r="D229" t="n">
+        <v>2</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>50 Wedge</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>120</v>
+      </c>
+      <c r="H229" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="I229" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="J229" t="n">
+        <v>30.064077052589</v>
+      </c>
+      <c r="K229" t="n">
+        <v>-95.517434030771</v>
+      </c>
+      <c r="L229" t="n">
+        <v>30.064489383276</v>
+      </c>
+      <c r="M229" t="n">
+        <v>-95.516397692263</v>
+      </c>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="R229" t="n">
+        <v>0</v>
+      </c>
+      <c r="S229" t="n">
+        <v>0</v>
+      </c>
+      <c r="T229" t="n">
+        <v>0</v>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V229" t="n">
+        <v>-0.546</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>8</v>
+      </c>
+      <c r="D230" t="n">
+        <v>3</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H230" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I230" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J230" t="n">
+        <v>30.064489383276</v>
+      </c>
+      <c r="K230" t="n">
+        <v>-95.516397692263</v>
+      </c>
+      <c r="L230" t="n">
+        <v>30.064346043945</v>
+      </c>
+      <c r="M230" t="n">
+        <v>-95.516396372793</v>
+      </c>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R230" t="n">
+        <v>0</v>
+      </c>
+      <c r="S230" t="n">
+        <v>0</v>
+      </c>
+      <c r="T230" t="n">
+        <v>0</v>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="V230" t="n">
+        <v>0.301</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>8</v>
+      </c>
+      <c r="D231" t="n">
+        <v>4</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>1</v>
+      </c>
+      <c r="H231" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J231" t="n">
+        <v>30.064346043945</v>
+      </c>
+      <c r="K231" t="n">
+        <v>-95.516396372793</v>
+      </c>
+      <c r="L231" t="n">
+        <v>30.064337820796</v>
+      </c>
+      <c r="M231" t="n">
+        <v>-95.516396297098</v>
+      </c>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R231" t="n">
+        <v>0</v>
+      </c>
+      <c r="S231" t="n">
+        <v>1</v>
+      </c>
+      <c r="T231" t="n">
+        <v>0</v>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V231" t="n">
+        <v>-0.747</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>8</v>
+      </c>
+      <c r="D232" t="n">
+        <v>5</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" t="n">
+        <v>30.064337820796</v>
+      </c>
+      <c r="K232" t="n">
+        <v>-95.516396297098</v>
+      </c>
+      <c r="L232" t="n">
+        <v>30.064332338697</v>
+      </c>
+      <c r="M232" t="n">
+        <v>-95.516396246634</v>
+      </c>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R232" t="n">
+        <v>0</v>
+      </c>
+      <c r="S232" t="n">
+        <v>1</v>
+      </c>
+      <c r="T232" t="n">
+        <v>0</v>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V232" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>9</v>
+      </c>
+      <c r="D233" t="n">
+        <v>1</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>272.3</v>
+      </c>
+      <c r="H233" t="n">
+        <v>429.8</v>
+      </c>
+      <c r="I233" t="n">
+        <v>159.7</v>
+      </c>
+      <c r="J233" t="n">
+        <v>30.064578465049</v>
+      </c>
+      <c r="K233" t="n">
+        <v>-95.515100508928</v>
+      </c>
+      <c r="L233" t="n">
+        <v>30.062424810919</v>
+      </c>
+      <c r="M233" t="n">
+        <v>-95.514392741024</v>
+      </c>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R233" t="n">
+        <v>1</v>
+      </c>
+      <c r="S233" t="n">
+        <v>0</v>
+      </c>
+      <c r="T233" t="n">
+        <v>0</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V233" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>9</v>
+      </c>
+      <c r="D234" t="n">
+        <v>2</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>144.4</v>
+      </c>
+      <c r="H234" t="n">
+        <v>159.7</v>
+      </c>
+      <c r="I234" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="J234" t="n">
+        <v>30.062424810919</v>
+      </c>
+      <c r="K234" t="n">
+        <v>-95.514392741024</v>
+      </c>
+      <c r="L234" t="n">
+        <v>30.061475064157</v>
+      </c>
+      <c r="M234" t="n">
+        <v>-95.51356896758099</v>
+      </c>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="R234" t="n">
+        <v>0</v>
+      </c>
+      <c r="S234" t="n">
+        <v>0</v>
+      </c>
+      <c r="T234" t="n">
+        <v>0</v>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V234" t="n">
+        <v>-0.526</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>9</v>
+      </c>
+      <c r="D235" t="n">
+        <v>3</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>27</v>
+      </c>
+      <c r="H235" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="I235" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J235" t="n">
+        <v>30.061475064157</v>
+      </c>
+      <c r="K235" t="n">
+        <v>-95.51356896758099</v>
+      </c>
+      <c r="L235" t="n">
+        <v>30.061274638266</v>
+      </c>
+      <c r="M235" t="n">
+        <v>-95.513680259626</v>
+      </c>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R235" t="n">
+        <v>0</v>
+      </c>
+      <c r="S235" t="n">
+        <v>0</v>
+      </c>
+      <c r="T235" t="n">
+        <v>0</v>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="V235" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>9</v>
+      </c>
+      <c r="D236" t="n">
+        <v>4</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>1</v>
+      </c>
+      <c r="H236" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I236" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J236" t="n">
+        <v>30.061274638266</v>
+      </c>
+      <c r="K236" t="n">
+        <v>-95.513680259626</v>
+      </c>
+      <c r="L236" t="n">
+        <v>30.061267226368</v>
+      </c>
+      <c r="M236" t="n">
+        <v>-95.513684375278</v>
+      </c>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R236" t="n">
+        <v>0</v>
+      </c>
+      <c r="S236" t="n">
+        <v>1</v>
+      </c>
+      <c r="T236" t="n">
+        <v>0</v>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V236" t="n">
+        <v>-0.747</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>28154206</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>9</v>
+      </c>
+      <c r="D237" t="n">
+        <v>5</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" t="n">
+        <v>30.061267226368</v>
+      </c>
+      <c r="K237" t="n">
+        <v>-95.513684375278</v>
+      </c>
+      <c r="L237" t="n">
+        <v>30.061262285103</v>
+      </c>
+      <c r="M237" t="n">
+        <v>-95.513687119046</v>
+      </c>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R237" t="n">
+        <v>0</v>
+      </c>
+      <c r="S237" t="n">
+        <v>1</v>
+      </c>
+      <c r="T237" t="n">
+        <v>0</v>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V237" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -18732,13 +23174,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>263.8</v>
+        <v>264.2</v>
       </c>
       <c r="F2" t="n">
-        <v>263.8</v>
+        <v>264.2</v>
       </c>
       <c r="G2" t="n">
-        <v>268.1</v>
+        <v>270.5</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -18747,17 +23189,17 @@
         <v>285.2</v>
       </c>
       <c r="L2" t="n">
-        <v>262.253</v>
+        <v>265.412</v>
       </c>
       <c r="M2" t="n">
-        <v>269.271</v>
+        <v>271.155</v>
       </c>
       <c r="N2" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -18817,12 +23259,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>5 Wood</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -18836,45 +23278,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>207.4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>207.4</v>
-      </c>
+        <v>200.1</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>220.5</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>220.5</v>
-      </c>
-      <c r="L4" t="n">
-        <v>220.471</v>
-      </c>
-      <c r="M4" t="n">
-        <v>220.471</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+        <v>141.5</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5 Wood</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -18888,24 +23320,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>203.2</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+        <v>196.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>196.3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>184.1</v>
+      </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>220.5</v>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>141.5</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+        <v>220.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>200.447</v>
+      </c>
+      <c r="M5" t="n">
+        <v>211.369</v>
+      </c>
+      <c r="N5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -18930,38 +23374,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>158.4</v>
+        <v>157.4</v>
       </c>
       <c r="F6" t="n">
-        <v>158.4</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>157.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>165</v>
+      </c>
       <c r="H6" t="n">
         <v>160.3</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>160.3</v>
+        <v>165</v>
       </c>
       <c r="L6" t="n">
-        <v>160.338</v>
+        <v>162.432</v>
       </c>
       <c r="M6" t="n">
-        <v>160.338</v>
+        <v>163.829</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
+        <v>1.4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5 Iron</t>
+          <t>7 Iron</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -18980,44 +23428,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>155.5</v>
+        <v>155.4</v>
       </c>
       <c r="F7" t="n">
-        <v>155.5</v>
+        <v>155.4</v>
       </c>
       <c r="G7" t="n">
-        <v>164.9</v>
+        <v>161.9</v>
       </c>
       <c r="H7" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="I7" t="n">
-        <v>172</v>
+        <v>134.1</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>184</v>
+        <v>161.9</v>
       </c>
       <c r="L7" t="n">
-        <v>152.576</v>
+        <v>150.417</v>
       </c>
       <c r="M7" t="n">
-        <v>170.43</v>
+        <v>157.992</v>
       </c>
       <c r="N7" t="n">
-        <v>17.9</v>
+        <v>7.6</v>
       </c>
       <c r="O7" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="P7" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7 Iron</t>
+          <t>5 Iron</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -19036,38 +23484,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>149</v>
+        <v>147.8</v>
       </c>
       <c r="F8" t="n">
-        <v>149</v>
+        <v>147.8</v>
       </c>
       <c r="G8" t="n">
-        <v>161.9</v>
+        <v>164.9</v>
       </c>
       <c r="H8" t="n">
-        <v>151.1</v>
+        <v>155.1</v>
       </c>
       <c r="I8" t="n">
-        <v>134.1</v>
+        <v>163.5</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>161.9</v>
+        <v>184</v>
       </c>
       <c r="L8" t="n">
-        <v>147.497</v>
+        <v>148.758</v>
       </c>
       <c r="M8" t="n">
-        <v>151.478</v>
+        <v>169.921</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>21.2</v>
       </c>
       <c r="O8" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="P8" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -19092,7 +23540,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>140.5</v>
+        <v>141.3</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -19188,38 +23636,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>111.7</v>
+        <v>112.7</v>
       </c>
       <c r="F11" t="n">
-        <v>111.7</v>
+        <v>112.7</v>
       </c>
       <c r="G11" t="n">
-        <v>131.2</v>
+        <v>129</v>
       </c>
       <c r="H11" t="n">
-        <v>112.2</v>
+        <v>111.5</v>
       </c>
       <c r="I11" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
         <v>131.2</v>
       </c>
       <c r="L11" t="n">
-        <v>109.448</v>
+        <v>112.531</v>
       </c>
       <c r="M11" t="n">
-        <v>121.677</v>
+        <v>121.317</v>
       </c>
       <c r="N11" t="n">
-        <v>12.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="P11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -19244,36 +23692,36 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100.3</v>
+        <v>107.6</v>
       </c>
       <c r="F12" t="n">
-        <v>100.3</v>
+        <v>107.6</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>98</v>
+        <v>113.5</v>
       </c>
       <c r="I12" t="n">
         <v>104.5</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>104.5</v>
+        <v>120.2</v>
       </c>
       <c r="L12" t="n">
-        <v>100.952</v>
+        <v>103.858</v>
       </c>
       <c r="M12" t="n">
-        <v>102.889</v>
+        <v>112.338</v>
       </c>
       <c r="N12" t="n">
-        <v>1.9</v>
+        <v>8.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -19298,34 +23746,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>88.8</v>
+        <v>91.2</v>
       </c>
       <c r="F13" t="n">
-        <v>88.8</v>
+        <v>91.2</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>91.40000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>71.3</v>
+        <v>91.2</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>94.2</v>
+        <v>94.3</v>
       </c>
       <c r="L13" t="n">
-        <v>79.5625</v>
+        <v>86.3596</v>
       </c>
       <c r="M13" t="n">
-        <v>90.8301</v>
+        <v>93.34439999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>11.3</v>
+        <v>7</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -19379,7 +23827,7 @@
         <v>100</v>
       </c>
       <c r="P14" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -19393,7 +23841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19444,7 +23892,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>28063887</v>
+        <v>28154206</v>
       </c>
       <c r="B2" t="n">
         <v>-18.0783</v>
@@ -19453,7 +23901,7 @@
         <v>-18.7461</v>
       </c>
       <c r="D2" t="n">
-        <v>-27.3459</v>
+        <v>-27.3458</v>
       </c>
       <c r="E2" t="n">
         <v>-18.5154</v>
@@ -19467,24 +23915,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-18.0783</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-18.7461</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-27.3459</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-18.5154</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-2.47542</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-8.83972</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>27924130</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B4" t="n">
         <v>-20.4148</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C4" t="n">
         <v>-7.49223</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>-30</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>-30</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>-4.95085</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G4" t="n">
         <v>-10.2852</v>
       </c>
     </row>
@@ -19531,7 +24002,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-21.9</v>
+        <v>-21.6</v>
       </c>
     </row>
     <row r="5">
@@ -19541,7 +24012,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-4.3</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="6">
@@ -19551,7 +24022,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-12.1</v>
+        <v>-12.6</v>
       </c>
     </row>
     <row r="7">
@@ -19561,7 +24032,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-3.4</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="8">
@@ -19571,7 +24042,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2.2</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="9">
@@ -19592,7 +24063,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>42.9</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="12">
@@ -19602,7 +24073,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27.8</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="13">
@@ -19622,7 +24093,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="15">
@@ -19632,7 +24103,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18.2</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="16">
@@ -19652,7 +24123,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="18">
@@ -19662,7 +24133,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="19">
@@ -19672,7 +24143,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>37</v>
+        <v>31.33</v>
       </c>
     </row>
     <row r="20">
@@ -19700,7 +24171,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -19710,7 +24181,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -19720,7 +24191,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
@@ -19730,7 +24201,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27">
@@ -19750,7 +24221,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -19770,7 +24241,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -19780,7 +24251,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5593.9</v>
+        <v>7071.18</v>
       </c>
     </row>
     <row r="32">
@@ -19800,7 +24271,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34">
@@ -19810,7 +24281,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35">
@@ -19820,7 +24291,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>52.41</v>
+        <v>50.67</v>
       </c>
     </row>
     <row r="36">
@@ -19850,7 +24321,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
@@ -19860,7 +24331,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
@@ -19870,7 +24341,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>795.7</v>
+        <v>964.01</v>
       </c>
     </row>
     <row r="41">
@@ -19880,7 +24351,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>167.78</v>
+        <v>168.31</v>
       </c>
     </row>
     <row r="42">
@@ -19890,7 +24361,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>51.63</v>
+        <v>54.53</v>
       </c>
     </row>
     <row r="43">
@@ -19977,7 +24448,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52">
@@ -19987,7 +24458,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53">
@@ -19997,7 +24468,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54">
@@ -20007,7 +24478,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55">
@@ -20017,7 +24488,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -20037,7 +24508,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -20047,7 +24518,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59">
@@ -20057,7 +24528,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60">
@@ -20067,7 +24538,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>188</v>
+        <v>238</v>
       </c>
     </row>
     <row r="61">
@@ -20077,7 +24548,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1862.75</v>
+        <v>2408.26</v>
       </c>
     </row>
     <row r="62">
@@ -20087,7 +24558,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>227.14</v>
+        <v>264.36</v>
       </c>
     </row>
     <row r="63">
@@ -20097,7 +24568,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>147.79</v>
+        <v>170.91</v>
       </c>
     </row>
     <row r="64">
@@ -20107,7 +24578,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -20184,7 +24655,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73">
@@ -20204,7 +24675,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75">
@@ -20224,7 +24695,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77">
@@ -20244,7 +24715,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79">
@@ -20254,7 +24725,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="80">
@@ -20264,7 +24735,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>203</v>
+        <v>244.28</v>
       </c>
     </row>
     <row r="81">
@@ -20274,7 +24745,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>160.81</v>
+        <v>202.09</v>
       </c>
     </row>
     <row r="82">
@@ -20284,7 +24755,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>146.93</v>
+        <v>176.83</v>
       </c>
     </row>
     <row r="83">
@@ -20668,7 +25139,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="122">
@@ -20678,7 +25149,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123">
@@ -20688,7 +25159,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
     </row>
     <row r="124">
@@ -20698,7 +25169,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="125">
@@ -20708,7 +25179,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="126">
@@ -20718,7 +25189,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127">
@@ -20748,7 +25219,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-5.67</v>
+        <v>-9.69</v>
       </c>
     </row>
     <row r="130">
@@ -20795,7 +25266,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135">
@@ -20805,7 +25276,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="136">
@@ -20815,7 +25286,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137">
@@ -20825,7 +25296,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138">
@@ -20835,7 +25306,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="139">
@@ -20845,7 +25316,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="140">
@@ -20855,7 +25326,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
     </row>
     <row r="141">
@@ -20865,7 +25336,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="142">
@@ -20875,7 +25346,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="143">
@@ -20885,7 +25356,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="144">
@@ -20930,7 +25401,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -20941,7 +25412,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>36 / 189</t>
+          <t>45 / 236</t>
         </is>
       </c>
     </row>
@@ -20953,7 +25424,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-06 -&gt; 2026-06-14</t>
+          <t>2026-06-06 -&gt; 2026-06-19</t>
         </is>
       </c>
     </row>
@@ -20976,7 +25447,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
@@ -20986,7 +25457,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -20996,7 +25467,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-21.9</v>
+        <v>-18.1</v>
       </c>
     </row>
     <row r="10">
@@ -21006,7 +25477,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-4.25</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="11">
@@ -21016,7 +25487,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-12.15</v>
+        <v>-10.37</v>
       </c>
     </row>
     <row r="12">
@@ -21026,7 +25497,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>-3.35</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="13">
@@ -21036,7 +25507,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-2.15</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="14">
@@ -21046,7 +25517,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-20.52</v>
+        <v>-16.98</v>
       </c>
     </row>
     <row r="15">
@@ -21056,7 +25527,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.8</v>
+        <v>25.93</v>
       </c>
     </row>
     <row r="16">
@@ -21066,7 +25537,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>42.85</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="17">
@@ -21086,7 +25557,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>11.15</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="19">
@@ -21096,7 +25567,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>37</v>
+        <v>31.33</v>
       </c>
     </row>
     <row r="20">
@@ -21106,7 +25577,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="21">
@@ -21116,7 +25587,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="22">
@@ -21126,7 +25597,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="23">
@@ -21136,7 +25607,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>218.7</v>
+        <v>222.83</v>
       </c>
     </row>
     <row r="24">
@@ -21146,7 +25617,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>277.75</v>
+        <v>280.4</v>
       </c>
     </row>
     <row r="25">
@@ -21156,7 +25627,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="26">
@@ -21166,7 +25637,7 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>-24.26</v>
+        <v>-22.34</v>
       </c>
     </row>
     <row r="27">
@@ -21176,7 +25647,7 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>-3.71</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="29">
@@ -21208,7 +25679,7 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="32">
@@ -21218,7 +25689,7 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>18.2</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="33">
@@ -21238,7 +25709,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27.8</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="35">
@@ -21248,7 +25719,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>42.9</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="36">
@@ -21258,7 +25729,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="37">
@@ -21268,7 +25739,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>11.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="38">
@@ -21278,7 +25749,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>37</v>
+        <v>31.33</v>
       </c>
     </row>
     <row r="40">
@@ -21305,7 +25776,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-16 13:08 UTC  |  Rounds: 2  Shots: 189</t>
+          <t>Date pulled: 2026-06-19 23:48 UTC  |  Rounds: 3  Shots: 236</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1259,6 +1259,173 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6586</v>
+      </c>
+      <c r="F5" t="n">
+        <v>133</v>
+      </c>
+      <c r="G5" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I5" t="n">
+        <v>89</v>
+      </c>
+      <c r="J5" t="n">
+        <v>72</v>
+      </c>
+      <c r="K5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>04:19:09</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>39</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>14</v>
+      </c>
+      <c r="U5" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="V5" t="n">
+        <v>12</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>231.3</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>294.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-15.58</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-5.72</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-16.3353</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-15.2098</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-22.4244</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-13.0907</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-1.41453</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-16.8471</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>188</v>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Partly cloudy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1270,7 +1437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA46"/>
+  <dimension ref="A1:AA64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5424,6 +5591,1576 @@
         <v>-0.769</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>360.1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>294.6</v>
+      </c>
+      <c r="V47" t="n">
+        <v>6</v>
+      </c>
+      <c r="W47" t="n">
+        <v>30.055411206014</v>
+      </c>
+      <c r="X47" t="n">
+        <v>-95.511839020529</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>-0.681</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>4</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W48" t="n">
+        <v>30.05563372276</v>
+      </c>
+      <c r="X48" t="n">
+        <v>-95.514369293519</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>-0.834</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>366</v>
+      </c>
+      <c r="U49" t="n">
+        <v>175.8</v>
+      </c>
+      <c r="V49" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="W49" t="n">
+        <v>30.054355296203</v>
+      </c>
+      <c r="X49" t="n">
+        <v>-95.516669417372</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>-0.859</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="n">
+        <v>5</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="n">
+        <v>538.5</v>
+      </c>
+      <c r="U50" t="n">
+        <v>277.4</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="W50" t="n">
+        <v>30.059030437092</v>
+      </c>
+      <c r="X50" t="n">
+        <v>-95.51500383920801</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0.029</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>4</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>362.9</v>
+      </c>
+      <c r="U51" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="W51" t="n">
+        <v>30.061686032225</v>
+      </c>
+      <c r="X51" t="n">
+        <v>-95.51821317595299</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.136</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>6</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W52" t="n">
+        <v>30.05960947786</v>
+      </c>
+      <c r="X52" t="n">
+        <v>-95.51868000478299</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-0.8070000000000001</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>7</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>5</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>341.5</v>
+      </c>
+      <c r="U53" t="n">
+        <v>200.9</v>
+      </c>
+      <c r="V53" t="n">
+        <v>5</v>
+      </c>
+      <c r="W53" t="n">
+        <v>30.062850520177</v>
+      </c>
+      <c r="X53" t="n">
+        <v>-95.52068827932</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-0.679</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" t="n">
+        <v>4</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>6</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>383.8</v>
+      </c>
+      <c r="U54" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="V54" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W54" t="n">
+        <v>30.064334778033</v>
+      </c>
+      <c r="X54" t="n">
+        <v>-95.516406441849</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>-1.68</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>9</v>
+      </c>
+      <c r="E55" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>436.7</v>
+      </c>
+      <c r="U55" t="n">
+        <v>262.4</v>
+      </c>
+      <c r="V55" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="W55" t="n">
+        <v>30.06132207949</v>
+      </c>
+      <c r="X55" t="n">
+        <v>-95.513664607349</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-0.751</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>4</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="n">
+        <v>384.7</v>
+      </c>
+      <c r="U56" t="n">
+        <v>258.3</v>
+      </c>
+      <c r="V56" t="n">
+        <v>5</v>
+      </c>
+      <c r="W56" t="n">
+        <v>30.057790742624</v>
+      </c>
+      <c r="X56" t="n">
+        <v>-95.508962374848</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0.194</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>151.7</v>
+      </c>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W57" t="n">
+        <v>30.059005195483</v>
+      </c>
+      <c r="X57" t="n">
+        <v>-95.50677836126999</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-1.838</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>12</v>
+      </c>
+      <c r="E58" t="n">
+        <v>5</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>6</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>441</v>
+      </c>
+      <c r="U58" t="n">
+        <v>272.1</v>
+      </c>
+      <c r="V58" t="n">
+        <v>9</v>
+      </c>
+      <c r="W58" t="n">
+        <v>30.061896957281</v>
+      </c>
+      <c r="X58" t="n">
+        <v>-95.50343808710301</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-1.491</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>13</v>
+      </c>
+      <c r="E59" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>6</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="n">
+        <v>399.5</v>
+      </c>
+      <c r="U59" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="V59" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="W59" t="n">
+        <v>30.061055362295</v>
+      </c>
+      <c r="X59" t="n">
+        <v>-95.509164412917</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>-1.482</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>14</v>
+      </c>
+      <c r="E60" t="n">
+        <v>5</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>7</v>
+      </c>
+      <c r="H60" t="n">
+        <v>2</v>
+      </c>
+      <c r="I60" t="n">
+        <v>2</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>499.8</v>
+      </c>
+      <c r="U60" t="n">
+        <v>213.7</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W60" t="n">
+        <v>30.065405271108</v>
+      </c>
+      <c r="X60" t="n">
+        <v>-95.506673302544</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>-1.834</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>15</v>
+      </c>
+      <c r="E61" t="n">
+        <v>4</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>6</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2</v>
+      </c>
+      <c r="J61" t="n">
+        <v>3</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>375.2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>211.7</v>
+      </c>
+      <c r="V61" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W61" t="n">
+        <v>30.063650072226</v>
+      </c>
+      <c r="X61" t="n">
+        <v>-95.509570339517</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>16</v>
+      </c>
+      <c r="E62" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>4</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>3</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>151.1</v>
+      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="W62" t="n">
+        <v>30.066546804935</v>
+      </c>
+      <c r="X62" t="n">
+        <v>-95.51033422506001</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-1.019</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>17</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>4</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>243.9</v>
+      </c>
+      <c r="U63" t="n">
+        <v>257.8</v>
+      </c>
+      <c r="V63" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="W63" t="n">
+        <v>30.064095369347</v>
+      </c>
+      <c r="X63" t="n">
+        <v>-95.511335274142</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-0.531</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>WindRose GC</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>18</v>
+      </c>
+      <c r="E64" t="n">
+        <v>4</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>arccos</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>4</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>462.6</v>
+      </c>
+      <c r="U64" t="n">
+        <v>293.4</v>
+      </c>
+      <c r="V64" t="n">
+        <v>5</v>
+      </c>
+      <c r="W64" t="n">
+        <v>30.060546277607</v>
+      </c>
+      <c r="X64" t="n">
+        <v>-95.51178746450201</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0.184</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5435,7 +7172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V237"/>
+  <dimension ref="A1:V326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23035,6 +24772,6592 @@
         </is>
       </c>
       <c r="V237" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>1</v>
+      </c>
+      <c r="D238" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>294.6</v>
+      </c>
+      <c r="H238" t="n">
+        <v>360.1</v>
+      </c>
+      <c r="I238" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="J238" t="n">
+        <v>30.0579279</v>
+      </c>
+      <c r="K238" t="n">
+        <v>-95.51364220000001</v>
+      </c>
+      <c r="L238" t="n">
+        <v>30.055669254839</v>
+      </c>
+      <c r="M238" t="n">
+        <v>-95.51262939999999</v>
+      </c>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R238" t="n">
+        <v>1</v>
+      </c>
+      <c r="S238" t="n">
+        <v>0</v>
+      </c>
+      <c r="T238" t="n">
+        <v>0</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V238" t="n">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>1</v>
+      </c>
+      <c r="D239" t="n">
+        <v>2</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>58 Wedge</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="H239" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I239" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="J239" t="n">
+        <v>30.055669254839</v>
+      </c>
+      <c r="K239" t="n">
+        <v>-95.51262939999999</v>
+      </c>
+      <c r="L239" t="n">
+        <v>30.055621252113</v>
+      </c>
+      <c r="M239" t="n">
+        <v>-95.512047490141</v>
+      </c>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R239" t="n">
+        <v>0</v>
+      </c>
+      <c r="S239" t="n">
+        <v>0</v>
+      </c>
+      <c r="T239" t="n">
+        <v>0</v>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V239" t="n">
+        <v>-0.5629999999999999</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>1</v>
+      </c>
+      <c r="D240" t="n">
+        <v>3</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="H240" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="I240" t="n">
+        <v>6</v>
+      </c>
+      <c r="J240" t="n">
+        <v>30.055621252113</v>
+      </c>
+      <c r="K240" t="n">
+        <v>-95.512047490141</v>
+      </c>
+      <c r="L240" t="n">
+        <v>30.0553997</v>
+      </c>
+      <c r="M240" t="n">
+        <v>-95.5117834</v>
+      </c>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr"/>
+      <c r="P240" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R240" t="n">
+        <v>0</v>
+      </c>
+      <c r="S240" t="n">
+        <v>0</v>
+      </c>
+      <c r="T240" t="n">
+        <v>0</v>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V240" t="n">
+        <v>-0.118</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>1</v>
+      </c>
+      <c r="D241" t="n">
+        <v>4</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G241" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H241" t="n">
+        <v>6</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J241" t="n">
+        <v>30.0553997</v>
+      </c>
+      <c r="K241" t="n">
+        <v>-95.5117834</v>
+      </c>
+      <c r="L241" t="n">
+        <v>30.055409931632</v>
+      </c>
+      <c r="M241" t="n">
+        <v>-95.51183286011</v>
+      </c>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R241" t="n">
+        <v>0</v>
+      </c>
+      <c r="S241" t="n">
+        <v>1</v>
+      </c>
+      <c r="T241" t="n">
+        <v>0</v>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V241" t="n">
+        <v>-0.165</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>1</v>
+      </c>
+      <c r="D242" t="n">
+        <v>5</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I242" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" t="n">
+        <v>30.055409931632</v>
+      </c>
+      <c r="K242" t="n">
+        <v>-95.51183286011</v>
+      </c>
+      <c r="L242" t="n">
+        <v>30.055411206014</v>
+      </c>
+      <c r="M242" t="n">
+        <v>-95.511839020529</v>
+      </c>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R242" t="n">
+        <v>0</v>
+      </c>
+      <c r="S242" t="n">
+        <v>1</v>
+      </c>
+      <c r="T242" t="n">
+        <v>0</v>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V242" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>2</v>
+      </c>
+      <c r="D243" t="n">
+        <v>1</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Pitching Wedge</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="H243" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="I243" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J243" t="n">
+        <v>30.0546273</v>
+      </c>
+      <c r="K243" t="n">
+        <v>-95.5142993</v>
+      </c>
+      <c r="L243" t="n">
+        <v>30.055529832692</v>
+      </c>
+      <c r="M243" t="n">
+        <v>-95.51446803461501</v>
+      </c>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R243" t="n">
+        <v>1</v>
+      </c>
+      <c r="S243" t="n">
+        <v>0</v>
+      </c>
+      <c r="T243" t="n">
+        <v>0</v>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V243" t="n">
+        <v>-0.333</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>2</v>
+      </c>
+      <c r="D244" t="n">
+        <v>2</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H244" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="I244" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J244" t="n">
+        <v>30.055529832692</v>
+      </c>
+      <c r="K244" t="n">
+        <v>-95.51446803461501</v>
+      </c>
+      <c r="L244" t="n">
+        <v>30.0557002</v>
+      </c>
+      <c r="M244" t="n">
+        <v>-95.5144172</v>
+      </c>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
+      <c r="P244" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R244" t="n">
+        <v>0</v>
+      </c>
+      <c r="S244" t="n">
+        <v>0</v>
+      </c>
+      <c r="T244" t="n">
+        <v>0</v>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>short_game</t>
+        </is>
+      </c>
+      <c r="V244" t="n">
+        <v>-0.465</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>2</v>
+      </c>
+      <c r="D245" t="n">
+        <v>3</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H245" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I245" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J245" t="n">
+        <v>30.0557002</v>
+      </c>
+      <c r="K245" t="n">
+        <v>-95.5144172</v>
+      </c>
+      <c r="L245" t="n">
+        <v>30.055638374338</v>
+      </c>
+      <c r="M245" t="n">
+        <v>-95.514372645652</v>
+      </c>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr"/>
+      <c r="P245" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R245" t="n">
+        <v>0</v>
+      </c>
+      <c r="S245" t="n">
+        <v>1</v>
+      </c>
+      <c r="T245" t="n">
+        <v>0</v>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V245" t="n">
+        <v>-0.049</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>2</v>
+      </c>
+      <c r="D246" t="n">
+        <v>4</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G246" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" t="n">
+        <v>30.055638374338</v>
+      </c>
+      <c r="K246" t="n">
+        <v>-95.514372645652</v>
+      </c>
+      <c r="L246" t="n">
+        <v>30.05563372276</v>
+      </c>
+      <c r="M246" t="n">
+        <v>-95.514369293519</v>
+      </c>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R246" t="n">
+        <v>0</v>
+      </c>
+      <c r="S246" t="n">
+        <v>1</v>
+      </c>
+      <c r="T246" t="n">
+        <v>0</v>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V246" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>3</v>
+      </c>
+      <c r="D247" t="n">
+        <v>1</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G247" t="n">
+        <v>175.8</v>
+      </c>
+      <c r="H247" t="n">
+        <v>366</v>
+      </c>
+      <c r="I247" t="n">
+        <v>190.8</v>
+      </c>
+      <c r="J247" t="n">
+        <v>30.056791294595</v>
+      </c>
+      <c r="K247" t="n">
+        <v>-95.514627856757</v>
+      </c>
+      <c r="L247" t="n">
+        <v>30.05556997037</v>
+      </c>
+      <c r="M247" t="n">
+        <v>-95.51552151666699</v>
+      </c>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr"/>
+      <c r="P247" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R247" t="n">
+        <v>1</v>
+      </c>
+      <c r="S247" t="n">
+        <v>0</v>
+      </c>
+      <c r="T247" t="n">
+        <v>0</v>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V247" t="n">
+        <v>-0.207</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>3</v>
+      </c>
+      <c r="D248" t="n">
+        <v>2</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G248" t="n">
+        <v>192.9</v>
+      </c>
+      <c r="H248" t="n">
+        <v>190.8</v>
+      </c>
+      <c r="I248" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="J248" t="n">
+        <v>30.05556997037</v>
+      </c>
+      <c r="K248" t="n">
+        <v>-95.51552151666699</v>
+      </c>
+      <c r="L248" t="n">
+        <v>30.054090305128</v>
+      </c>
+      <c r="M248" t="n">
+        <v>-95.516182530769</v>
+      </c>
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr"/>
+      <c r="P248" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="R248" t="n">
+        <v>0</v>
+      </c>
+      <c r="S248" t="n">
+        <v>0</v>
+      </c>
+      <c r="T248" t="n">
+        <v>0</v>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V248" t="n">
+        <v>-0.5620000000000001</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>3</v>
+      </c>
+      <c r="D249" t="n">
+        <v>3</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G249" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="H249" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="I249" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J249" t="n">
+        <v>30.054090305128</v>
+      </c>
+      <c r="K249" t="n">
+        <v>-95.516182530769</v>
+      </c>
+      <c r="L249" t="n">
+        <v>30.0542938</v>
+      </c>
+      <c r="M249" t="n">
+        <v>-95.5167501</v>
+      </c>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr"/>
+      <c r="P249" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R249" t="n">
+        <v>0</v>
+      </c>
+      <c r="S249" t="n">
+        <v>0</v>
+      </c>
+      <c r="T249" t="n">
+        <v>0</v>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V249" t="n">
+        <v>-0.097</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>3</v>
+      </c>
+      <c r="D250" t="n">
+        <v>4</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H250" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I250" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J250" t="n">
+        <v>30.0542938</v>
+      </c>
+      <c r="K250" t="n">
+        <v>-95.5167501</v>
+      </c>
+      <c r="L250" t="n">
+        <v>30.054351673085</v>
+      </c>
+      <c r="M250" t="n">
+        <v>-95.516674170885</v>
+      </c>
+      <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr"/>
+      <c r="P250" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R250" t="n">
+        <v>0</v>
+      </c>
+      <c r="S250" t="n">
+        <v>1</v>
+      </c>
+      <c r="T250" t="n">
+        <v>0</v>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V250" t="n">
+        <v>-0.006</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>3</v>
+      </c>
+      <c r="D251" t="n">
+        <v>5</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" t="n">
+        <v>30.054351673085</v>
+      </c>
+      <c r="K251" t="n">
+        <v>-95.516674170885</v>
+      </c>
+      <c r="L251" t="n">
+        <v>30.054355296203</v>
+      </c>
+      <c r="M251" t="n">
+        <v>-95.516669417372</v>
+      </c>
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R251" t="n">
+        <v>0</v>
+      </c>
+      <c r="S251" t="n">
+        <v>1</v>
+      </c>
+      <c r="T251" t="n">
+        <v>0</v>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V251" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>4</v>
+      </c>
+      <c r="D252" t="n">
+        <v>1</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>277.4</v>
+      </c>
+      <c r="H252" t="n">
+        <v>538.5</v>
+      </c>
+      <c r="I252" t="n">
+        <v>261.6</v>
+      </c>
+      <c r="J252" t="n">
+        <v>30.0548652</v>
+      </c>
+      <c r="K252" t="n">
+        <v>-95.51674060000001</v>
+      </c>
+      <c r="L252" t="n">
+        <v>30.0569756</v>
+      </c>
+      <c r="M252" t="n">
+        <v>-95.5157409</v>
+      </c>
+      <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr"/>
+      <c r="P252" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R252" t="n">
+        <v>1</v>
+      </c>
+      <c r="S252" t="n">
+        <v>0</v>
+      </c>
+      <c r="T252" t="n">
+        <v>0</v>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V252" t="n">
+        <v>0.053</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>4</v>
+      </c>
+      <c r="D253" t="n">
+        <v>2</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>85</v>
+      </c>
+      <c r="H253" t="n">
+        <v>261.6</v>
+      </c>
+      <c r="I253" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="J253" t="n">
+        <v>30.0569756</v>
+      </c>
+      <c r="K253" t="n">
+        <v>-95.5157409</v>
+      </c>
+      <c r="L253" t="n">
+        <v>30.0575741625</v>
+      </c>
+      <c r="M253" t="n">
+        <v>-95.515324646154</v>
+      </c>
+      <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr"/>
+      <c r="P253" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R253" t="n">
+        <v>0</v>
+      </c>
+      <c r="S253" t="n">
+        <v>0</v>
+      </c>
+      <c r="T253" t="n">
+        <v>0</v>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V253" t="n">
+        <v>-0.335</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>4</v>
+      </c>
+      <c r="D254" t="n">
+        <v>3</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>7 Iron</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="H254" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="I254" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J254" t="n">
+        <v>30.0575741625</v>
+      </c>
+      <c r="K254" t="n">
+        <v>-95.515324646154</v>
+      </c>
+      <c r="L254" t="n">
+        <v>30.059025051834</v>
+      </c>
+      <c r="M254" t="n">
+        <v>-95.51500502556</v>
+      </c>
+      <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr"/>
+      <c r="P254" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R254" t="n">
+        <v>0</v>
+      </c>
+      <c r="S254" t="n">
+        <v>0</v>
+      </c>
+      <c r="T254" t="n">
+        <v>0</v>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V254" t="n">
+        <v>1.298</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>4</v>
+      </c>
+      <c r="D255" t="n">
+        <v>4</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I255" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J255" t="n">
+        <v>30.059025051834</v>
+      </c>
+      <c r="K255" t="n">
+        <v>-95.51500502556</v>
+      </c>
+      <c r="L255" t="n">
+        <v>30.059025051834</v>
+      </c>
+      <c r="M255" t="n">
+        <v>-95.51500502556</v>
+      </c>
+      <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr"/>
+      <c r="P255" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R255" t="n">
+        <v>0</v>
+      </c>
+      <c r="S255" t="n">
+        <v>1</v>
+      </c>
+      <c r="T255" t="n">
+        <v>0</v>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V255" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>4</v>
+      </c>
+      <c r="D256" t="n">
+        <v>5</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H256" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I256" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" t="n">
+        <v>30.059025051834</v>
+      </c>
+      <c r="K256" t="n">
+        <v>-95.51500502556</v>
+      </c>
+      <c r="L256" t="n">
+        <v>30.059030437092</v>
+      </c>
+      <c r="M256" t="n">
+        <v>-95.51500383920801</v>
+      </c>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr"/>
+      <c r="P256" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R256" t="n">
+        <v>0</v>
+      </c>
+      <c r="S256" t="n">
+        <v>1</v>
+      </c>
+      <c r="T256" t="n">
+        <v>0</v>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V256" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>5</v>
+      </c>
+      <c r="D257" t="n">
+        <v>1</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="H257" t="n">
+        <v>362.9</v>
+      </c>
+      <c r="I257" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="J257" t="n">
+        <v>30.0602324</v>
+      </c>
+      <c r="K257" t="n">
+        <v>-95.5152021</v>
+      </c>
+      <c r="L257" t="n">
+        <v>30.0612443</v>
+      </c>
+      <c r="M257" t="n">
+        <v>-95.5176774</v>
+      </c>
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr"/>
+      <c r="P257" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R257" t="n">
+        <v>1</v>
+      </c>
+      <c r="S257" t="n">
+        <v>0</v>
+      </c>
+      <c r="T257" t="n">
+        <v>0</v>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V257" t="n">
+        <v>0.182</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>5</v>
+      </c>
+      <c r="D258" t="n">
+        <v>2</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G258" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="H258" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="I258" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="J258" t="n">
+        <v>30.0612443</v>
+      </c>
+      <c r="K258" t="n">
+        <v>-95.5176774</v>
+      </c>
+      <c r="L258" t="n">
+        <v>30.061590833333</v>
+      </c>
+      <c r="M258" t="n">
+        <v>-95.51818016666699</v>
+      </c>
+      <c r="N258" t="inlineStr"/>
+      <c r="O258" t="inlineStr"/>
+      <c r="P258" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R258" t="n">
+        <v>0</v>
+      </c>
+      <c r="S258" t="n">
+        <v>0</v>
+      </c>
+      <c r="T258" t="n">
+        <v>0</v>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V258" t="n">
+        <v>-0.07199999999999999</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>5</v>
+      </c>
+      <c r="D259" t="n">
+        <v>3</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H259" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="I259" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J259" t="n">
+        <v>30.061590833333</v>
+      </c>
+      <c r="K259" t="n">
+        <v>-95.51818016666699</v>
+      </c>
+      <c r="L259" t="n">
+        <v>30.061680781303</v>
+      </c>
+      <c r="M259" t="n">
+        <v>-95.518211355245</v>
+      </c>
+      <c r="N259" t="inlineStr"/>
+      <c r="O259" t="inlineStr"/>
+      <c r="P259" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R259" t="n">
+        <v>0</v>
+      </c>
+      <c r="S259" t="n">
+        <v>1</v>
+      </c>
+      <c r="T259" t="n">
+        <v>0</v>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V259" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>5</v>
+      </c>
+      <c r="D260" t="n">
+        <v>4</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H260" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I260" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" t="n">
+        <v>30.061680781303</v>
+      </c>
+      <c r="K260" t="n">
+        <v>-95.518211355245</v>
+      </c>
+      <c r="L260" t="n">
+        <v>30.061686032225</v>
+      </c>
+      <c r="M260" t="n">
+        <v>-95.51821317595299</v>
+      </c>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr"/>
+      <c r="P260" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R260" t="n">
+        <v>0</v>
+      </c>
+      <c r="S260" t="n">
+        <v>1</v>
+      </c>
+      <c r="T260" t="n">
+        <v>0</v>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V260" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>6</v>
+      </c>
+      <c r="D261" t="n">
+        <v>1</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>7 Iron</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="H261" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="I261" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="J261" t="n">
+        <v>30.060851058537</v>
+      </c>
+      <c r="K261" t="n">
+        <v>-95.518430490244</v>
+      </c>
+      <c r="L261" t="n">
+        <v>30.059810596552</v>
+      </c>
+      <c r="M261" t="n">
+        <v>-95.518175236207</v>
+      </c>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr"/>
+      <c r="P261" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R261" t="n">
+        <v>1</v>
+      </c>
+      <c r="S261" t="n">
+        <v>0</v>
+      </c>
+      <c r="T261" t="n">
+        <v>0</v>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V261" t="n">
+        <v>-0.711</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>6</v>
+      </c>
+      <c r="D262" t="n">
+        <v>2</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>58</v>
+      </c>
+      <c r="H262" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="I262" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J262" t="n">
+        <v>30.059810596552</v>
+      </c>
+      <c r="K262" t="n">
+        <v>-95.518175236207</v>
+      </c>
+      <c r="L262" t="n">
+        <v>30.0595573</v>
+      </c>
+      <c r="M262" t="n">
+        <v>-95.5186424</v>
+      </c>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr"/>
+      <c r="P262" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R262" t="n">
+        <v>0</v>
+      </c>
+      <c r="S262" t="n">
+        <v>0</v>
+      </c>
+      <c r="T262" t="n">
+        <v>0</v>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V262" t="n">
+        <v>-0.002</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>6</v>
+      </c>
+      <c r="D263" t="n">
+        <v>3</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H263" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I263" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J263" t="n">
+        <v>30.0595573</v>
+      </c>
+      <c r="K263" t="n">
+        <v>-95.5186424</v>
+      </c>
+      <c r="L263" t="n">
+        <v>30.059604826338</v>
+      </c>
+      <c r="M263" t="n">
+        <v>-95.518676652411</v>
+      </c>
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" t="inlineStr"/>
+      <c r="P263" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R263" t="n">
+        <v>0</v>
+      </c>
+      <c r="S263" t="n">
+        <v>1</v>
+      </c>
+      <c r="T263" t="n">
+        <v>0</v>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V263" t="n">
+        <v>-0.107</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>6</v>
+      </c>
+      <c r="D264" t="n">
+        <v>4</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H264" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
+        <v>30.059604826338</v>
+      </c>
+      <c r="K264" t="n">
+        <v>-95.518676652411</v>
+      </c>
+      <c r="L264" t="n">
+        <v>30.05960947786</v>
+      </c>
+      <c r="M264" t="n">
+        <v>-95.51868000478299</v>
+      </c>
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" t="inlineStr"/>
+      <c r="P264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R264" t="n">
+        <v>0</v>
+      </c>
+      <c r="S264" t="n">
+        <v>1</v>
+      </c>
+      <c r="T264" t="n">
+        <v>0</v>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V264" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>7</v>
+      </c>
+      <c r="D265" t="n">
+        <v>1</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>200.9</v>
+      </c>
+      <c r="H265" t="n">
+        <v>341.5</v>
+      </c>
+      <c r="I265" t="n">
+        <v>148.3</v>
+      </c>
+      <c r="J265" t="n">
+        <v>30.060222290625</v>
+      </c>
+      <c r="K265" t="n">
+        <v>-95.519543917188</v>
+      </c>
+      <c r="L265" t="n">
+        <v>30.061848</v>
+      </c>
+      <c r="M265" t="n">
+        <v>-95.5198858</v>
+      </c>
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" t="inlineStr"/>
+      <c r="P265" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R265" t="n">
+        <v>1</v>
+      </c>
+      <c r="S265" t="n">
+        <v>0</v>
+      </c>
+      <c r="T265" t="n">
+        <v>0</v>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V265" t="n">
+        <v>-0.075</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>7</v>
+      </c>
+      <c r="D266" t="n">
+        <v>2</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>7 Iron</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="H266" t="n">
+        <v>148.3</v>
+      </c>
+      <c r="I266" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="J266" t="n">
+        <v>30.061848</v>
+      </c>
+      <c r="K266" t="n">
+        <v>-95.5198858</v>
+      </c>
+      <c r="L266" t="n">
+        <v>30.062371418736</v>
+      </c>
+      <c r="M266" t="n">
+        <v>-95.5201202631</v>
+      </c>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr"/>
+      <c r="P266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R266" t="n">
+        <v>0</v>
+      </c>
+      <c r="S266" t="n">
+        <v>0</v>
+      </c>
+      <c r="T266" t="n">
+        <v>0</v>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V266" t="n">
+        <v>-0.574</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>7</v>
+      </c>
+      <c r="D267" t="n">
+        <v>3</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>58 Wedge</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="H267" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="I267" t="n">
+        <v>5</v>
+      </c>
+      <c r="J267" t="n">
+        <v>30.062371418736</v>
+      </c>
+      <c r="K267" t="n">
+        <v>-95.5201202631</v>
+      </c>
+      <c r="L267" t="n">
+        <v>30.062821823007</v>
+      </c>
+      <c r="M267" t="n">
+        <v>-95.520654256106</v>
+      </c>
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" t="inlineStr"/>
+      <c r="P267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R267" t="n">
+        <v>0</v>
+      </c>
+      <c r="S267" t="n">
+        <v>0</v>
+      </c>
+      <c r="T267" t="n">
+        <v>0</v>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V267" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>7</v>
+      </c>
+      <c r="D268" t="n">
+        <v>4</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H268" t="n">
+        <v>5</v>
+      </c>
+      <c r="I268" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J268" t="n">
+        <v>30.062821823007</v>
+      </c>
+      <c r="K268" t="n">
+        <v>-95.520654256106</v>
+      </c>
+      <c r="L268" t="n">
+        <v>30.062846693888</v>
+      </c>
+      <c r="M268" t="n">
+        <v>-95.52068374289099</v>
+      </c>
+      <c r="N268" t="inlineStr"/>
+      <c r="O268" t="inlineStr"/>
+      <c r="P268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R268" t="n">
+        <v>0</v>
+      </c>
+      <c r="S268" t="n">
+        <v>1</v>
+      </c>
+      <c r="T268" t="n">
+        <v>0</v>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V268" t="n">
+        <v>-0.223</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>7</v>
+      </c>
+      <c r="D269" t="n">
+        <v>5</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H269" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" t="n">
+        <v>30.062846693888</v>
+      </c>
+      <c r="K269" t="n">
+        <v>-95.52068374289099</v>
+      </c>
+      <c r="L269" t="n">
+        <v>30.062850520177</v>
+      </c>
+      <c r="M269" t="n">
+        <v>-95.52068827932</v>
+      </c>
+      <c r="N269" t="inlineStr"/>
+      <c r="O269" t="inlineStr"/>
+      <c r="P269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R269" t="n">
+        <v>0</v>
+      </c>
+      <c r="S269" t="n">
+        <v>1</v>
+      </c>
+      <c r="T269" t="n">
+        <v>0</v>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V269" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>8</v>
+      </c>
+      <c r="D270" t="n">
+        <v>1</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="H270" t="n">
+        <v>383.8</v>
+      </c>
+      <c r="I270" t="n">
+        <v>274.7</v>
+      </c>
+      <c r="J270" t="n">
+        <v>30.0641189</v>
+      </c>
+      <c r="K270" t="n">
+        <v>-95.5200449</v>
+      </c>
+      <c r="L270" t="n">
+        <v>30.0638602</v>
+      </c>
+      <c r="M270" t="n">
+        <v>-95.51895810000001</v>
+      </c>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr"/>
+      <c r="P270" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R270" t="n">
+        <v>1</v>
+      </c>
+      <c r="S270" t="n">
+        <v>0</v>
+      </c>
+      <c r="T270" t="n">
+        <v>0</v>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V270" t="n">
+        <v>-0.695</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>8</v>
+      </c>
+      <c r="D271" t="n">
+        <v>2</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>223.5</v>
+      </c>
+      <c r="H271" t="n">
+        <v>274.7</v>
+      </c>
+      <c r="I271" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="J271" t="n">
+        <v>30.0638602</v>
+      </c>
+      <c r="K271" t="n">
+        <v>-95.51895810000001</v>
+      </c>
+      <c r="L271" t="n">
+        <v>30.064197367647</v>
+      </c>
+      <c r="M271" t="n">
+        <v>-95.51687087254901</v>
+      </c>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr"/>
+      <c r="P271" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R271" t="n">
+        <v>0</v>
+      </c>
+      <c r="S271" t="n">
+        <v>0</v>
+      </c>
+      <c r="T271" t="n">
+        <v>0</v>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V271" t="n">
+        <v>0.139</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>8</v>
+      </c>
+      <c r="D272" t="n">
+        <v>3</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="H272" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="I272" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J272" t="n">
+        <v>30.064197367647</v>
+      </c>
+      <c r="K272" t="n">
+        <v>-95.51687087254901</v>
+      </c>
+      <c r="L272" t="n">
+        <v>30.0643543</v>
+      </c>
+      <c r="M272" t="n">
+        <v>-95.5162986</v>
+      </c>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr"/>
+      <c r="P272" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R272" t="n">
+        <v>0</v>
+      </c>
+      <c r="S272" t="n">
+        <v>0</v>
+      </c>
+      <c r="T272" t="n">
+        <v>0</v>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V272" t="n">
+        <v>-0.138</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>8</v>
+      </c>
+      <c r="D273" t="n">
+        <v>4</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H273" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I273" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J273" t="n">
+        <v>30.0643543</v>
+      </c>
+      <c r="K273" t="n">
+        <v>-95.5162986</v>
+      </c>
+      <c r="L273" t="n">
+        <v>30.064338706462</v>
+      </c>
+      <c r="M273" t="n">
+        <v>-95.516384740747</v>
+      </c>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr"/>
+      <c r="P273" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R273" t="n">
+        <v>0</v>
+      </c>
+      <c r="S273" t="n">
+        <v>1</v>
+      </c>
+      <c r="T273" t="n">
+        <v>0</v>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V273" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>8</v>
+      </c>
+      <c r="D274" t="n">
+        <v>5</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H274" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I274" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J274" t="n">
+        <v>30.064338706462</v>
+      </c>
+      <c r="K274" t="n">
+        <v>-95.516384740747</v>
+      </c>
+      <c r="L274" t="n">
+        <v>30.064335900442</v>
+      </c>
+      <c r="M274" t="n">
+        <v>-95.516400241534</v>
+      </c>
+      <c r="N274" t="inlineStr"/>
+      <c r="O274" t="inlineStr"/>
+      <c r="P274" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R274" t="n">
+        <v>0</v>
+      </c>
+      <c r="S274" t="n">
+        <v>1</v>
+      </c>
+      <c r="T274" t="n">
+        <v>0</v>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V274" t="n">
+        <v>-0.579</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>8</v>
+      </c>
+      <c r="D275" t="n">
+        <v>6</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H275" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I275" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" t="n">
+        <v>30.064335900442</v>
+      </c>
+      <c r="K275" t="n">
+        <v>-95.516400241534</v>
+      </c>
+      <c r="L275" t="n">
+        <v>30.064334778033</v>
+      </c>
+      <c r="M275" t="n">
+        <v>-95.516406441849</v>
+      </c>
+      <c r="N275" t="inlineStr"/>
+      <c r="O275" t="inlineStr"/>
+      <c r="P275" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R275" t="n">
+        <v>0</v>
+      </c>
+      <c r="S275" t="n">
+        <v>1</v>
+      </c>
+      <c r="T275" t="n">
+        <v>0</v>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V275" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>9</v>
+      </c>
+      <c r="D276" t="n">
+        <v>1</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G276" t="n">
+        <v>262.4</v>
+      </c>
+      <c r="H276" t="n">
+        <v>436.7</v>
+      </c>
+      <c r="I276" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="J276" t="n">
+        <v>30.064682075</v>
+      </c>
+      <c r="K276" t="n">
+        <v>-95.51512836000001</v>
+      </c>
+      <c r="L276" t="n">
+        <v>30.0625694</v>
+      </c>
+      <c r="M276" t="n">
+        <v>-95.514619</v>
+      </c>
+      <c r="N276" t="inlineStr"/>
+      <c r="O276" t="inlineStr"/>
+      <c r="P276" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R276" t="n">
+        <v>1</v>
+      </c>
+      <c r="S276" t="n">
+        <v>0</v>
+      </c>
+      <c r="T276" t="n">
+        <v>0</v>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V276" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>9</v>
+      </c>
+      <c r="D277" t="n">
+        <v>2</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G277" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="H277" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="I277" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="J277" t="n">
+        <v>30.0625694</v>
+      </c>
+      <c r="K277" t="n">
+        <v>-95.514619</v>
+      </c>
+      <c r="L277" t="n">
+        <v>30.061200117778</v>
+      </c>
+      <c r="M277" t="n">
+        <v>-95.51336418222201</v>
+      </c>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr"/>
+      <c r="P277" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="R277" t="n">
+        <v>0</v>
+      </c>
+      <c r="S277" t="n">
+        <v>0</v>
+      </c>
+      <c r="T277" t="n">
+        <v>0</v>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V277" t="n">
+        <v>-0.469</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>9</v>
+      </c>
+      <c r="D278" t="n">
+        <v>3</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="H278" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="I278" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="J278" t="n">
+        <v>30.061200117778</v>
+      </c>
+      <c r="K278" t="n">
+        <v>-95.51336418222201</v>
+      </c>
+      <c r="L278" t="n">
+        <v>30.061196869492</v>
+      </c>
+      <c r="M278" t="n">
+        <v>-95.513666276271</v>
+      </c>
+      <c r="N278" t="inlineStr"/>
+      <c r="O278" t="inlineStr"/>
+      <c r="P278" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R278" t="n">
+        <v>0</v>
+      </c>
+      <c r="S278" t="n">
+        <v>0</v>
+      </c>
+      <c r="T278" t="n">
+        <v>0</v>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V278" t="n">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>9</v>
+      </c>
+      <c r="D279" t="n">
+        <v>4</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H279" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="I279" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J279" t="n">
+        <v>30.061196869492</v>
+      </c>
+      <c r="K279" t="n">
+        <v>-95.513666276271</v>
+      </c>
+      <c r="L279" t="n">
+        <v>30.061316597581</v>
+      </c>
+      <c r="M279" t="n">
+        <v>-95.513664680418</v>
+      </c>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
+      <c r="P279" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R279" t="n">
+        <v>0</v>
+      </c>
+      <c r="S279" t="n">
+        <v>1</v>
+      </c>
+      <c r="T279" t="n">
+        <v>0</v>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V279" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>9</v>
+      </c>
+      <c r="D280" t="n">
+        <v>5</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H280" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I280" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" t="n">
+        <v>30.061316597581</v>
+      </c>
+      <c r="K280" t="n">
+        <v>-95.513664680418</v>
+      </c>
+      <c r="L280" t="n">
+        <v>30.06132207949</v>
+      </c>
+      <c r="M280" t="n">
+        <v>-95.513664607349</v>
+      </c>
+      <c r="N280" t="inlineStr"/>
+      <c r="O280" t="inlineStr"/>
+      <c r="P280" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R280" t="n">
+        <v>0</v>
+      </c>
+      <c r="S280" t="n">
+        <v>1</v>
+      </c>
+      <c r="T280" t="n">
+        <v>0</v>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V280" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>10</v>
+      </c>
+      <c r="D281" t="n">
+        <v>1</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>258.3</v>
+      </c>
+      <c r="H281" t="n">
+        <v>384.7</v>
+      </c>
+      <c r="I281" t="n">
+        <v>126.7</v>
+      </c>
+      <c r="J281" t="n">
+        <v>30.059218</v>
+      </c>
+      <c r="K281" t="n">
+        <v>-95.5122239</v>
+      </c>
+      <c r="L281" t="n">
+        <v>30.0582034</v>
+      </c>
+      <c r="M281" t="n">
+        <v>-95.5100679</v>
+      </c>
+      <c r="N281" t="inlineStr"/>
+      <c r="O281" t="inlineStr"/>
+      <c r="P281" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R281" t="n">
+        <v>1</v>
+      </c>
+      <c r="S281" t="n">
+        <v>0</v>
+      </c>
+      <c r="T281" t="n">
+        <v>0</v>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V281" t="n">
+        <v>0.097</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>10</v>
+      </c>
+      <c r="D282" t="n">
+        <v>2</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>9 Iron</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G282" t="n">
+        <v>219.1</v>
+      </c>
+      <c r="H282" t="n">
+        <v>126.7</v>
+      </c>
+      <c r="I282" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="J282" t="n">
+        <v>30.0582034</v>
+      </c>
+      <c r="K282" t="n">
+        <v>-95.5100679</v>
+      </c>
+      <c r="L282" t="n">
+        <v>30.058210322727</v>
+      </c>
+      <c r="M282" t="n">
+        <v>-95.507985763636</v>
+      </c>
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr"/>
+      <c r="P282" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="R282" t="n">
+        <v>0</v>
+      </c>
+      <c r="S282" t="n">
+        <v>0</v>
+      </c>
+      <c r="T282" t="n">
+        <v>0</v>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V282" t="n">
+        <v>-0.967</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>10</v>
+      </c>
+      <c r="D283" t="n">
+        <v>3</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Pitching Wedge</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="H283" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="I283" t="n">
+        <v>5</v>
+      </c>
+      <c r="J283" t="n">
+        <v>30.058210322727</v>
+      </c>
+      <c r="K283" t="n">
+        <v>-95.507985763636</v>
+      </c>
+      <c r="L283" t="n">
+        <v>30.057809024224</v>
+      </c>
+      <c r="M283" t="n">
+        <v>-95.508919823269</v>
+      </c>
+      <c r="N283" t="inlineStr"/>
+      <c r="O283" t="inlineStr"/>
+      <c r="P283" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R283" t="n">
+        <v>0</v>
+      </c>
+      <c r="S283" t="n">
+        <v>0</v>
+      </c>
+      <c r="T283" t="n">
+        <v>0</v>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V283" t="n">
+        <v>0.274</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>10</v>
+      </c>
+      <c r="D284" t="n">
+        <v>4</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>5</v>
+      </c>
+      <c r="H284" t="n">
+        <v>5</v>
+      </c>
+      <c r="I284" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" t="n">
+        <v>30.057809024224</v>
+      </c>
+      <c r="K284" t="n">
+        <v>-95.508919823269</v>
+      </c>
+      <c r="L284" t="n">
+        <v>30.057790742624</v>
+      </c>
+      <c r="M284" t="n">
+        <v>-95.508962374848</v>
+      </c>
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr"/>
+      <c r="P284" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R284" t="n">
+        <v>0</v>
+      </c>
+      <c r="S284" t="n">
+        <v>1</v>
+      </c>
+      <c r="T284" t="n">
+        <v>0</v>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V284" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>11</v>
+      </c>
+      <c r="D285" t="n">
+        <v>1</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>7 Iron</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>164.7</v>
+      </c>
+      <c r="H285" t="n">
+        <v>151.7</v>
+      </c>
+      <c r="I285" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="J285" t="n">
+        <v>30.058004188919</v>
+      </c>
+      <c r="K285" t="n">
+        <v>-95.507638268173</v>
+      </c>
+      <c r="L285" t="n">
+        <v>30.059217746793</v>
+      </c>
+      <c r="M285" t="n">
+        <v>-95.506943240762</v>
+      </c>
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" t="inlineStr"/>
+      <c r="P285" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R285" t="n">
+        <v>1</v>
+      </c>
+      <c r="S285" t="n">
+        <v>0</v>
+      </c>
+      <c r="T285" t="n">
+        <v>0</v>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V285" t="n">
+        <v>-0.547</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>11</v>
+      </c>
+      <c r="D286" t="n">
+        <v>2</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Pitching Wedge</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="H286" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="I286" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J286" t="n">
+        <v>30.059217746793</v>
+      </c>
+      <c r="K286" t="n">
+        <v>-95.506943240762</v>
+      </c>
+      <c r="L286" t="n">
+        <v>30.059016574442</v>
+      </c>
+      <c r="M286" t="n">
+        <v>-95.506787188091</v>
+      </c>
+      <c r="N286" t="inlineStr"/>
+      <c r="O286" t="inlineStr"/>
+      <c r="P286" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R286" t="n">
+        <v>0</v>
+      </c>
+      <c r="S286" t="n">
+        <v>0</v>
+      </c>
+      <c r="T286" t="n">
+        <v>0</v>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V286" t="n">
+        <v>0.443</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>11</v>
+      </c>
+      <c r="D287" t="n">
+        <v>3</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G287" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H287" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I287" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J287" t="n">
+        <v>30.059016574442</v>
+      </c>
+      <c r="K287" t="n">
+        <v>-95.506787188091</v>
+      </c>
+      <c r="L287" t="n">
+        <v>30.059021126025</v>
+      </c>
+      <c r="M287" t="n">
+        <v>-95.50679071882</v>
+      </c>
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" t="inlineStr"/>
+      <c r="P287" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R287" t="n">
+        <v>0</v>
+      </c>
+      <c r="S287" t="n">
+        <v>1</v>
+      </c>
+      <c r="T287" t="n">
+        <v>0</v>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V287" t="n">
+        <v>-1.168</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>11</v>
+      </c>
+      <c r="D288" t="n">
+        <v>4</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H288" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I288" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J288" t="n">
+        <v>30.059021126025</v>
+      </c>
+      <c r="K288" t="n">
+        <v>-95.50679071882</v>
+      </c>
+      <c r="L288" t="n">
+        <v>30.059009747066</v>
+      </c>
+      <c r="M288" t="n">
+        <v>-95.506781891998</v>
+      </c>
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" t="inlineStr"/>
+      <c r="P288" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R288" t="n">
+        <v>0</v>
+      </c>
+      <c r="S288" t="n">
+        <v>1</v>
+      </c>
+      <c r="T288" t="n">
+        <v>0</v>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V288" t="n">
+        <v>-0.579</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>11</v>
+      </c>
+      <c r="D289" t="n">
+        <v>5</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H289" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I289" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" t="n">
+        <v>30.059009747066</v>
+      </c>
+      <c r="K289" t="n">
+        <v>-95.506781891998</v>
+      </c>
+      <c r="L289" t="n">
+        <v>30.059005195483</v>
+      </c>
+      <c r="M289" t="n">
+        <v>-95.50677836126999</v>
+      </c>
+      <c r="N289" t="inlineStr"/>
+      <c r="O289" t="inlineStr"/>
+      <c r="P289" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R289" t="n">
+        <v>0</v>
+      </c>
+      <c r="S289" t="n">
+        <v>1</v>
+      </c>
+      <c r="T289" t="n">
+        <v>0</v>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V289" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>12</v>
+      </c>
+      <c r="D290" t="n">
+        <v>1</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>272.1</v>
+      </c>
+      <c r="H290" t="n">
+        <v>441</v>
+      </c>
+      <c r="I290" t="n">
+        <v>195.6</v>
+      </c>
+      <c r="J290" t="n">
+        <v>30.0585863</v>
+      </c>
+      <c r="K290" t="n">
+        <v>-95.5051476</v>
+      </c>
+      <c r="L290" t="n">
+        <v>30.060288834921</v>
+      </c>
+      <c r="M290" t="n">
+        <v>-95.503469846032</v>
+      </c>
+      <c r="N290" t="inlineStr"/>
+      <c r="O290" t="inlineStr"/>
+      <c r="P290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R290" t="n">
+        <v>1</v>
+      </c>
+      <c r="S290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T290" t="n">
+        <v>0</v>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V290" t="n">
+        <v>-0.081</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>12</v>
+      </c>
+      <c r="D291" t="n">
+        <v>2</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="H291" t="n">
+        <v>195.6</v>
+      </c>
+      <c r="I291" t="n">
+        <v>149.6</v>
+      </c>
+      <c r="J291" t="n">
+        <v>30.060288834921</v>
+      </c>
+      <c r="K291" t="n">
+        <v>-95.503469846032</v>
+      </c>
+      <c r="L291" t="n">
+        <v>30.060667282857</v>
+      </c>
+      <c r="M291" t="n">
+        <v>-95.50339869428601</v>
+      </c>
+      <c r="N291" t="inlineStr"/>
+      <c r="O291" t="inlineStr"/>
+      <c r="P291" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="R291" t="n">
+        <v>0</v>
+      </c>
+      <c r="S291" t="n">
+        <v>0</v>
+      </c>
+      <c r="T291" t="n">
+        <v>0</v>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V291" t="n">
+        <v>-0.778</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>12</v>
+      </c>
+      <c r="D292" t="n">
+        <v>3</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>139.2</v>
+      </c>
+      <c r="H292" t="n">
+        <v>149.6</v>
+      </c>
+      <c r="I292" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="J292" t="n">
+        <v>30.060667282857</v>
+      </c>
+      <c r="K292" t="n">
+        <v>-95.50339869428601</v>
+      </c>
+      <c r="L292" t="n">
+        <v>30.0617673</v>
+      </c>
+      <c r="M292" t="n">
+        <v>-95.5037655</v>
+      </c>
+      <c r="N292" t="inlineStr"/>
+      <c r="O292" t="inlineStr"/>
+      <c r="P292" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R292" t="n">
+        <v>0</v>
+      </c>
+      <c r="S292" t="n">
+        <v>0</v>
+      </c>
+      <c r="T292" t="n">
+        <v>0</v>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V292" t="n">
+        <v>-0.395</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>12</v>
+      </c>
+      <c r="D293" t="n">
+        <v>4</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="H293" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="I293" t="n">
+        <v>9</v>
+      </c>
+      <c r="J293" t="n">
+        <v>30.0617673</v>
+      </c>
+      <c r="K293" t="n">
+        <v>-95.5037655</v>
+      </c>
+      <c r="L293" t="n">
+        <v>30.0618302</v>
+      </c>
+      <c r="M293" t="n">
+        <v>-95.5034745</v>
+      </c>
+      <c r="N293" t="inlineStr"/>
+      <c r="O293" t="inlineStr"/>
+      <c r="P293" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R293" t="n">
+        <v>0</v>
+      </c>
+      <c r="S293" t="n">
+        <v>0</v>
+      </c>
+      <c r="T293" t="n">
+        <v>0</v>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V293" t="n">
+        <v>-0.188</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>12</v>
+      </c>
+      <c r="D294" t="n">
+        <v>5</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G294" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H294" t="n">
+        <v>9</v>
+      </c>
+      <c r="I294" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J294" t="n">
+        <v>30.0618302</v>
+      </c>
+      <c r="K294" t="n">
+        <v>-95.5034745</v>
+      </c>
+      <c r="L294" t="n">
+        <v>30.061891999672</v>
+      </c>
+      <c r="M294" t="n">
+        <v>-95.50344079124299</v>
+      </c>
+      <c r="N294" t="inlineStr"/>
+      <c r="O294" t="inlineStr"/>
+      <c r="P294" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R294" t="n">
+        <v>0</v>
+      </c>
+      <c r="S294" t="n">
+        <v>1</v>
+      </c>
+      <c r="T294" t="n">
+        <v>0</v>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V294" t="n">
+        <v>-0.062</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>12</v>
+      </c>
+      <c r="D295" t="n">
+        <v>6</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G295" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H295" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I295" t="n">
+        <v>0</v>
+      </c>
+      <c r="J295" t="n">
+        <v>30.061891999672</v>
+      </c>
+      <c r="K295" t="n">
+        <v>-95.50344079124299</v>
+      </c>
+      <c r="L295" t="n">
+        <v>30.061896957281</v>
+      </c>
+      <c r="M295" t="n">
+        <v>-95.50343808710301</v>
+      </c>
+      <c r="N295" t="inlineStr"/>
+      <c r="O295" t="inlineStr"/>
+      <c r="P295" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R295" t="n">
+        <v>0</v>
+      </c>
+      <c r="S295" t="n">
+        <v>1</v>
+      </c>
+      <c r="T295" t="n">
+        <v>0</v>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V295" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>13</v>
+      </c>
+      <c r="D296" t="n">
+        <v>1</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G296" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="H296" t="n">
+        <v>399.5</v>
+      </c>
+      <c r="I296" t="n">
+        <v>296.8</v>
+      </c>
+      <c r="J296" t="n">
+        <v>30.0621077</v>
+      </c>
+      <c r="K296" t="n">
+        <v>-95.50556880000001</v>
+      </c>
+      <c r="L296" t="n">
+        <v>30.061501180138</v>
+      </c>
+      <c r="M296" t="n">
+        <v>-95.506391711533</v>
+      </c>
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R296" t="n">
+        <v>1</v>
+      </c>
+      <c r="S296" t="n">
+        <v>0</v>
+      </c>
+      <c r="T296" t="n">
+        <v>0</v>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V296" t="n">
+        <v>-0.776</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>13</v>
+      </c>
+      <c r="D297" t="n">
+        <v>2</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G297" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="H297" t="n">
+        <v>296.8</v>
+      </c>
+      <c r="I297" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="J297" t="n">
+        <v>30.061501180138</v>
+      </c>
+      <c r="K297" t="n">
+        <v>-95.506391711533</v>
+      </c>
+      <c r="L297" t="n">
+        <v>30.0611651625</v>
+      </c>
+      <c r="M297" t="n">
+        <v>-95.5081209375</v>
+      </c>
+      <c r="N297" t="inlineStr"/>
+      <c r="O297" t="inlineStr"/>
+      <c r="P297" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R297" t="n">
+        <v>0</v>
+      </c>
+      <c r="S297" t="n">
+        <v>0</v>
+      </c>
+      <c r="T297" t="n">
+        <v>0</v>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V297" t="n">
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>13</v>
+      </c>
+      <c r="D298" t="n">
+        <v>3</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Pitching Wedge</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G298" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="H298" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="I298" t="n">
+        <v>34</v>
+      </c>
+      <c r="J298" t="n">
+        <v>30.0611651625</v>
+      </c>
+      <c r="K298" t="n">
+        <v>-95.5081209375</v>
+      </c>
+      <c r="L298" t="n">
+        <v>30.060922759375</v>
+      </c>
+      <c r="M298" t="n">
+        <v>-95.509448540625</v>
+      </c>
+      <c r="N298" t="inlineStr"/>
+      <c r="O298" t="inlineStr"/>
+      <c r="P298" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R298" t="n">
+        <v>0</v>
+      </c>
+      <c r="S298" t="n">
+        <v>0</v>
+      </c>
+      <c r="T298" t="n">
+        <v>0</v>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V298" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>13</v>
+      </c>
+      <c r="D299" t="n">
+        <v>4</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G299" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="H299" t="n">
+        <v>34</v>
+      </c>
+      <c r="I299" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J299" t="n">
+        <v>30.060922759375</v>
+      </c>
+      <c r="K299" t="n">
+        <v>-95.509448540625</v>
+      </c>
+      <c r="L299" t="n">
+        <v>30.0611223</v>
+      </c>
+      <c r="M299" t="n">
+        <v>-95.5093021</v>
+      </c>
+      <c r="N299" t="inlineStr"/>
+      <c r="O299" t="inlineStr"/>
+      <c r="P299" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R299" t="n">
+        <v>0</v>
+      </c>
+      <c r="S299" t="n">
+        <v>0</v>
+      </c>
+      <c r="T299" t="n">
+        <v>0</v>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V299" t="n">
+        <v>-0.401</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>13</v>
+      </c>
+      <c r="D300" t="n">
+        <v>5</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G300" t="n">
+        <v>16</v>
+      </c>
+      <c r="H300" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="I300" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J300" t="n">
+        <v>30.0611223</v>
+      </c>
+      <c r="K300" t="n">
+        <v>-95.5093021</v>
+      </c>
+      <c r="L300" t="n">
+        <v>30.061058047187</v>
+      </c>
+      <c r="M300" t="n">
+        <v>-95.509169935578</v>
+      </c>
+      <c r="N300" t="inlineStr"/>
+      <c r="O300" t="inlineStr"/>
+      <c r="P300" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R300" t="n">
+        <v>0</v>
+      </c>
+      <c r="S300" t="n">
+        <v>1</v>
+      </c>
+      <c r="T300" t="n">
+        <v>0</v>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V300" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>13</v>
+      </c>
+      <c r="D301" t="n">
+        <v>6</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G301" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H301" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I301" t="n">
+        <v>0</v>
+      </c>
+      <c r="J301" t="n">
+        <v>30.061058047187</v>
+      </c>
+      <c r="K301" t="n">
+        <v>-95.509169935578</v>
+      </c>
+      <c r="L301" t="n">
+        <v>30.061055362295</v>
+      </c>
+      <c r="M301" t="n">
+        <v>-95.509164412917</v>
+      </c>
+      <c r="N301" t="inlineStr"/>
+      <c r="O301" t="inlineStr"/>
+      <c r="P301" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R301" t="n">
+        <v>0</v>
+      </c>
+      <c r="S301" t="n">
+        <v>1</v>
+      </c>
+      <c r="T301" t="n">
+        <v>0</v>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V301" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>14</v>
+      </c>
+      <c r="D302" t="n">
+        <v>1</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G302" t="n">
+        <v>213.7</v>
+      </c>
+      <c r="H302" t="n">
+        <v>499.8</v>
+      </c>
+      <c r="I302" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="J302" t="n">
+        <v>30.0623367</v>
+      </c>
+      <c r="K302" t="n">
+        <v>-95.50983290000001</v>
+      </c>
+      <c r="L302" t="n">
+        <v>30.0635451</v>
+      </c>
+      <c r="M302" t="n">
+        <v>-95.5083592</v>
+      </c>
+      <c r="N302" t="inlineStr"/>
+      <c r="O302" t="inlineStr"/>
+      <c r="P302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R302" t="n">
+        <v>1</v>
+      </c>
+      <c r="S302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V302" t="n">
+        <v>-0.315</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>14</v>
+      </c>
+      <c r="D303" t="n">
+        <v>2</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="H303" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="I303" t="n">
+        <v>242</v>
+      </c>
+      <c r="J303" t="n">
+        <v>30.0635451</v>
+      </c>
+      <c r="K303" t="n">
+        <v>-95.5083592</v>
+      </c>
+      <c r="L303" t="n">
+        <v>30.064026251042</v>
+      </c>
+      <c r="M303" t="n">
+        <v>-95.508331442708</v>
+      </c>
+      <c r="N303" t="inlineStr"/>
+      <c r="O303" t="inlineStr"/>
+      <c r="P303" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R303" t="n">
+        <v>0</v>
+      </c>
+      <c r="S303" t="n">
+        <v>0</v>
+      </c>
+      <c r="T303" t="n">
+        <v>0</v>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V303" t="n">
+        <v>-0.607</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>14</v>
+      </c>
+      <c r="D304" t="n">
+        <v>3</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>3 Wood</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="G304" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="H304" t="n">
+        <v>242</v>
+      </c>
+      <c r="I304" t="n">
+        <v>170.6</v>
+      </c>
+      <c r="J304" t="n">
+        <v>30.064026251042</v>
+      </c>
+      <c r="K304" t="n">
+        <v>-95.508331442708</v>
+      </c>
+      <c r="L304" t="n">
+        <v>30.0644487</v>
+      </c>
+      <c r="M304" t="n">
+        <v>-95.5078589</v>
+      </c>
+      <c r="N304" t="inlineStr"/>
+      <c r="O304" t="inlineStr"/>
+      <c r="P304" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R304" t="n">
+        <v>0</v>
+      </c>
+      <c r="S304" t="n">
+        <v>0</v>
+      </c>
+      <c r="T304" t="n">
+        <v>0</v>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V304" t="n">
+        <v>-0.383</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>14</v>
+      </c>
+      <c r="D305" t="n">
+        <v>4</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>8 Iron</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G305" t="n">
+        <v>176.4</v>
+      </c>
+      <c r="H305" t="n">
+        <v>170.6</v>
+      </c>
+      <c r="I305" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="J305" t="n">
+        <v>30.0644487</v>
+      </c>
+      <c r="K305" t="n">
+        <v>-95.5078589</v>
+      </c>
+      <c r="L305" t="n">
+        <v>30.065680721739</v>
+      </c>
+      <c r="M305" t="n">
+        <v>-95.506974686956</v>
+      </c>
+      <c r="N305" t="inlineStr"/>
+      <c r="O305" t="inlineStr"/>
+      <c r="P305" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R305" t="n">
+        <v>0</v>
+      </c>
+      <c r="S305" t="n">
+        <v>0</v>
+      </c>
+      <c r="T305" t="n">
+        <v>0</v>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V305" t="n">
+        <v>-0.364</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>14</v>
+      </c>
+      <c r="D306" t="n">
+        <v>5</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G306" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="H306" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="I306" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J306" t="n">
+        <v>30.065680721739</v>
+      </c>
+      <c r="K306" t="n">
+        <v>-95.506974686956</v>
+      </c>
+      <c r="L306" t="n">
+        <v>30.0653936</v>
+      </c>
+      <c r="M306" t="n">
+        <v>-95.506665</v>
+      </c>
+      <c r="N306" t="inlineStr"/>
+      <c r="O306" t="inlineStr"/>
+      <c r="P306" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R306" t="n">
+        <v>0</v>
+      </c>
+      <c r="S306" t="n">
+        <v>0</v>
+      </c>
+      <c r="T306" t="n">
+        <v>0</v>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V306" t="n">
+        <v>0.569</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>14</v>
+      </c>
+      <c r="D307" t="n">
+        <v>6</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G307" t="n">
+        <v>1</v>
+      </c>
+      <c r="H307" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I307" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J307" t="n">
+        <v>30.0653936</v>
+      </c>
+      <c r="K307" t="n">
+        <v>-95.506665</v>
+      </c>
+      <c r="L307" t="n">
+        <v>30.065400602665</v>
+      </c>
+      <c r="M307" t="n">
+        <v>-95.506669981526</v>
+      </c>
+      <c r="N307" t="inlineStr"/>
+      <c r="O307" t="inlineStr"/>
+      <c r="P307" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R307" t="n">
+        <v>0</v>
+      </c>
+      <c r="S307" t="n">
+        <v>1</v>
+      </c>
+      <c r="T307" t="n">
+        <v>0</v>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V307" t="n">
+        <v>-0.747</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>14</v>
+      </c>
+      <c r="D308" t="n">
+        <v>7</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H308" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" t="n">
+        <v>30.065400602665</v>
+      </c>
+      <c r="K308" t="n">
+        <v>-95.506669981526</v>
+      </c>
+      <c r="L308" t="n">
+        <v>30.065405271108</v>
+      </c>
+      <c r="M308" t="n">
+        <v>-95.506673302544</v>
+      </c>
+      <c r="N308" t="inlineStr"/>
+      <c r="O308" t="inlineStr"/>
+      <c r="P308" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R308" t="n">
+        <v>0</v>
+      </c>
+      <c r="S308" t="n">
+        <v>1</v>
+      </c>
+      <c r="T308" t="n">
+        <v>0</v>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V308" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>15</v>
+      </c>
+      <c r="D309" t="n">
+        <v>1</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>211.7</v>
+      </c>
+      <c r="H309" t="n">
+        <v>375.2</v>
+      </c>
+      <c r="I309" t="n">
+        <v>193.2</v>
+      </c>
+      <c r="J309" t="n">
+        <v>30.0661593</v>
+      </c>
+      <c r="K309" t="n">
+        <v>-95.5074953</v>
+      </c>
+      <c r="L309" t="n">
+        <v>30.064474011765</v>
+      </c>
+      <c r="M309" t="n">
+        <v>-95.50800068088201</v>
+      </c>
+      <c r="N309" t="inlineStr"/>
+      <c r="O309" t="inlineStr"/>
+      <c r="P309" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R309" t="n">
+        <v>1</v>
+      </c>
+      <c r="S309" t="n">
+        <v>0</v>
+      </c>
+      <c r="T309" t="n">
+        <v>0</v>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V309" t="n">
+        <v>-0.202</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>15</v>
+      </c>
+      <c r="D310" t="n">
+        <v>2</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>163</v>
+      </c>
+      <c r="H310" t="n">
+        <v>193.2</v>
+      </c>
+      <c r="I310" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="J310" t="n">
+        <v>30.064474011765</v>
+      </c>
+      <c r="K310" t="n">
+        <v>-95.50800068088201</v>
+      </c>
+      <c r="L310" t="n">
+        <v>30.063916925</v>
+      </c>
+      <c r="M310" t="n">
+        <v>-95.509409866667</v>
+      </c>
+      <c r="N310" t="inlineStr"/>
+      <c r="O310" t="inlineStr"/>
+      <c r="P310" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R310" t="n">
+        <v>0</v>
+      </c>
+      <c r="S310" t="n">
+        <v>0</v>
+      </c>
+      <c r="T310" t="n">
+        <v>0</v>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V310" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>15</v>
+      </c>
+      <c r="D311" t="n">
+        <v>3</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G311" t="n">
+        <v>25</v>
+      </c>
+      <c r="H311" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="I311" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J311" t="n">
+        <v>30.063916925</v>
+      </c>
+      <c r="K311" t="n">
+        <v>-95.509409866667</v>
+      </c>
+      <c r="L311" t="n">
+        <v>30.063798831579</v>
+      </c>
+      <c r="M311" t="n">
+        <v>-95.509604821053</v>
+      </c>
+      <c r="N311" t="inlineStr"/>
+      <c r="O311" t="inlineStr"/>
+      <c r="P311" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R311" t="n">
+        <v>0</v>
+      </c>
+      <c r="S311" t="n">
+        <v>0</v>
+      </c>
+      <c r="T311" t="n">
+        <v>0</v>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V311" t="n">
+        <v>-0.428</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>15</v>
+      </c>
+      <c r="D312" t="n">
+        <v>4</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G312" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H312" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I312" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J312" t="n">
+        <v>30.063798831579</v>
+      </c>
+      <c r="K312" t="n">
+        <v>-95.509604821053</v>
+      </c>
+      <c r="L312" t="n">
+        <v>30.063668885354</v>
+      </c>
+      <c r="M312" t="n">
+        <v>-95.509574700282</v>
+      </c>
+      <c r="N312" t="inlineStr"/>
+      <c r="O312" t="inlineStr"/>
+      <c r="P312" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R312" t="n">
+        <v>0</v>
+      </c>
+      <c r="S312" t="n">
+        <v>1</v>
+      </c>
+      <c r="T312" t="n">
+        <v>0</v>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V312" t="n">
+        <v>-0.254</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>15</v>
+      </c>
+      <c r="D313" t="n">
+        <v>5</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G313" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H313" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I313" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J313" t="n">
+        <v>30.063668885354</v>
+      </c>
+      <c r="K313" t="n">
+        <v>-95.509574700282</v>
+      </c>
+      <c r="L313" t="n">
+        <v>30.063655447405</v>
+      </c>
+      <c r="M313" t="n">
+        <v>-95.50957158545</v>
+      </c>
+      <c r="N313" t="inlineStr"/>
+      <c r="O313" t="inlineStr"/>
+      <c r="P313" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R313" t="n">
+        <v>0</v>
+      </c>
+      <c r="S313" t="n">
+        <v>1</v>
+      </c>
+      <c r="T313" t="n">
+        <v>0</v>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V313" t="n">
+        <v>-0.579</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>15</v>
+      </c>
+      <c r="D314" t="n">
+        <v>6</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G314" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H314" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I314" t="n">
+        <v>0</v>
+      </c>
+      <c r="J314" t="n">
+        <v>30.063655447405</v>
+      </c>
+      <c r="K314" t="n">
+        <v>-95.50957158545</v>
+      </c>
+      <c r="L314" t="n">
+        <v>30.063650072226</v>
+      </c>
+      <c r="M314" t="n">
+        <v>-95.509570339517</v>
+      </c>
+      <c r="N314" t="inlineStr"/>
+      <c r="O314" t="inlineStr"/>
+      <c r="P314" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R314" t="n">
+        <v>0</v>
+      </c>
+      <c r="S314" t="n">
+        <v>1</v>
+      </c>
+      <c r="T314" t="n">
+        <v>0</v>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V314" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>16</v>
+      </c>
+      <c r="D315" t="n">
+        <v>1</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>8 Iron</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G315" t="n">
+        <v>157.3</v>
+      </c>
+      <c r="H315" t="n">
+        <v>151.1</v>
+      </c>
+      <c r="I315" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J315" t="n">
+        <v>30.0653375</v>
+      </c>
+      <c r="K315" t="n">
+        <v>-95.51000380000001</v>
+      </c>
+      <c r="L315" t="n">
+        <v>30.0665753</v>
+      </c>
+      <c r="M315" t="n">
+        <v>-95.510437</v>
+      </c>
+      <c r="N315" t="inlineStr"/>
+      <c r="O315" t="inlineStr"/>
+      <c r="P315" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R315" t="n">
+        <v>1</v>
+      </c>
+      <c r="S315" t="n">
+        <v>0</v>
+      </c>
+      <c r="T315" t="n">
+        <v>0</v>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V315" t="n">
+        <v>-0.029</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>16</v>
+      </c>
+      <c r="D316" t="n">
+        <v>2</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G316" t="n">
+        <v>9</v>
+      </c>
+      <c r="H316" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I316" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J316" t="n">
+        <v>30.0665753</v>
+      </c>
+      <c r="K316" t="n">
+        <v>-95.510437</v>
+      </c>
+      <c r="L316" t="n">
+        <v>30.066552658995</v>
+      </c>
+      <c r="M316" t="n">
+        <v>-95.510355339238</v>
+      </c>
+      <c r="N316" t="inlineStr"/>
+      <c r="O316" t="inlineStr"/>
+      <c r="P316" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R316" t="n">
+        <v>0</v>
+      </c>
+      <c r="S316" t="n">
+        <v>1</v>
+      </c>
+      <c r="T316" t="n">
+        <v>0</v>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V316" t="n">
+        <v>-0.424</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>16</v>
+      </c>
+      <c r="D317" t="n">
+        <v>3</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G317" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H317" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I317" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J317" t="n">
+        <v>30.066552658995</v>
+      </c>
+      <c r="K317" t="n">
+        <v>-95.510355339238</v>
+      </c>
+      <c r="L317" t="n">
+        <v>30.066548477524</v>
+      </c>
+      <c r="M317" t="n">
+        <v>-95.510340257682</v>
+      </c>
+      <c r="N317" t="inlineStr"/>
+      <c r="O317" t="inlineStr"/>
+      <c r="P317" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R317" t="n">
+        <v>0</v>
+      </c>
+      <c r="S317" t="n">
+        <v>1</v>
+      </c>
+      <c r="T317" t="n">
+        <v>0</v>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V317" t="n">
+        <v>-0.579</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>16</v>
+      </c>
+      <c r="D318" t="n">
+        <v>4</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G318" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H318" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I318" t="n">
+        <v>0</v>
+      </c>
+      <c r="J318" t="n">
+        <v>30.066548477524</v>
+      </c>
+      <c r="K318" t="n">
+        <v>-95.510340257682</v>
+      </c>
+      <c r="L318" t="n">
+        <v>30.066546804935</v>
+      </c>
+      <c r="M318" t="n">
+        <v>-95.51033422506001</v>
+      </c>
+      <c r="N318" t="inlineStr"/>
+      <c r="O318" t="inlineStr"/>
+      <c r="P318" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R318" t="n">
+        <v>0</v>
+      </c>
+      <c r="S318" t="n">
+        <v>1</v>
+      </c>
+      <c r="T318" t="n">
+        <v>0</v>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V318" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>17</v>
+      </c>
+      <c r="D319" t="n">
+        <v>1</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>3 Wood</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="G319" t="n">
+        <v>257.8</v>
+      </c>
+      <c r="H319" t="n">
+        <v>243.9</v>
+      </c>
+      <c r="I319" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="J319" t="n">
+        <v>30.0660282</v>
+      </c>
+      <c r="K319" t="n">
+        <v>-95.5119541</v>
+      </c>
+      <c r="L319" t="n">
+        <v>30.064059576471</v>
+      </c>
+      <c r="M319" t="n">
+        <v>-95.511045741177</v>
+      </c>
+      <c r="N319" t="inlineStr"/>
+      <c r="O319" t="inlineStr"/>
+      <c r="P319" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R319" t="n">
+        <v>1</v>
+      </c>
+      <c r="S319" t="n">
+        <v>0</v>
+      </c>
+      <c r="T319" t="n">
+        <v>0</v>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V319" t="n">
+        <v>-0.237</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>17</v>
+      </c>
+      <c r="D320" t="n">
+        <v>2</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>54 Wedge</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Wedge</t>
+        </is>
+      </c>
+      <c r="G320" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H320" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="I320" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J320" t="n">
+        <v>30.064059576471</v>
+      </c>
+      <c r="K320" t="n">
+        <v>-95.511045741177</v>
+      </c>
+      <c r="L320" t="n">
+        <v>30.064007</v>
+      </c>
+      <c r="M320" t="n">
+        <v>-95.5111686</v>
+      </c>
+      <c r="N320" t="inlineStr"/>
+      <c r="O320" t="inlineStr"/>
+      <c r="P320" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>rough</t>
+        </is>
+      </c>
+      <c r="R320" t="n">
+        <v>0</v>
+      </c>
+      <c r="S320" t="n">
+        <v>0</v>
+      </c>
+      <c r="T320" t="n">
+        <v>0</v>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V320" t="n">
+        <v>-0.525</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>17</v>
+      </c>
+      <c r="D321" t="n">
+        <v>3</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G321" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H321" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="I321" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J321" t="n">
+        <v>30.064007</v>
+      </c>
+      <c r="K321" t="n">
+        <v>-95.5111686</v>
+      </c>
+      <c r="L321" t="n">
+        <v>30.064092505522</v>
+      </c>
+      <c r="M321" t="n">
+        <v>-95.511329872647</v>
+      </c>
+      <c r="N321" t="inlineStr"/>
+      <c r="O321" t="inlineStr"/>
+      <c r="P321" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R321" t="n">
+        <v>0</v>
+      </c>
+      <c r="S321" t="n">
+        <v>1</v>
+      </c>
+      <c r="T321" t="n">
+        <v>0</v>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V321" t="n">
+        <v>0.218</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>17</v>
+      </c>
+      <c r="D322" t="n">
+        <v>4</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G322" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H322" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I322" t="n">
+        <v>0</v>
+      </c>
+      <c r="J322" t="n">
+        <v>30.064092505522</v>
+      </c>
+      <c r="K322" t="n">
+        <v>-95.511329872647</v>
+      </c>
+      <c r="L322" t="n">
+        <v>30.064095369347</v>
+      </c>
+      <c r="M322" t="n">
+        <v>-95.511335274142</v>
+      </c>
+      <c r="N322" t="inlineStr"/>
+      <c r="O322" t="inlineStr"/>
+      <c r="P322" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R322" t="n">
+        <v>0</v>
+      </c>
+      <c r="S322" t="n">
+        <v>1</v>
+      </c>
+      <c r="T322" t="n">
+        <v>0</v>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V322" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>18</v>
+      </c>
+      <c r="D323" t="n">
+        <v>1</v>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G323" t="n">
+        <v>293.4</v>
+      </c>
+      <c r="H323" t="n">
+        <v>462.6</v>
+      </c>
+      <c r="I323" t="n">
+        <v>171</v>
+      </c>
+      <c r="J323" t="n">
+        <v>30.063958663165</v>
+      </c>
+      <c r="K323" t="n">
+        <v>-95.50984371453499</v>
+      </c>
+      <c r="L323" t="n">
+        <v>30.061728098709</v>
+      </c>
+      <c r="M323" t="n">
+        <v>-95.51090721041</v>
+      </c>
+      <c r="N323" t="inlineStr"/>
+      <c r="O323" t="inlineStr"/>
+      <c r="P323" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="R323" t="n">
+        <v>1</v>
+      </c>
+      <c r="S323" t="n">
+        <v>0</v>
+      </c>
+      <c r="T323" t="n">
+        <v>0</v>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>off_tee</t>
+        </is>
+      </c>
+      <c r="V323" t="n">
+        <v>0.149</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>18</v>
+      </c>
+      <c r="D324" t="n">
+        <v>2</v>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>5 Iron</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G324" t="n">
+        <v>166</v>
+      </c>
+      <c r="H324" t="n">
+        <v>171</v>
+      </c>
+      <c r="I324" t="n">
+        <v>5</v>
+      </c>
+      <c r="J324" t="n">
+        <v>30.061728098709</v>
+      </c>
+      <c r="K324" t="n">
+        <v>-95.51090721041</v>
+      </c>
+      <c r="L324" t="n">
+        <v>30.060580836372</v>
+      </c>
+      <c r="M324" t="n">
+        <v>-95.51176172450801</v>
+      </c>
+      <c r="N324" t="inlineStr"/>
+      <c r="O324" t="inlineStr"/>
+      <c r="P324" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>fairway</t>
+        </is>
+      </c>
+      <c r="R324" t="n">
+        <v>0</v>
+      </c>
+      <c r="S324" t="n">
+        <v>0</v>
+      </c>
+      <c r="T324" t="n">
+        <v>0</v>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="V324" t="n">
+        <v>0.245</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>18</v>
+      </c>
+      <c r="D325" t="n">
+        <v>3</v>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G325" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H325" t="n">
+        <v>5</v>
+      </c>
+      <c r="I325" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J325" t="n">
+        <v>30.060580836372</v>
+      </c>
+      <c r="K325" t="n">
+        <v>-95.51176172450801</v>
+      </c>
+      <c r="L325" t="n">
+        <v>30.060550885443</v>
+      </c>
+      <c r="M325" t="n">
+        <v>-95.511784032504</v>
+      </c>
+      <c r="N325" t="inlineStr"/>
+      <c r="O325" t="inlineStr"/>
+      <c r="P325" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R325" t="n">
+        <v>0</v>
+      </c>
+      <c r="S325" t="n">
+        <v>1</v>
+      </c>
+      <c r="T325" t="n">
+        <v>0</v>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V325" t="n">
+        <v>-0.223</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>28279143</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>18</v>
+      </c>
+      <c r="D326" t="n">
+        <v>4</v>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Putter</t>
+        </is>
+      </c>
+      <c r="G326" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H326" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I326" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" t="n">
+        <v>30.060550885443</v>
+      </c>
+      <c r="K326" t="n">
+        <v>-95.511784032504</v>
+      </c>
+      <c r="L326" t="n">
+        <v>30.060546277607</v>
+      </c>
+      <c r="M326" t="n">
+        <v>-95.51178746450201</v>
+      </c>
+      <c r="N326" t="inlineStr"/>
+      <c r="O326" t="inlineStr"/>
+      <c r="P326" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R326" t="n">
+        <v>0</v>
+      </c>
+      <c r="S326" t="n">
+        <v>1</v>
+      </c>
+      <c r="T326" t="n">
+        <v>0</v>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>putting</t>
+        </is>
+      </c>
+      <c r="V326" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -23174,32 +31497,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>264.2</v>
+        <v>271.6</v>
       </c>
       <c r="F2" t="n">
-        <v>264.2</v>
+        <v>271.6</v>
       </c>
       <c r="G2" t="n">
-        <v>270.5</v>
+        <v>275.7</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>285.2</v>
+        <v>293.9</v>
       </c>
       <c r="L2" t="n">
-        <v>265.412</v>
+        <v>269.719</v>
       </c>
       <c r="M2" t="n">
-        <v>271.155</v>
+        <v>280.937</v>
       </c>
       <c r="N2" t="n">
-        <v>5.7</v>
+        <v>11.2</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -23224,13 +31547,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229</v>
+        <v>238.2</v>
       </c>
       <c r="F3" t="n">
-        <v>229</v>
+        <v>238.2</v>
       </c>
       <c r="G3" t="n">
-        <v>239</v>
+        <v>246.7</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
@@ -23238,22 +31561,22 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>239.8</v>
+        <v>257.2</v>
       </c>
       <c r="L3" t="n">
-        <v>225.476</v>
+        <v>237.963</v>
       </c>
       <c r="M3" t="n">
-        <v>238.387</v>
+        <v>244.141</v>
       </c>
       <c r="N3" t="n">
-        <v>12.9</v>
+        <v>6.2</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -23278,7 +31601,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>200.1</v>
+        <v>210.6</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -23320,42 +31643,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>196.3</v>
+        <v>208.9</v>
       </c>
       <c r="F5" t="n">
-        <v>196.3</v>
+        <v>208.9</v>
       </c>
       <c r="G5" t="n">
         <v>184.1</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>192.4</v>
+      </c>
       <c r="I5" t="n">
-        <v>220.5</v>
+        <v>221.8</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>220.5</v>
+        <v>223.9</v>
       </c>
       <c r="L5" t="n">
-        <v>200.447</v>
+        <v>190.773</v>
       </c>
       <c r="M5" t="n">
-        <v>211.369</v>
+        <v>220.471</v>
       </c>
       <c r="N5" t="n">
-        <v>10.9</v>
+        <v>29.7</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6 Iron</t>
+          <t>5 Iron</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -23374,42 +31699,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>157.4</v>
+        <v>169</v>
       </c>
       <c r="F6" t="n">
-        <v>157.4</v>
+        <v>169</v>
       </c>
       <c r="G6" t="n">
-        <v>165</v>
+        <v>183.8</v>
       </c>
       <c r="H6" t="n">
-        <v>160.3</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>166.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>163.5</v>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>165</v>
+        <v>212.3</v>
       </c>
       <c r="L6" t="n">
-        <v>162.432</v>
+        <v>150.055</v>
       </c>
       <c r="M6" t="n">
-        <v>163.829</v>
+        <v>177.084</v>
       </c>
       <c r="N6" t="n">
-        <v>1.4</v>
+        <v>27</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7 Iron</t>
+          <t>8 Iron</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -23428,44 +31755,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>155.4</v>
+        <v>157.5</v>
       </c>
       <c r="F7" t="n">
-        <v>155.4</v>
+        <v>157.5</v>
       </c>
       <c r="G7" t="n">
-        <v>161.9</v>
+        <v>166.3</v>
       </c>
       <c r="H7" t="n">
-        <v>155</v>
-      </c>
-      <c r="I7" t="n">
-        <v>134.1</v>
-      </c>
+        <v>159.6</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>161.9</v>
+        <v>176.1</v>
       </c>
       <c r="L7" t="n">
-        <v>150.417</v>
+        <v>161.565</v>
       </c>
       <c r="M7" t="n">
-        <v>157.992</v>
+        <v>171.748</v>
       </c>
       <c r="N7" t="n">
-        <v>7.6</v>
+        <v>10.2</v>
       </c>
       <c r="O7" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5 Iron</t>
+          <t>6 Iron</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -23484,44 +31809,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>147.8</v>
+        <v>157.4</v>
       </c>
       <c r="F8" t="n">
-        <v>147.8</v>
+        <v>157.4</v>
       </c>
       <c r="G8" t="n">
-        <v>164.9</v>
+        <v>165</v>
       </c>
       <c r="H8" t="n">
-        <v>155.1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>163.5</v>
-      </c>
+        <v>160.3</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="L8" t="n">
-        <v>148.758</v>
+        <v>162.432</v>
       </c>
       <c r="M8" t="n">
-        <v>169.921</v>
+        <v>163.829</v>
       </c>
       <c r="N8" t="n">
-        <v>21.2</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8 Iron</t>
+          <t>7 Iron</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -23540,24 +31863,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>141.3</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+        <v>155.4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>155.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>163.6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>155</v>
+      </c>
+      <c r="I9" t="n">
+        <v>134.1</v>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>170.3</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+        <v>164.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>151.053</v>
+      </c>
+      <c r="M9" t="n">
+        <v>161.048</v>
+      </c>
+      <c r="N9" t="n">
+        <v>10</v>
+      </c>
       <c r="O9" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -23582,36 +31919,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F10" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G10" t="n">
         <v>127.9</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>219.6</v>
+      </c>
       <c r="I10" t="n">
         <v>144.1</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>152</v>
+        <v>219.6</v>
       </c>
       <c r="L10" t="n">
-        <v>132.87</v>
+        <v>142.004</v>
       </c>
       <c r="M10" t="n">
-        <v>147.537</v>
+        <v>151.96</v>
       </c>
       <c r="N10" t="n">
-        <v>14.7</v>
+        <v>10</v>
       </c>
       <c r="O10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -23642,32 +31981,32 @@
         <v>112.7</v>
       </c>
       <c r="G11" t="n">
-        <v>129</v>
+        <v>126.8</v>
       </c>
       <c r="H11" t="n">
-        <v>111.5</v>
+        <v>124.5</v>
       </c>
       <c r="I11" t="n">
-        <v>105</v>
+        <v>111.4</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>131.2</v>
+        <v>143.1</v>
       </c>
       <c r="L11" t="n">
-        <v>112.531</v>
+        <v>111.639</v>
       </c>
       <c r="M11" t="n">
-        <v>121.317</v>
+        <v>123.878</v>
       </c>
       <c r="N11" t="n">
-        <v>8.800000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="O11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -23746,34 +32085,36 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>91.2</v>
+        <v>88</v>
       </c>
       <c r="F13" t="n">
-        <v>91.2</v>
+        <v>88</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>91.40000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>91.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
         <v>94.3</v>
       </c>
       <c r="L13" t="n">
-        <v>86.3596</v>
+        <v>79.40179999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>93.34439999999999</v>
+        <v>91.6682</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
+        <v>12.3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="P13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -23798,36 +32139,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>72.2</v>
+        <v>64.5</v>
       </c>
       <c r="F14" t="n">
-        <v>72.2</v>
+        <v>64.5</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>59.2</v>
+        <v>62.1</v>
       </c>
       <c r="I14" t="n">
-        <v>92.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
         <v>102.4</v>
       </c>
       <c r="L14" t="n">
-        <v>67.6871</v>
+        <v>64.3009</v>
       </c>
       <c r="M14" t="n">
-        <v>85.49679999999999</v>
+        <v>68.1348</v>
       </c>
       <c r="N14" t="n">
-        <v>17.8</v>
+        <v>3.8</v>
       </c>
       <c r="O14" t="n">
         <v>100</v>
       </c>
       <c r="P14" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -23841,7 +32182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23892,30 +32233,30 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>28154206</v>
+        <v>28279143</v>
       </c>
       <c r="B2" t="n">
-        <v>-18.0783</v>
+        <v>-16.3353</v>
       </c>
       <c r="C2" t="n">
-        <v>-18.7461</v>
+        <v>-15.2098</v>
       </c>
       <c r="D2" t="n">
-        <v>-27.3458</v>
+        <v>-22.4244</v>
       </c>
       <c r="E2" t="n">
-        <v>-18.5154</v>
+        <v>-13.0907</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.47542</v>
+        <v>-1.41453</v>
       </c>
       <c r="G2" t="n">
-        <v>-8.83972</v>
+        <v>-16.8471</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>28063887</v>
+        <v>28154206</v>
       </c>
       <c r="B3" t="n">
         <v>-18.0783</v>
@@ -23924,7 +32265,7 @@
         <v>-18.7461</v>
       </c>
       <c r="D3" t="n">
-        <v>-27.3459</v>
+        <v>-27.3458</v>
       </c>
       <c r="E3" t="n">
         <v>-18.5154</v>
@@ -23938,24 +32279,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>28063887</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-18.0783</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-18.7461</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-27.3459</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-18.5154</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-2.47542</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-8.83972</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>27924130</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B5" t="n">
         <v>-20.4148</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C5" t="n">
         <v>-7.49223</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>-30</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E5" t="n">
         <v>-30</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" t="n">
         <v>-4.95085</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G5" t="n">
         <v>-10.2852</v>
       </c>
     </row>
@@ -24002,7 +32366,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-21.6</v>
+        <v>-20.1</v>
       </c>
     </row>
     <row r="5">
@@ -24022,7 +32386,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-12.6</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="7">
@@ -24042,7 +32406,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-4.2</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="9">
@@ -24063,7 +32427,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45.7</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="12">
@@ -24073,7 +32437,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26.7</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="13">
@@ -24093,7 +32457,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.7</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="15">
@@ -24103,7 +32467,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14.3</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="16">
@@ -24123,7 +32487,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15.6</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="18">
@@ -24133,7 +32497,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="19">
@@ -24143,7 +32507,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31.33</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="20">
@@ -24171,7 +32535,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -24181,7 +32545,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -24191,7 +32555,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -24201,7 +32565,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27">
@@ -24221,7 +32585,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -24241,7 +32605,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -24251,7 +32615,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7071.18</v>
+        <v>10028.48</v>
       </c>
     </row>
     <row r="32">
@@ -24261,7 +32625,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>260.8</v>
+        <v>268.75</v>
       </c>
     </row>
     <row r="33">
@@ -24271,7 +32635,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34">
@@ -24281,7 +32645,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35">
@@ -24291,7 +32655,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>50.67</v>
+        <v>51.72</v>
       </c>
     </row>
     <row r="36">
@@ -24311,7 +32675,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
@@ -24321,7 +32685,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
@@ -24331,7 +32695,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40">
@@ -24341,7 +32705,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>964.01</v>
+        <v>1328.09</v>
       </c>
     </row>
     <row r="41">
@@ -24351,7 +32715,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>168.31</v>
+        <v>170.85</v>
       </c>
     </row>
     <row r="42">
@@ -24361,7 +32725,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>54.53</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="43">
@@ -24371,7 +32735,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-18.75</v>
+        <v>-15.21</v>
       </c>
     </row>
     <row r="44">
@@ -24448,7 +32812,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
@@ -24458,7 +32822,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53">
@@ -24468,7 +32832,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54">
@@ -24478,7 +32842,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55">
@@ -24508,7 +32872,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
@@ -24518,7 +32882,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59">
@@ -24528,7 +32892,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60">
@@ -24538,7 +32902,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>238</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61">
@@ -24548,7 +32912,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2408.26</v>
+        <v>3137.14</v>
       </c>
     </row>
     <row r="62">
@@ -24558,7 +32922,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>264.36</v>
+        <v>360.6</v>
       </c>
     </row>
     <row r="63">
@@ -24568,7 +32932,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>170.91</v>
+        <v>230.21</v>
       </c>
     </row>
     <row r="64">
@@ -24578,7 +32942,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -24588,7 +32952,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-27.35</v>
+        <v>-22.42</v>
       </c>
     </row>
     <row r="66">
@@ -24655,7 +33019,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73">
@@ -24665,7 +33029,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -24675,7 +33039,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75">
@@ -24695,7 +33059,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77">
@@ -24715,7 +33079,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="79">
@@ -24725,7 +33089,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>84</v>
+        <v>107</v>
       </c>
     </row>
     <row r="80">
@@ -24735,7 +33099,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>244.28</v>
+        <v>301.75</v>
       </c>
     </row>
     <row r="81">
@@ -24745,7 +33109,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>202.09</v>
+        <v>259.56</v>
       </c>
     </row>
     <row r="82">
@@ -24755,7 +33119,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>176.83</v>
+        <v>234.3</v>
       </c>
     </row>
     <row r="83">
@@ -24845,7 +33209,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-18.52</v>
+        <v>-13.09</v>
       </c>
     </row>
     <row r="92">
@@ -25102,7 +33466,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-2.48</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="118">
@@ -25129,7 +33493,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121">
@@ -25139,7 +33503,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="122">
@@ -25149,7 +33513,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="123">
@@ -25159,7 +33523,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>94</v>
+        <v>133</v>
       </c>
     </row>
     <row r="124">
@@ -25169,7 +33533,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="125">
@@ -25179,7 +33543,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="126">
@@ -25189,7 +33553,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="127">
@@ -25219,7 +33583,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-9.69</v>
+        <v>-14.72</v>
       </c>
     </row>
     <row r="130">
@@ -25229,7 +33593,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-8.84</v>
+        <v>-16.85</v>
       </c>
     </row>
     <row r="131">
@@ -25266,7 +33630,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135">
@@ -25276,7 +33640,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="136">
@@ -25286,7 +33650,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137">
@@ -25296,7 +33660,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="138">
@@ -25306,7 +33670,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
     </row>
     <row r="139">
@@ -25316,7 +33680,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="140">
@@ -25326,7 +33690,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>130</v>
+        <v>179</v>
       </c>
     </row>
     <row r="141">
@@ -25336,7 +33700,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="142">
@@ -25346,7 +33710,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
     </row>
     <row r="143">
@@ -25356,7 +33720,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="144">
@@ -25366,7 +33730,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-18.08</v>
+        <v>-16.34</v>
       </c>
     </row>
   </sheetData>
@@ -25401,7 +33765,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -25412,7 +33776,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>45 / 236</t>
+          <t>63 / 325</t>
         </is>
       </c>
     </row>
@@ -25424,7 +33788,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-06 -&gt; 2026-06-19</t>
+          <t>2026-06-06 -&gt; 2026-06-26</t>
         </is>
       </c>
     </row>
@@ -25447,7 +33811,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>79</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="8">
@@ -25457,7 +33821,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="9">
@@ -25467,7 +33831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-18.1</v>
+        <v>-17.43</v>
       </c>
     </row>
     <row r="10">
@@ -25477,7 +33841,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-3</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="11">
@@ -25487,7 +33851,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-10.37</v>
+        <v>-9.17</v>
       </c>
     </row>
     <row r="12">
@@ -25497,7 +33861,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>-1.93</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="13">
@@ -25507,7 +33871,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-2.8</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="14">
@@ -25517,7 +33881,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-16.98</v>
+        <v>-16.63</v>
       </c>
     </row>
     <row r="15">
@@ -25527,7 +33891,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25.93</v>
+        <v>27.77</v>
       </c>
     </row>
     <row r="16">
@@ -25537,7 +33901,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>47.6</v>
+        <v>44.62</v>
       </c>
     </row>
     <row r="17">
@@ -25547,7 +33911,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="18">
@@ -25557,7 +33921,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>10.63</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="19">
@@ -25567,7 +33931,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31.33</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="20">
@@ -25577,7 +33941,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="21">
@@ -25587,7 +33951,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="22">
@@ -25597,7 +33961,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="23">
@@ -25607,7 +33971,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>222.83</v>
+        <v>224.95</v>
       </c>
     </row>
     <row r="24">
@@ -25617,7 +33981,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>280.4</v>
+        <v>283.95</v>
       </c>
     </row>
     <row r="25">
@@ -25627,7 +33991,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="26">
@@ -25637,7 +34001,7 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>-22.34</v>
+        <v>-20.03</v>
       </c>
     </row>
     <row r="27">
@@ -25647,7 +34011,7 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>-3.3</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="29">
@@ -25679,7 +34043,7 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>16.7</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="32">
@@ -25689,7 +34053,7 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>14.3</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="33">
@@ -25709,7 +34073,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26.7</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="35">
@@ -25719,7 +34083,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>45.7</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="36">
@@ -25729,7 +34093,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15.6</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="37">
@@ -25739,7 +34103,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="38">
@@ -25749,7 +34113,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.33</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="40">
@@ -25776,7 +34140,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-19 23:48 UTC  |  Rounds: 3  Shots: 236</t>
+          <t>Date pulled: 2026-06-27 02:40 UTC  |  Rounds: 4  Shots: 325</t>
         </is>
       </c>
     </row>

--- a/arccos_sg_baseline.xlsx
+++ b/arccos_sg_baseline.xlsx
@@ -34140,7 +34140,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Date pulled: 2026-06-27 02:40 UTC  |  Rounds: 4  Shots: 325</t>
+          <t>Date pulled: 2026-06-27 13:23 UTC  |  Rounds: 4  Shots: 325</t>
         </is>
       </c>
     </row>
